--- a/research/traditional_assets/database/data/qatar/qatar_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_telecom_services.xlsx
@@ -647,10 +647,10 @@
         <v>0.1265493324329267</v>
       </c>
       <c r="X2">
-        <v>0.08221894212014037</v>
+        <v>0.08220095282327598</v>
       </c>
       <c r="Y2">
-        <v>0.04433039031278636</v>
+        <v>0.04434837960965075</v>
       </c>
       <c r="Z2">
         <v>0.7394685750406357</v>
@@ -659,10 +659,10 @@
         <v>0.1323927841797245</v>
       </c>
       <c r="AB2">
-        <v>0.07379283244844961</v>
+        <v>0.07378007927419104</v>
       </c>
       <c r="AC2">
-        <v>0.05859995173127491</v>
+        <v>0.05861270490553348</v>
       </c>
       <c r="AD2">
         <v>4172.5</v>
@@ -781,10 +781,10 @@
         <v>0.1265493324329267</v>
       </c>
       <c r="X3">
-        <v>0.08221894212014037</v>
+        <v>0.08220095282327598</v>
       </c>
       <c r="Y3">
-        <v>0.04433039031278636</v>
+        <v>0.04434837960965075</v>
       </c>
       <c r="Z3">
         <v>0.7394685750406357</v>
@@ -793,10 +793,10 @@
         <v>0.1323927841797245</v>
       </c>
       <c r="AB3">
-        <v>0.07379283244844961</v>
+        <v>0.07378007927419104</v>
       </c>
       <c r="AC3">
-        <v>0.05859995173127491</v>
+        <v>0.05861270490553348</v>
       </c>
       <c r="AD3">
         <v>4172.5</v>
@@ -1151,13 +1151,13 @@
         <v>10162.6</v>
       </c>
       <c r="L2">
-        <v>14463.4096341336</v>
+        <v>14463.446627001</v>
       </c>
       <c r="M2">
         <v>10791.7</v>
       </c>
       <c r="N2">
-        <v>10920.0096341336</v>
+        <v>10920.046627001</v>
       </c>
       <c r="O2">
         <v>4172.5</v>
@@ -1166,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0737928324484496</v>
+        <v>0.073780079274191</v>
       </c>
       <c r="R2">
-        <v>0.0723925513775575</v>
+        <v>0.0723794158696799</v>
       </c>
       <c r="S2">
         <v>0.0532700805851723</v>
       </c>
       <c r="T2">
-        <v>0.0509300805851723</v>
+        <v>0.0496700805851723</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0822189421201404</v>
+        <v>0.082200952823276</v>
       </c>
       <c r="X2">
-        <v>0.0723925513775575</v>
+        <v>0.0723794158696799</v>
       </c>
       <c r="Y2">
         <v>0.729608321237027</v>
@@ -1230,7 +1230,7 @@
         <v>10162.6</v>
       </c>
       <c r="AK2">
-        <v>0.04991574391365663</v>
+        <v>0.04989108781210082</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07239255137755748</v>
+        <v>0.07237941586967991</v>
       </c>
       <c r="C2">
-        <v>14463.40963413359</v>
+        <v>14463.44662700098</v>
       </c>
       <c r="D2">
-        <v>10920.00963413359</v>
+        <v>10920.04662700098</v>
       </c>
       <c r="E2">
         <v>-4172.5</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07239255137755748</v>
+        <v>0.07237941586967991</v>
       </c>
       <c r="T2">
         <v>0.532748774085323</v>
       </c>
       <c r="U2">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V2">
         <v>0.1</v>
       </c>
       <c r="W2">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07241725963203166</v>
+        <v>0.07239153725966195</v>
       </c>
       <c r="C3">
-        <v>14317.76814535546</v>
+        <v>14318.97181663384</v>
       </c>
       <c r="D3">
-        <v>10917.71914535546</v>
+        <v>10918.92281663384</v>
       </c>
       <c r="E3">
         <v>-4029.149</v>
@@ -1533,37 +1533,37 @@
         <v>1052.8</v>
       </c>
       <c r="M3">
-        <v>8.112086646627821</v>
+        <v>7.911395246627821</v>
       </c>
       <c r="N3">
-        <v>1044.687913353372</v>
+        <v>1044.888604753372</v>
       </c>
       <c r="O3">
-        <v>104.4687913353372</v>
+        <v>104.4888604753372</v>
       </c>
       <c r="P3">
-        <v>940.2191220180349</v>
+        <v>940.399744278035</v>
       </c>
       <c r="Q3">
-        <v>2165.519122018035</v>
+        <v>2165.699744278035</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.0726343018446262</v>
+        <v>0.07262104692304064</v>
       </c>
       <c r="T3">
         <v>0.5375919447588259</v>
       </c>
       <c r="U3">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V3">
         <v>0.1</v>
       </c>
       <c r="W3">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>129.7816512398381</v>
+        <v>133.0738722033574</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07244196788650582</v>
+        <v>0.07240365864964399</v>
       </c>
       <c r="C4">
-        <v>14172.1276172429</v>
+        <v>14174.49723755138</v>
       </c>
       <c r="D4">
-        <v>10915.4296172429</v>
+        <v>10917.79923755138</v>
       </c>
       <c r="E4">
         <v>-3885.798</v>
@@ -1615,37 +1615,37 @@
         <v>1052.8</v>
       </c>
       <c r="M4">
-        <v>16.22417329325564</v>
+        <v>15.82279049325564</v>
       </c>
       <c r="N4">
-        <v>1036.575826706744</v>
+        <v>1036.977209506744</v>
       </c>
       <c r="O4">
-        <v>103.6575826706744</v>
+        <v>103.6977209506744</v>
       </c>
       <c r="P4">
-        <v>932.9182440360698</v>
+        <v>933.2794885560697</v>
       </c>
       <c r="Q4">
-        <v>2158.21824403607</v>
+        <v>2158.57948855607</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07288098599469631</v>
+        <v>0.07286760922238832</v>
       </c>
       <c r="T4">
         <v>0.5425339556501554</v>
       </c>
       <c r="U4">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V4">
         <v>0.1</v>
       </c>
       <c r="W4">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.89082561991907</v>
+        <v>66.53693610167871</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07246667614097999</v>
+        <v>0.07241578003962604</v>
       </c>
       <c r="C5">
-        <v>14026.48804919166</v>
+        <v>14030.02288968222</v>
       </c>
       <c r="D5">
-        <v>10913.14104919166</v>
+        <v>10916.67588968222</v>
       </c>
       <c r="E5">
         <v>-3742.447</v>
@@ -1697,37 +1697,37 @@
         <v>1052.8</v>
       </c>
       <c r="M5">
-        <v>24.33625993988346</v>
+        <v>23.73418573988346</v>
       </c>
       <c r="N5">
-        <v>1028.463740060116</v>
+        <v>1029.065814260116</v>
       </c>
       <c r="O5">
-        <v>102.8463740060116</v>
+        <v>102.9065814260117</v>
       </c>
       <c r="P5">
-        <v>925.6173660541048</v>
+        <v>926.1592328341048</v>
       </c>
       <c r="Q5">
-        <v>2150.917366054105</v>
+        <v>2151.459232834105</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07313275641590188</v>
+        <v>0.07311925528048543</v>
       </c>
       <c r="T5">
         <v>0.5475778636732649</v>
       </c>
       <c r="U5">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V5">
         <v>0.1</v>
       </c>
       <c r="W5">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.26055041327938</v>
+        <v>44.35795740111914</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07249138439545415</v>
+        <v>0.0724279014296081</v>
       </c>
       <c r="C6">
-        <v>13880.84944059801</v>
+        <v>13885.54877295499</v>
       </c>
       <c r="D6">
-        <v>10910.85344059801</v>
+        <v>10915.55277295499</v>
       </c>
       <c r="E6">
         <v>-3599.096</v>
@@ -1779,37 +1779,37 @@
         <v>1052.8</v>
       </c>
       <c r="M6">
-        <v>32.44834658651128</v>
+        <v>31.64558098651128</v>
       </c>
       <c r="N6">
-        <v>1020.351653413489</v>
+        <v>1021.154419013489</v>
       </c>
       <c r="O6">
-        <v>102.0351653413489</v>
+        <v>102.1154419013489</v>
       </c>
       <c r="P6">
-        <v>918.3164880721398</v>
+        <v>919.0389771121398</v>
       </c>
       <c r="Q6">
-        <v>2143.61648807214</v>
+        <v>2144.33897711214</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.0733897720542159</v>
+        <v>0.07337614396479292</v>
       </c>
       <c r="T6">
         <v>0.5527268531135227</v>
       </c>
       <c r="U6">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V6">
         <v>0.1</v>
       </c>
       <c r="W6">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.44541280995954</v>
+        <v>33.26846805083935</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07251609264992831</v>
+        <v>0.07244002281959012</v>
       </c>
       <c r="C7">
-        <v>13735.21179085869</v>
+        <v>13741.07488729837</v>
       </c>
       <c r="D7">
-        <v>10908.56679085869</v>
+        <v>10914.42988729837</v>
       </c>
       <c r="E7">
         <v>-3455.745</v>
@@ -1861,37 +1861,37 @@
         <v>1052.8</v>
       </c>
       <c r="M7">
-        <v>40.56043323313911</v>
+        <v>39.55697623313911</v>
       </c>
       <c r="N7">
-        <v>1012.239566766861</v>
+        <v>1013.243023766861</v>
       </c>
       <c r="O7">
-        <v>101.2239566766861</v>
+        <v>101.3243023766861</v>
       </c>
       <c r="P7">
-        <v>911.0156100901747</v>
+        <v>911.9187213901747</v>
       </c>
       <c r="Q7">
-        <v>2136.315610090175</v>
+        <v>2137.218721390175</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07365219854807337</v>
+        <v>0.0736384408319279</v>
       </c>
       <c r="T7">
         <v>0.5579842423314698</v>
       </c>
       <c r="U7">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V7">
         <v>0.1</v>
       </c>
       <c r="W7">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.95633024796763</v>
+        <v>26.61477444067148</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07254080090440249</v>
+        <v>0.07245214420957218</v>
       </c>
       <c r="C8">
-        <v>13589.57509937098</v>
+        <v>13596.60123264103</v>
       </c>
       <c r="D8">
-        <v>10906.28109937098</v>
+        <v>10913.30723264103</v>
       </c>
       <c r="E8">
         <v>-3312.394</v>
@@ -1943,37 +1943,37 @@
         <v>1052.8</v>
       </c>
       <c r="M8">
-        <v>48.67251987976692</v>
+        <v>47.46837147976692</v>
       </c>
       <c r="N8">
-        <v>1004.127480120233</v>
+        <v>1005.331628520233</v>
       </c>
       <c r="O8">
-        <v>100.4127480120233</v>
+        <v>100.5331628520233</v>
       </c>
       <c r="P8">
-        <v>903.7147321082098</v>
+        <v>904.7984656682097</v>
       </c>
       <c r="Q8">
-        <v>2129.01473210821</v>
+        <v>2130.098465668209</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07392020858435336</v>
+        <v>0.07390631848347004</v>
       </c>
       <c r="T8">
         <v>0.5633534908944798</v>
       </c>
       <c r="U8">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V8">
         <v>0.1</v>
       </c>
       <c r="W8">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.63027520663969</v>
+        <v>22.17897870055957</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07256550915887665</v>
+        <v>0.0724642655995542</v>
       </c>
       <c r="C9">
-        <v>13443.93936553266</v>
+        <v>13452.12780891172</v>
       </c>
       <c r="D9">
-        <v>10903.99636553266</v>
+        <v>10912.18480891172</v>
       </c>
       <c r="E9">
         <v>-3169.043</v>
@@ -2025,37 +2025,37 @@
         <v>1052.8</v>
       </c>
       <c r="M9">
-        <v>56.78460652639475</v>
+        <v>55.37976672639476</v>
       </c>
       <c r="N9">
-        <v>996.0153934736052</v>
+        <v>997.4202332736052</v>
       </c>
       <c r="O9">
-        <v>99.60153934736053</v>
+        <v>99.74202332736053</v>
       </c>
       <c r="P9">
-        <v>896.4138541262446</v>
+        <v>897.6782099462446</v>
       </c>
       <c r="Q9">
-        <v>2121.713854126245</v>
+        <v>2122.978209946245</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07419398227732751</v>
+        <v>0.07417995694472274</v>
       </c>
       <c r="T9">
         <v>0.5688382071685223</v>
       </c>
       <c r="U9">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V9">
         <v>0.1</v>
       </c>
       <c r="W9">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.54023589140544</v>
+        <v>19.0105531719082</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07259021741335081</v>
+        <v>0.07247638698953625</v>
       </c>
       <c r="C10">
-        <v>13298.304588742</v>
+        <v>13307.65461603919</v>
       </c>
       <c r="D10">
-        <v>10901.712588742</v>
+        <v>10911.06261603919</v>
       </c>
       <c r="E10">
         <v>-3025.692</v>
@@ -2107,37 +2107,37 @@
         <v>1052.8</v>
       </c>
       <c r="M10">
-        <v>64.89669317302257</v>
+        <v>63.29116197302257</v>
       </c>
       <c r="N10">
-        <v>987.9033068269774</v>
+        <v>989.5088380269774</v>
       </c>
       <c r="O10">
-        <v>98.79033068269774</v>
+        <v>98.95088380269775</v>
       </c>
       <c r="P10">
-        <v>889.1129761442796</v>
+        <v>890.5579542242797</v>
       </c>
       <c r="Q10">
-        <v>2114.41297614428</v>
+        <v>2115.85795422428</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07447370757232286</v>
+        <v>0.07445954406817659</v>
       </c>
       <c r="T10">
         <v>0.5744421564050439</v>
       </c>
       <c r="U10">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V10">
         <v>0.1</v>
       </c>
       <c r="W10">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.22270640497977</v>
+        <v>16.63423402541968</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07261492566782497</v>
+        <v>0.07248850837951828</v>
       </c>
       <c r="C11">
-        <v>13152.67076839778</v>
+        <v>13163.18165395222</v>
       </c>
       <c r="D11">
-        <v>10899.42976839778</v>
+        <v>10909.94065395222</v>
       </c>
       <c r="E11">
         <v>-2882.341</v>
@@ -2189,37 +2189,37 @@
         <v>1052.8</v>
       </c>
       <c r="M11">
-        <v>73.00877981965039</v>
+        <v>71.20255721965039</v>
       </c>
       <c r="N11">
-        <v>979.7912201803496</v>
+        <v>981.5974427803495</v>
       </c>
       <c r="O11">
-        <v>97.97912201803496</v>
+        <v>98.15974427803496</v>
       </c>
       <c r="P11">
-        <v>881.8120981623147</v>
+        <v>883.4376985023146</v>
       </c>
       <c r="Q11">
-        <v>2107.112098162314</v>
+        <v>2108.737698502315</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07475958067599942</v>
+        <v>0.07474527596357448</v>
       </c>
       <c r="T11">
         <v>0.5801692693610494</v>
       </c>
       <c r="U11">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V11">
         <v>0.1</v>
       </c>
       <c r="W11">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.42018347109313</v>
+        <v>14.78598580037305</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07263963392229915</v>
+        <v>0.07250062976950034</v>
       </c>
       <c r="C12">
-        <v>13007.03790389929</v>
+        <v>13018.70892257962</v>
       </c>
       <c r="D12">
-        <v>10897.14790389929</v>
+        <v>10908.81892257962</v>
       </c>
       <c r="E12">
         <v>-2738.99</v>
@@ -2271,37 +2271,37 @@
         <v>1052.8</v>
       </c>
       <c r="M12">
-        <v>81.12086646627822</v>
+        <v>79.11395246627822</v>
       </c>
       <c r="N12">
-        <v>971.6791335337217</v>
+        <v>973.6860475337218</v>
       </c>
       <c r="O12">
-        <v>97.16791335337217</v>
+        <v>97.36860475337218</v>
       </c>
       <c r="P12">
-        <v>874.5112201803495</v>
+        <v>876.3174427803496</v>
       </c>
       <c r="Q12">
-        <v>2099.81122018035</v>
+        <v>2101.617442780349</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07505180651531324</v>
+        <v>0.0750373574566479</v>
       </c>
       <c r="T12">
         <v>0.5860236514938553</v>
       </c>
       <c r="U12">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.97816512398381</v>
+        <v>13.30738722033574</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07266434217677331</v>
+        <v>0.0725127511594824</v>
       </c>
       <c r="C13">
-        <v>12861.40599464632</v>
+        <v>12874.23642185024</v>
       </c>
       <c r="D13">
-        <v>10894.86699464633</v>
+        <v>10907.69742185025</v>
       </c>
       <c r="E13">
         <v>-2595.639</v>
@@ -2353,37 +2353,37 @@
         <v>1052.8</v>
       </c>
       <c r="M13">
-        <v>89.23295311290603</v>
+        <v>87.02534771290604</v>
       </c>
       <c r="N13">
-        <v>963.567046887094</v>
+        <v>965.7746522870939</v>
       </c>
       <c r="O13">
-        <v>96.3567046887094</v>
+        <v>96.5774652287094</v>
       </c>
       <c r="P13">
-        <v>867.2103421983845</v>
+        <v>869.1971870583845</v>
       </c>
       <c r="Q13">
-        <v>2092.510342198384</v>
+        <v>2094.497187058384</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07535059922742063</v>
+        <v>0.07533600257877913</v>
       </c>
       <c r="T13">
         <v>0.5920095927757127</v>
       </c>
       <c r="U13">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V13">
         <v>0.1</v>
       </c>
       <c r="W13">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.79833193089438</v>
+        <v>12.09762474575976</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07268905043124747</v>
+        <v>0.07252487254946444</v>
       </c>
       <c r="C14">
-        <v>12715.77504003917</v>
+        <v>12729.76415169296</v>
       </c>
       <c r="D14">
-        <v>10892.58704003917</v>
+        <v>10906.57615169296</v>
       </c>
       <c r="E14">
         <v>-2452.288</v>
@@ -2435,37 +2435,37 @@
         <v>1052.8</v>
       </c>
       <c r="M14">
-        <v>97.34503975953385</v>
+        <v>94.93674295953385</v>
       </c>
       <c r="N14">
-        <v>955.4549602404661</v>
+        <v>957.8632570404661</v>
       </c>
       <c r="O14">
-        <v>95.54549602404661</v>
+        <v>95.78632570404662</v>
       </c>
       <c r="P14">
-        <v>859.9094642164195</v>
+        <v>862.0769313364195</v>
       </c>
       <c r="Q14">
-        <v>2085.209464216419</v>
+        <v>2087.37693133642</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.075656182682985</v>
+        <v>0.07564143509004972</v>
       </c>
       <c r="T14">
         <v>0.5981315781776126</v>
       </c>
       <c r="U14">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V14">
         <v>0.1</v>
       </c>
       <c r="W14">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.81513760331985</v>
+        <v>11.08948935027979</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07271375868572164</v>
+        <v>0.07253699393944649</v>
       </c>
       <c r="C15">
-        <v>12570.14503947861</v>
+        <v>12585.29211203666</v>
       </c>
       <c r="D15">
-        <v>10890.30803947861</v>
+        <v>10905.45511203666</v>
       </c>
       <c r="E15">
         <v>-2308.937</v>
@@ -2517,37 +2517,37 @@
         <v>1052.8</v>
       </c>
       <c r="M15">
-        <v>105.4571264061617</v>
+        <v>102.8481382061617</v>
       </c>
       <c r="N15">
-        <v>947.3428735938382</v>
+        <v>949.9518617938382</v>
       </c>
       <c r="O15">
-        <v>94.73428735938383</v>
+        <v>94.99518617938384</v>
       </c>
       <c r="P15">
-        <v>852.6085862344544</v>
+        <v>854.9566756144544</v>
       </c>
       <c r="Q15">
-        <v>2077.908586234455</v>
+        <v>2080.256675614454</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07596879104557384</v>
+        <v>0.07595388903836101</v>
       </c>
       <c r="T15">
         <v>0.6043942988761077</v>
       </c>
       <c r="U15">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V15">
         <v>0.1</v>
       </c>
       <c r="W15">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.983203941526011</v>
+        <v>10.23645170795057</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07273846694019581</v>
+        <v>0.07254911532942852</v>
       </c>
       <c r="C16">
-        <v>12424.51599236594</v>
+        <v>12440.82030281029</v>
       </c>
       <c r="D16">
-        <v>10888.02999236595</v>
+        <v>10904.33430281029</v>
       </c>
       <c r="E16">
         <v>-2165.586</v>
@@ -2599,37 +2599,37 @@
         <v>1052.8</v>
       </c>
       <c r="M16">
-        <v>113.5692130527895</v>
+        <v>110.7595334527895</v>
       </c>
       <c r="N16">
-        <v>939.2307869472104</v>
+        <v>942.0404665472105</v>
       </c>
       <c r="O16">
-        <v>93.92307869472104</v>
+        <v>94.20404665472105</v>
       </c>
       <c r="P16">
-        <v>845.3077082524893</v>
+        <v>847.8364198924894</v>
       </c>
       <c r="Q16">
-        <v>2070.607708252489</v>
+        <v>2073.136419892489</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07628866937008336</v>
+        <v>0.07627360935756325</v>
       </c>
       <c r="T16">
         <v>0.6108026642420098</v>
       </c>
       <c r="U16">
-        <v>0.05658897842796926</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V16">
         <v>0.1</v>
       </c>
       <c r="W16">
-        <v>0.05093008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.270117945702722</v>
+        <v>9.5052765859541</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07291167519466998</v>
+        <v>0.07256123671941056</v>
       </c>
       <c r="C17">
-        <v>12265.22228820013</v>
+        <v>12296.3487239428</v>
       </c>
       <c r="D17">
-        <v>10872.08728820013</v>
+        <v>10903.2137239428</v>
       </c>
       <c r="E17">
         <v>-2022.235</v>
@@ -2681,45 +2681,45 @@
         <v>1052.8</v>
       </c>
       <c r="M17">
-        <v>124.0465911994173</v>
+        <v>118.6709286994173</v>
       </c>
       <c r="N17">
-        <v>928.7534088005826</v>
+        <v>934.1290713005826</v>
       </c>
       <c r="O17">
-        <v>92.87534088005827</v>
+        <v>93.41290713005827</v>
       </c>
       <c r="P17">
-        <v>835.8780679205244</v>
+        <v>840.7161641705243</v>
       </c>
       <c r="Q17">
-        <v>2061.178067920524</v>
+        <v>2066.016164170524</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07661607424340486</v>
+        <v>0.07660085250780554</v>
       </c>
       <c r="T17">
         <v>0.6173618146753449</v>
       </c>
       <c r="U17">
-        <v>0.05768897842796925</v>
+        <v>0.05518897842796926</v>
       </c>
       <c r="V17">
         <v>0.1</v>
       </c>
       <c r="W17">
-        <v>0.05192008058517233</v>
+        <v>0.04967008058517233</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>8.487133663411345</v>
+        <v>8.871591480223827</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07294628344914414</v>
+        <v>0.0727893581093926</v>
       </c>
       <c r="C18">
-        <v>12118.69141590724</v>
+        <v>12131.95159311831</v>
       </c>
       <c r="D18">
-        <v>10868.90741590724</v>
+        <v>10882.16759311831</v>
       </c>
       <c r="E18">
         <v>-1878.884</v>
@@ -2763,37 +2763,37 @@
         <v>1052.8</v>
       </c>
       <c r="M18">
-        <v>132.3163639460451</v>
+        <v>130.0227479460451</v>
       </c>
       <c r="N18">
-        <v>920.4836360539548</v>
+        <v>922.7772520539548</v>
       </c>
       <c r="O18">
-        <v>92.04836360539548</v>
+        <v>92.27772520539548</v>
       </c>
       <c r="P18">
-        <v>828.4352724485593</v>
+        <v>830.4995268485593</v>
       </c>
       <c r="Q18">
-        <v>2053.735272448559</v>
+        <v>2055.799526848559</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07695127447085306</v>
+        <v>0.07693588716162504</v>
       </c>
       <c r="T18">
         <v>0.6240771353570926</v>
       </c>
       <c r="U18">
-        <v>0.05768897842796925</v>
+        <v>0.05668897842796925</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.05192008058517233</v>
+        <v>0.05102008058517233</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.956687809448135</v>
+        <v>8.09704468357241</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07298089170361832</v>
+        <v>0.07281497949937464</v>
       </c>
       <c r="C19">
-        <v>11972.16240317103</v>
+        <v>11986.24187694724</v>
       </c>
       <c r="D19">
-        <v>10865.72940317103</v>
+        <v>10879.80887694724</v>
       </c>
       <c r="E19">
         <v>-1735.533</v>
@@ -2845,37 +2845,37 @@
         <v>1052.8</v>
       </c>
       <c r="M19">
-        <v>140.5861366926729</v>
+        <v>138.149169692673</v>
       </c>
       <c r="N19">
-        <v>912.2138633073271</v>
+        <v>914.6508303073269</v>
       </c>
       <c r="O19">
-        <v>91.22138633073271</v>
+        <v>91.4650830307327</v>
       </c>
       <c r="P19">
-        <v>820.9924769765944</v>
+        <v>823.1857472765943</v>
       </c>
       <c r="Q19">
-        <v>2046.292476976594</v>
+        <v>2048.485747276594</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07729455181221569</v>
+        <v>0.07727899493963294</v>
       </c>
       <c r="T19">
         <v>0.6309542709950271</v>
       </c>
       <c r="U19">
-        <v>0.05768897842796925</v>
+        <v>0.05668897842796925</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.05192008058517233</v>
+        <v>0.05102008058517233</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.488647350068834</v>
+        <v>7.620747937479913</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07301549995809248</v>
+        <v>0.07284060088935669</v>
       </c>
       <c r="C20">
-        <v>11825.63524836079</v>
+        <v>11840.5331830608</v>
       </c>
       <c r="D20">
-        <v>10862.55324836079</v>
+        <v>10877.4511830608</v>
       </c>
       <c r="E20">
         <v>-1592.182</v>
@@ -2927,37 +2927,37 @@
         <v>1052.8</v>
       </c>
       <c r="M20">
-        <v>148.8559094393007</v>
+        <v>146.2755914393007</v>
       </c>
       <c r="N20">
-        <v>903.9440905606992</v>
+        <v>906.5244085606992</v>
       </c>
       <c r="O20">
-        <v>90.39440905606993</v>
+        <v>90.65244085606992</v>
       </c>
       <c r="P20">
-        <v>813.5496815046293</v>
+        <v>815.8719677046292</v>
       </c>
       <c r="Q20">
-        <v>2038.849681504629</v>
+        <v>2041.171967704629</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07764620177166032</v>
+        <v>0.0776304712000313</v>
       </c>
       <c r="T20">
         <v>0.6379991416485209</v>
       </c>
       <c r="U20">
-        <v>0.05768897842796925</v>
+        <v>0.05668897842796925</v>
       </c>
       <c r="V20">
         <v>0.1</v>
       </c>
       <c r="W20">
-        <v>0.05192008058517233</v>
+        <v>0.05102008058517233</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.072611386176121</v>
+        <v>7.197373052064364</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07342630821256664</v>
+        <v>0.07286622227933874</v>
       </c>
       <c r="C21">
-        <v>11644.72387831152</v>
+        <v>11694.82551079454</v>
       </c>
       <c r="D21">
-        <v>10824.99287831152</v>
+        <v>10875.09451079454</v>
       </c>
       <c r="E21">
         <v>-1448.831</v>
@@ -3009,45 +3009,45 @@
         <v>1052.8</v>
       </c>
       <c r="M21">
-        <v>163.1177539859286</v>
+        <v>154.4020131859286</v>
       </c>
       <c r="N21">
-        <v>889.6822460140713</v>
+        <v>898.3979868140714</v>
       </c>
       <c r="O21">
-        <v>88.96822460140714</v>
+        <v>89.83979868140715</v>
       </c>
       <c r="P21">
-        <v>800.7140214126641</v>
+        <v>808.5581881326642</v>
       </c>
       <c r="Q21">
-        <v>2026.014021412664</v>
+        <v>2033.858188132664</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07800653444615296</v>
+        <v>0.07799062588661233</v>
       </c>
       <c r="T21">
         <v>0.6452179597255577</v>
       </c>
       <c r="U21">
-        <v>0.05988897842796925</v>
+        <v>0.05668897842796925</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.05390008058517233</v>
+        <v>0.05102008058517233</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.454233057247833</v>
+        <v>6.818563944060974</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07348071646704081</v>
+        <v>0.07319784366932076</v>
       </c>
       <c r="C22">
-        <v>11496.41777911825</v>
+        <v>11521.06364504187</v>
       </c>
       <c r="D22">
-        <v>10820.03777911825</v>
+        <v>10844.68364504187</v>
       </c>
       <c r="E22">
         <v>-1305.48</v>
@@ -3091,37 +3091,37 @@
         <v>1052.8</v>
       </c>
       <c r="M22">
-        <v>171.7028989325564</v>
+        <v>167.4023689325564</v>
       </c>
       <c r="N22">
-        <v>881.0971010674435</v>
+        <v>885.3976310674435</v>
       </c>
       <c r="O22">
-        <v>88.10971010674436</v>
+        <v>88.53976310674436</v>
       </c>
       <c r="P22">
-        <v>792.9873909606991</v>
+        <v>796.8578679606992</v>
       </c>
       <c r="Q22">
-        <v>2018.287390960699</v>
+        <v>2022.157867960699</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07837587543750793</v>
+        <v>0.07835978444035788</v>
       </c>
       <c r="T22">
         <v>0.6526172482545206</v>
       </c>
       <c r="U22">
-        <v>0.05988897842796925</v>
+        <v>0.05838897842796925</v>
       </c>
       <c r="V22">
         <v>0.1</v>
       </c>
       <c r="W22">
-        <v>0.05390008058517233</v>
+        <v>0.05255008058517233</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.131521404385442</v>
+        <v>6.289038839254151</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07353512472151498</v>
+        <v>0.07323876505930282</v>
       </c>
       <c r="C23">
-        <v>11348.11621420493</v>
+        <v>11373.97179207683</v>
       </c>
       <c r="D23">
-        <v>10815.08721420493</v>
+        <v>10840.94279207683</v>
       </c>
       <c r="E23">
         <v>-1162.129</v>
@@ -3173,37 +3173,37 @@
         <v>1052.8</v>
       </c>
       <c r="M23">
-        <v>180.2880438791842</v>
+        <v>175.7724873791842</v>
       </c>
       <c r="N23">
-        <v>872.5119561208157</v>
+        <v>877.0275126208157</v>
       </c>
       <c r="O23">
-        <v>87.25119561208157</v>
+        <v>87.70275126208158</v>
       </c>
       <c r="P23">
-        <v>785.2607605087342</v>
+        <v>789.3247613587341</v>
       </c>
       <c r="Q23">
-        <v>2010.560760508734</v>
+        <v>2014.624761358734</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07875456683370732</v>
+        <v>0.07873828878027421</v>
       </c>
       <c r="T23">
         <v>0.6602038605437103</v>
       </c>
       <c r="U23">
-        <v>0.05988897842796925</v>
+        <v>0.05838897842796925</v>
       </c>
       <c r="V23">
         <v>0.1</v>
       </c>
       <c r="W23">
-        <v>0.05390008058517233</v>
+        <v>0.05255008058517233</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.839544194652802</v>
+        <v>5.989560799289669</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07388653297598914</v>
+        <v>0.07327968644928487</v>
       </c>
       <c r="C24">
-        <v>11172.89964503855</v>
+        <v>11226.88251902207</v>
       </c>
       <c r="D24">
-        <v>10783.22164503855</v>
+        <v>10837.20451902207</v>
       </c>
       <c r="E24">
         <v>-1018.778</v>
@@ -3255,45 +3255,45 @@
         <v>1052.8</v>
       </c>
       <c r="M24">
-        <v>193.6037718258121</v>
+        <v>184.1426058258121</v>
       </c>
       <c r="N24">
-        <v>859.1962281741879</v>
+        <v>868.6573941741879</v>
       </c>
       <c r="O24">
-        <v>85.9196228174188</v>
+        <v>86.86573941741879</v>
       </c>
       <c r="P24">
-        <v>773.2766053567691</v>
+        <v>781.791654756769</v>
       </c>
       <c r="Q24">
-        <v>1998.576605356769</v>
+        <v>2007.091654756769</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.0791429682657067</v>
+        <v>0.07912649835967558</v>
       </c>
       <c r="T24">
         <v>0.6679850013531357</v>
       </c>
       <c r="U24">
-        <v>0.06138897842796925</v>
+        <v>0.05838897842796925</v>
       </c>
       <c r="V24">
         <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.05525008058517233</v>
+        <v>0.05255008058517233</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>5.4379105844447</v>
+        <v>5.717308035685592</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07395444123046331</v>
+        <v>0.0734862078392669</v>
       </c>
       <c r="C25">
-        <v>11023.41238738844</v>
+        <v>11064.70453459964</v>
       </c>
       <c r="D25">
-        <v>10777.08538738844</v>
+        <v>10818.37753459964</v>
       </c>
       <c r="E25">
         <v>-875.4269999999997</v>
@@ -3337,37 +3337,37 @@
         <v>1052.8</v>
       </c>
       <c r="M25">
-        <v>202.4039432724399</v>
+        <v>195.1503826724399</v>
       </c>
       <c r="N25">
-        <v>850.3960567275601</v>
+        <v>857.64961732756</v>
       </c>
       <c r="O25">
-        <v>85.03960567275601</v>
+        <v>85.76496173275601</v>
       </c>
       <c r="P25">
-        <v>765.3564510548041</v>
+        <v>771.884655594804</v>
       </c>
       <c r="Q25">
-        <v>1990.656451054804</v>
+        <v>1997.184655594804</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07954145804658919</v>
+        <v>0.07952479130477567</v>
       </c>
       <c r="T25">
         <v>0.6759682497160526</v>
       </c>
       <c r="U25">
-        <v>0.06138897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V25">
         <v>0.1</v>
       </c>
       <c r="W25">
-        <v>0.05525008058517233</v>
+        <v>0.05327008058517233</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.201479689468843</v>
+        <v>5.394813915210844</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07402234948493747</v>
+        <v>0.07353432922924896</v>
       </c>
       <c r="C26">
-        <v>10873.93210951569</v>
+        <v>10916.97606654141</v>
       </c>
       <c r="D26">
-        <v>10770.95610951569</v>
+        <v>10814.00006654141</v>
       </c>
       <c r="E26">
         <v>-732.076</v>
@@ -3419,37 +3419,37 @@
         <v>1052.8</v>
       </c>
       <c r="M26">
-        <v>211.2041147190677</v>
+        <v>203.6351819190677</v>
       </c>
       <c r="N26">
-        <v>841.5958852809323</v>
+        <v>849.1648180809323</v>
       </c>
       <c r="O26">
-        <v>84.15958852809324</v>
+        <v>84.91648180809324</v>
       </c>
       <c r="P26">
-        <v>757.4362967528391</v>
+        <v>764.248336272839</v>
       </c>
       <c r="Q26">
-        <v>1982.736296752839</v>
+        <v>1989.548336272839</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07995043440065278</v>
+        <v>0.07993356564316789</v>
       </c>
       <c r="T26">
         <v>0.6841615835622042</v>
       </c>
       <c r="U26">
-        <v>0.06138897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V26">
         <v>0.1</v>
       </c>
       <c r="W26">
-        <v>0.05525008058517233</v>
+        <v>0.05327008058517233</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.984751369074308</v>
+        <v>5.17003000207706</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07409025773941164</v>
+        <v>0.07358245061923099</v>
       </c>
       <c r="C27">
-        <v>10724.45879951818</v>
+        <v>10769.25113958277</v>
       </c>
       <c r="D27">
-        <v>10764.83379951818</v>
+        <v>10809.62613958277</v>
       </c>
       <c r="E27">
         <v>-588.7249999999999</v>
@@ -3501,37 +3501,37 @@
         <v>1052.8</v>
       </c>
       <c r="M27">
-        <v>220.0042861656955</v>
+        <v>212.1199811656955</v>
       </c>
       <c r="N27">
-        <v>832.7957138343045</v>
+        <v>840.6800188343044</v>
       </c>
       <c r="O27">
-        <v>83.27957138343045</v>
+        <v>84.06800188343044</v>
       </c>
       <c r="P27">
-        <v>749.516142450874</v>
+        <v>756.612016950874</v>
       </c>
       <c r="Q27">
-        <v>1974.816142450874</v>
+        <v>1981.912016950874</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08037031679082474</v>
+        <v>0.08035324063058388</v>
       </c>
       <c r="T27">
         <v>0.6925734063109199</v>
       </c>
       <c r="U27">
-        <v>0.06138897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V27">
         <v>0.1</v>
       </c>
       <c r="W27">
-        <v>0.05525008058517233</v>
+        <v>0.05327008058517233</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.785361314311336</v>
+        <v>4.963228801993977</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07415816599388581</v>
+        <v>0.07363057200921304</v>
       </c>
       <c r="C28">
-        <v>10574.99244552084</v>
+        <v>10621.52974942864</v>
       </c>
       <c r="D28">
-        <v>10758.71844552084</v>
+        <v>10805.25574942864</v>
       </c>
       <c r="E28">
         <v>-445.3739999999998</v>
@@ -3583,37 +3583,37 @@
         <v>1052.8</v>
       </c>
       <c r="M28">
-        <v>228.8044576123233</v>
+        <v>220.6047804123234</v>
       </c>
       <c r="N28">
-        <v>823.9955423876766</v>
+        <v>832.1952195876765</v>
       </c>
       <c r="O28">
-        <v>82.39955423876766</v>
+        <v>83.21952195876766</v>
       </c>
       <c r="P28">
-        <v>741.5959881489089</v>
+        <v>748.9756976289088</v>
       </c>
       <c r="Q28">
-        <v>1966.895988148909</v>
+        <v>1974.275697628909</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08080154735370405</v>
+        <v>0.08078425818522733</v>
       </c>
       <c r="T28">
         <v>0.7012125756204116</v>
       </c>
       <c r="U28">
-        <v>0.06138897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V28">
         <v>0.1</v>
       </c>
       <c r="W28">
-        <v>0.05525008058517233</v>
+        <v>0.05327008058517233</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.601308956068592</v>
+        <v>4.77233538653267</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07422607424835997</v>
+        <v>0.07367869339919508</v>
       </c>
       <c r="C29">
-        <v>10425.53303567559</v>
+        <v>10473.81189179093</v>
       </c>
       <c r="D29">
-        <v>10752.61003567559</v>
+        <v>10800.88889179093</v>
       </c>
       <c r="E29">
         <v>-302.0229999999997</v>
@@ -3665,37 +3665,37 @@
         <v>1052.8</v>
       </c>
       <c r="M29">
-        <v>237.6046290589512</v>
+        <v>229.0895796589512</v>
       </c>
       <c r="N29">
-        <v>815.1953709410488</v>
+        <v>823.7104203410488</v>
       </c>
       <c r="O29">
-        <v>81.51953709410489</v>
+        <v>82.37104203410489</v>
       </c>
       <c r="P29">
-        <v>733.675833846944</v>
+        <v>741.3393783069439</v>
       </c>
       <c r="Q29">
-        <v>1958.975833846944</v>
+        <v>1966.639378306944</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08124459245255267</v>
+        <v>0.08122708443999802</v>
       </c>
       <c r="T29">
         <v>0.7100884345000265</v>
       </c>
       <c r="U29">
-        <v>0.06138897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V29">
         <v>0.1</v>
       </c>
       <c r="W29">
-        <v>0.05525008058517233</v>
+        <v>0.05327008058517233</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.430890105843829</v>
+        <v>4.595582224068497</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07429398250283414</v>
+        <v>0.07372681478917713</v>
       </c>
       <c r="C30">
-        <v>10276.08055816122</v>
+        <v>10326.09756238844</v>
       </c>
       <c r="D30">
-        <v>10746.50855816122</v>
+        <v>10796.52556238844</v>
       </c>
       <c r="E30">
         <v>-158.6719999999996</v>
@@ -3747,37 +3747,37 @@
         <v>1052.8</v>
       </c>
       <c r="M30">
-        <v>246.404800505579</v>
+        <v>237.574378905579</v>
       </c>
       <c r="N30">
-        <v>806.3951994944209</v>
+        <v>815.2256210944209</v>
       </c>
       <c r="O30">
-        <v>80.6395199494421</v>
+        <v>81.52256210944211</v>
       </c>
       <c r="P30">
-        <v>725.7556795449789</v>
+        <v>733.7030589849788</v>
       </c>
       <c r="Q30">
-        <v>1951.055679544979</v>
+        <v>1959.003058984979</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08169994435970263</v>
+        <v>0.08168221142406788</v>
       </c>
       <c r="T30">
         <v>0.7192108450151861</v>
       </c>
       <c r="U30">
-        <v>0.06138897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V30">
         <v>0.1</v>
       </c>
       <c r="W30">
-        <v>0.05525008058517233</v>
+        <v>0.05327008058517233</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.272644030635121</v>
+        <v>4.431454287494622</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07472729075730829</v>
+        <v>0.07377493617915916</v>
       </c>
       <c r="C31">
-        <v>10093.95978299364</v>
+        <v>10178.38675694691</v>
       </c>
       <c r="D31">
-        <v>10707.73878299364</v>
+        <v>10792.16575694691</v>
       </c>
       <c r="E31">
         <v>-15.32099999999991</v>
@@ -3829,45 +3829,45 @@
         <v>1052.8</v>
       </c>
       <c r="M31">
-        <v>261.0250225522068</v>
+        <v>246.0591781522068</v>
       </c>
       <c r="N31">
-        <v>791.7749774477932</v>
+        <v>806.7408218477931</v>
       </c>
       <c r="O31">
-        <v>79.17749774477932</v>
+        <v>80.67408218477931</v>
       </c>
       <c r="P31">
-        <v>712.5974797030138</v>
+        <v>726.0667396630138</v>
       </c>
       <c r="Q31">
-        <v>1937.897479703014</v>
+        <v>1951.366739663014</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08216812308113848</v>
+        <v>0.08215015888656224</v>
       </c>
       <c r="T31">
         <v>0.7285902248406317</v>
       </c>
       <c r="U31">
-        <v>0.06278897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V31">
         <v>0.1</v>
       </c>
       <c r="W31">
-        <v>0.05651008058517233</v>
+        <v>0.05327008058517233</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.033329792316875</v>
+        <v>4.278645518960325</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07480779901178246</v>
+        <v>0.0740930575691412</v>
       </c>
       <c r="C32">
-        <v>9943.436191452685</v>
+        <v>10006.30225356264</v>
       </c>
       <c r="D32">
-        <v>10700.56619145268</v>
+        <v>10763.43225356264</v>
       </c>
       <c r="E32">
         <v>128.0299999999997</v>
@@ -3911,37 +3911,37 @@
         <v>1052.8</v>
       </c>
       <c r="M32">
-        <v>270.0258853988346</v>
+        <v>258.8445073988346</v>
       </c>
       <c r="N32">
-        <v>782.7741146011654</v>
+        <v>793.9554926011654</v>
       </c>
       <c r="O32">
-        <v>78.27741146011654</v>
+        <v>79.39554926011654</v>
       </c>
       <c r="P32">
-        <v>704.4967031410488</v>
+        <v>714.5599433410488</v>
       </c>
       <c r="Q32">
-        <v>1929.796703141049</v>
+        <v>1939.859943341049</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08264967833747253</v>
+        <v>0.08263147627655644</v>
       </c>
       <c r="T32">
         <v>0.7382375869468046</v>
       </c>
       <c r="U32">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V32">
         <v>0.1</v>
       </c>
       <c r="W32">
-        <v>0.05651008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.898885465906313</v>
+        <v>4.067306703084943</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07488830726625663</v>
+        <v>0.07415017895912325</v>
       </c>
       <c r="C33">
-        <v>9792.922202617268</v>
+        <v>9857.808104865635</v>
       </c>
       <c r="D33">
-        <v>10693.40320261727</v>
+        <v>10758.28910486563</v>
       </c>
       <c r="E33">
         <v>271.3810000000003</v>
@@ -3993,37 +3993,37 @@
         <v>1052.8</v>
       </c>
       <c r="M33">
-        <v>279.0267482454624</v>
+        <v>267.4726576454624</v>
       </c>
       <c r="N33">
-        <v>773.7732517545376</v>
+        <v>785.3273423545374</v>
       </c>
       <c r="O33">
-        <v>77.37732517545376</v>
+        <v>78.53273423545374</v>
       </c>
       <c r="P33">
-        <v>696.3959265790838</v>
+        <v>706.7946081190837</v>
       </c>
       <c r="Q33">
-        <v>1921.695926579084</v>
+        <v>1932.094608119084</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08314519171717857</v>
+        <v>0.08312674489524613</v>
       </c>
       <c r="T33">
         <v>0.7481645827372144</v>
       </c>
       <c r="U33">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V33">
         <v>0.1</v>
       </c>
       <c r="W33">
-        <v>0.05651008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.773114967006109</v>
+        <v>3.936103261049944</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.0749688155207308</v>
+        <v>0.07420730034910529</v>
       </c>
       <c r="C34">
-        <v>9642.417797216063</v>
+        <v>9709.318868977896</v>
       </c>
       <c r="D34">
-        <v>10686.24979721606</v>
+        <v>10753.1508689779</v>
       </c>
       <c r="E34">
         <v>414.732</v>
@@ -4075,37 +4075,37 @@
         <v>1052.8</v>
       </c>
       <c r="M34">
-        <v>288.0276110920902</v>
+        <v>276.1008078920902</v>
       </c>
       <c r="N34">
-        <v>764.7723889079098</v>
+        <v>776.6991921079098</v>
       </c>
       <c r="O34">
-        <v>76.47723889079099</v>
+        <v>77.66991921079098</v>
       </c>
       <c r="P34">
-        <v>688.2951500171188</v>
+        <v>699.0292728971187</v>
       </c>
       <c r="Q34">
-        <v>1913.595150017119</v>
+        <v>1924.329272897119</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08365527901981715</v>
+        <v>0.08363658023801493</v>
       </c>
       <c r="T34">
         <v>0.758383548992048</v>
       </c>
       <c r="U34">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V34">
         <v>0.1</v>
       </c>
       <c r="W34">
-        <v>0.05651008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.655205124287169</v>
+        <v>3.813100034142133</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07504932377520496</v>
+        <v>0.07426442173908734</v>
       </c>
       <c r="C35">
-        <v>9491.922956029264</v>
+        <v>9560.834538863608</v>
       </c>
       <c r="D35">
-        <v>10679.10595602927</v>
+        <v>10748.01753886361</v>
       </c>
       <c r="E35">
         <v>558.0830000000005</v>
@@ -4157,37 +4157,37 @@
         <v>1052.8</v>
       </c>
       <c r="M35">
-        <v>297.0284739387181</v>
+        <v>284.7289581387181</v>
       </c>
       <c r="N35">
-        <v>755.7715260612819</v>
+        <v>768.0710418612819</v>
       </c>
       <c r="O35">
-        <v>75.57715260612819</v>
+        <v>76.80710418612819</v>
       </c>
       <c r="P35">
-        <v>680.1943734551537</v>
+        <v>691.2639376751537</v>
       </c>
       <c r="Q35">
-        <v>1905.494373455154</v>
+        <v>1916.563937675154</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08418059280910165</v>
+        <v>0.08416163454623951</v>
       </c>
       <c r="T35">
         <v>0.7689075590156825</v>
       </c>
       <c r="U35">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V35">
         <v>0.1</v>
       </c>
       <c r="W35">
-        <v>0.05651008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.544441332642102</v>
+        <v>3.697551548259038</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07512983202967913</v>
+        <v>0.07432154312906938</v>
       </c>
       <c r="C36">
-        <v>9341.43765988843</v>
+        <v>9412.355107500382</v>
       </c>
       <c r="D36">
-        <v>10671.97165988843</v>
+        <v>10742.88910750038</v>
       </c>
       <c r="E36">
         <v>701.4340000000002</v>
@@ -4239,37 +4239,37 @@
         <v>1052.8</v>
       </c>
       <c r="M36">
-        <v>306.0293367853459</v>
+        <v>293.3571083853459</v>
       </c>
       <c r="N36">
-        <v>746.7706632146541</v>
+        <v>759.4428916146541</v>
       </c>
       <c r="O36">
-        <v>74.6770663214654</v>
+        <v>75.94428916146541</v>
       </c>
       <c r="P36">
-        <v>672.0935968931886</v>
+        <v>683.4986024531886</v>
       </c>
       <c r="Q36">
-        <v>1897.393596893189</v>
+        <v>1908.798602453189</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08472182519806143</v>
+        <v>0.08470259959107695</v>
       </c>
       <c r="T36">
         <v>0.7797504784339728</v>
       </c>
       <c r="U36">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V36">
         <v>0.1</v>
       </c>
       <c r="W36">
-        <v>0.05651008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.440193058152629</v>
+        <v>3.588800032133773</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.0752103402841533</v>
+        <v>0.07437866451905142</v>
       </c>
       <c r="C37">
-        <v>9190.961889676306</v>
+        <v>9263.88056787922</v>
       </c>
       <c r="D37">
-        <v>10664.84688967631</v>
+        <v>10737.76556787922</v>
       </c>
       <c r="E37">
         <v>844.7850000000008</v>
@@ -4321,37 +4321,37 @@
         <v>1052.8</v>
       </c>
       <c r="M37">
-        <v>315.0301996319737</v>
+        <v>301.9852586319737</v>
       </c>
       <c r="N37">
-        <v>737.7698003680262</v>
+        <v>750.8147413680263</v>
       </c>
       <c r="O37">
-        <v>73.77698003680261</v>
+        <v>75.08147413680263</v>
       </c>
       <c r="P37">
-        <v>663.9928203312236</v>
+        <v>675.7332672312236</v>
       </c>
       <c r="Q37">
-        <v>1889.292820331224</v>
+        <v>1901.033267231224</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08527971089129691</v>
+        <v>0.08526020971421711</v>
       </c>
       <c r="T37">
         <v>0.7909270261420565</v>
       </c>
       <c r="U37">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V37">
         <v>0.1</v>
       </c>
       <c r="W37">
-        <v>0.05651008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.341901827919696</v>
+        <v>3.486262888358522</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07529084853862747</v>
+        <v>0.07443578590903346</v>
       </c>
       <c r="C38">
-        <v>9040.495626326665</v>
+        <v>9115.410913004496</v>
       </c>
       <c r="D38">
-        <v>10657.73162632666</v>
+        <v>10732.6469130045</v>
       </c>
       <c r="E38">
         <v>988.1359999999995</v>
@@ -4403,37 +4403,37 @@
         <v>1052.8</v>
       </c>
       <c r="M38">
-        <v>324.0310624786015</v>
+        <v>310.6134088786015</v>
       </c>
       <c r="N38">
-        <v>728.7689375213985</v>
+        <v>742.1865911213985</v>
       </c>
       <c r="O38">
-        <v>72.87689375213985</v>
+        <v>74.21865911213985</v>
       </c>
       <c r="P38">
-        <v>655.8920437692586</v>
+        <v>667.9679320092587</v>
       </c>
       <c r="Q38">
-        <v>1881.192043769259</v>
+        <v>1893.267932009259</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08585503051244597</v>
+        <v>0.08583524515370536</v>
       </c>
       <c r="T38">
         <v>0.8024528409660178</v>
       </c>
       <c r="U38">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V38">
         <v>0.1</v>
       </c>
       <c r="W38">
-        <v>0.05651008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.249071221588595</v>
+        <v>3.389422252570786</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07537135679310163</v>
+        <v>0.0744929072990155</v>
       </c>
       <c r="C39">
-        <v>8890.038850824112</v>
+        <v>8966.946135893919</v>
       </c>
       <c r="D39">
-        <v>10650.62585082411</v>
+        <v>10727.53313589392</v>
       </c>
       <c r="E39">
         <v>1131.487</v>
@@ -4485,37 +4485,37 @@
         <v>1052.8</v>
       </c>
       <c r="M39">
-        <v>333.0319253252293</v>
+        <v>319.2415591252293</v>
       </c>
       <c r="N39">
-        <v>719.7680746747706</v>
+        <v>733.5584408747707</v>
       </c>
       <c r="O39">
-        <v>71.97680746747706</v>
+        <v>73.35584408747707</v>
       </c>
       <c r="P39">
-        <v>647.7912672072935</v>
+        <v>660.2025967872936</v>
       </c>
       <c r="Q39">
-        <v>1873.091267207293</v>
+        <v>1885.502596787293</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08644861424855216</v>
+        <v>0.08642853568651071</v>
       </c>
       <c r="T39">
         <v>0.8143445546732793</v>
       </c>
       <c r="U39">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V39">
         <v>0.1</v>
       </c>
       <c r="W39">
-        <v>0.05651008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.161258485869983</v>
+        <v>3.297816245744548</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.0754518650475758</v>
+        <v>0.07455002868899756</v>
       </c>
       <c r="C40">
-        <v>8739.59154420394</v>
+        <v>8818.486229578484</v>
       </c>
       <c r="D40">
-        <v>10643.52954420394</v>
+        <v>10722.42422957849</v>
       </c>
       <c r="E40">
         <v>1274.838000000001</v>
@@ -4567,37 +4567,37 @@
         <v>1052.8</v>
       </c>
       <c r="M40">
-        <v>342.0327881718572</v>
+        <v>327.8697093718572</v>
       </c>
       <c r="N40">
-        <v>710.7672118281428</v>
+        <v>724.9302906281428</v>
       </c>
       <c r="O40">
-        <v>71.07672118281428</v>
+        <v>72.49302906281427</v>
       </c>
       <c r="P40">
-        <v>639.6904906453285</v>
+        <v>652.4372615653285</v>
       </c>
       <c r="Q40">
-        <v>1864.990490645328</v>
+        <v>1877.737261565328</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08706134584711341</v>
+        <v>0.08704096462360011</v>
       </c>
       <c r="T40">
         <v>0.8266198720485173</v>
       </c>
       <c r="U40">
-        <v>0.06278897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V40">
         <v>0.1</v>
       </c>
       <c r="W40">
-        <v>0.05651008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.078067473083931</v>
+        <v>3.211031607698638</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07644497330204997</v>
+        <v>0.07460715007897961</v>
       </c>
       <c r="C41">
-        <v>8509.475605820928</v>
+        <v>8670.031187102477</v>
       </c>
       <c r="D41">
-        <v>10556.76460582093</v>
+        <v>10717.32018710248</v>
       </c>
       <c r="E41">
         <v>1418.189</v>
@@ -4649,45 +4649,45 @@
         <v>1052.8</v>
       </c>
       <c r="M41">
-        <v>365.569442418485</v>
+        <v>336.497859618485</v>
       </c>
       <c r="N41">
-        <v>687.2305575815149</v>
+        <v>716.302140381515</v>
       </c>
       <c r="O41">
-        <v>68.72305575815149</v>
+        <v>71.63021403815149</v>
       </c>
       <c r="P41">
-        <v>618.5075018233633</v>
+        <v>644.6719263433635</v>
       </c>
       <c r="Q41">
-        <v>1843.807501823363</v>
+        <v>1869.971926343364</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.0876941670062832</v>
+        <v>0.08767347319797114</v>
       </c>
       <c r="T41">
         <v>0.839297658845894</v>
       </c>
       <c r="U41">
-        <v>0.06538897842796926</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V41">
         <v>0.1</v>
       </c>
       <c r="W41">
-        <v>0.05885008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.879890597624975</v>
+        <v>3.128697463911494</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07654888155652412</v>
+        <v>0.07466427146896165</v>
       </c>
       <c r="C42">
-        <v>8357.128125706344</v>
+        <v>8521.581001523404</v>
       </c>
       <c r="D42">
-        <v>10547.76812570635</v>
+        <v>10712.2210015234</v>
       </c>
       <c r="E42">
         <v>1561.540000000001</v>
@@ -4731,45 +4731,45 @@
         <v>1052.8</v>
       </c>
       <c r="M42">
-        <v>374.9430178651129</v>
+        <v>345.1260098651128</v>
       </c>
       <c r="N42">
-        <v>677.8569821348871</v>
+        <v>707.6739901348872</v>
       </c>
       <c r="O42">
-        <v>67.78569821348871</v>
+        <v>70.76739901348871</v>
       </c>
       <c r="P42">
-        <v>610.0712839213984</v>
+        <v>636.9065911213985</v>
       </c>
       <c r="Q42">
-        <v>1835.371283921398</v>
+        <v>1862.206591121399</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08834808220409199</v>
+        <v>0.08832706539148785</v>
       </c>
       <c r="T42">
         <v>0.8523980385365167</v>
       </c>
       <c r="U42">
-        <v>0.06538897842796926</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V42">
         <v>0.1</v>
       </c>
       <c r="W42">
-        <v>0.05885008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.807893332684351</v>
+        <v>3.050480027313707</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.0766527898109983</v>
+        <v>0.07564389285894368</v>
       </c>
       <c r="C43">
-        <v>8204.795966145346</v>
+        <v>8291.528963679244</v>
       </c>
       <c r="D43">
-        <v>10538.78696614535</v>
+        <v>10625.51996367925</v>
       </c>
       <c r="E43">
         <v>1704.891000000001</v>
@@ -4813,37 +4813,37 @@
         <v>1052.8</v>
       </c>
       <c r="M43">
-        <v>384.3165933117407</v>
+        <v>368.4476376117407</v>
       </c>
       <c r="N43">
-        <v>668.4834066882593</v>
+        <v>684.3523623882593</v>
       </c>
       <c r="O43">
-        <v>66.84834066882593</v>
+        <v>68.43523623882594</v>
       </c>
       <c r="P43">
-        <v>601.6350660194333</v>
+        <v>615.9171261494333</v>
       </c>
       <c r="Q43">
-        <v>1826.935066019433</v>
+        <v>1841.217126149433</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08902416401877566</v>
+        <v>0.08900281325258141</v>
       </c>
       <c r="T43">
         <v>0.8659424988946182</v>
       </c>
       <c r="U43">
-        <v>0.06538897842796926</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V43">
         <v>0.1</v>
       </c>
       <c r="W43">
-        <v>0.05885008058517233</v>
+        <v>0.05642008058517232</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.739408129448147</v>
+        <v>2.857393812657335</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07675669806547246</v>
+        <v>0.07572351424892573</v>
       </c>
       <c r="C44">
-        <v>8052.479088036031</v>
+        <v>8141.192731279416</v>
       </c>
       <c r="D44">
-        <v>10529.82108803603</v>
+        <v>10618.53473127942</v>
       </c>
       <c r="E44">
         <v>1848.242</v>
@@ -4895,37 +4895,37 @@
         <v>1052.8</v>
       </c>
       <c r="M44">
-        <v>393.6901687583685</v>
+        <v>377.4341653583684</v>
       </c>
       <c r="N44">
-        <v>659.1098312416315</v>
+        <v>675.3658346416315</v>
       </c>
       <c r="O44">
-        <v>65.91098312416315</v>
+        <v>67.53658346416316</v>
       </c>
       <c r="P44">
-        <v>593.1988481174683</v>
+        <v>607.8292511774683</v>
       </c>
       <c r="Q44">
-        <v>1818.498848117468</v>
+        <v>1833.129251177468</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08972355899948289</v>
+        <v>0.08970186276405751</v>
       </c>
       <c r="T44">
         <v>0.8799540096098954</v>
       </c>
       <c r="U44">
-        <v>0.06538897842796926</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V44">
         <v>0.1</v>
       </c>
       <c r="W44">
-        <v>0.05885008058517233</v>
+        <v>0.05642008058517232</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.674184126366049</v>
+        <v>2.789360626641685</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07686060631994662</v>
+        <v>0.07580313563890777</v>
       </c>
       <c r="C45">
-        <v>7900.177452409444</v>
+        <v>7990.865677049883</v>
       </c>
       <c r="D45">
-        <v>10520.87045240944</v>
+        <v>10611.55867704988</v>
       </c>
       <c r="E45">
         <v>1991.593</v>
@@ -4977,37 +4977,37 @@
         <v>1052.8</v>
       </c>
       <c r="M45">
-        <v>403.0637442049963</v>
+        <v>386.4206931049962</v>
       </c>
       <c r="N45">
-        <v>649.7362557950037</v>
+        <v>666.3793068950038</v>
       </c>
       <c r="O45">
-        <v>64.97362557950036</v>
+        <v>66.63793068950038</v>
       </c>
       <c r="P45">
-        <v>584.7626302155033</v>
+        <v>599.7413762055033</v>
       </c>
       <c r="Q45">
-        <v>1810.062630215503</v>
+        <v>1825.041376205503</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09044749415495179</v>
+        <v>0.09042544032856784</v>
       </c>
       <c r="T45">
         <v>0.8944571522800948</v>
       </c>
       <c r="U45">
-        <v>0.06538897842796926</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V45">
         <v>0.1</v>
       </c>
       <c r="W45">
-        <v>0.05885008058517233</v>
+        <v>0.05642008058517232</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.611993797845908</v>
+        <v>2.72449177485932</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.0769645145744208</v>
+        <v>0.07588275702888982</v>
       </c>
       <c r="C46">
-        <v>7747.891020429014</v>
+        <v>7840.547782913184</v>
       </c>
       <c r="D46">
-        <v>10511.93502042901</v>
+        <v>10604.59178291318</v>
       </c>
       <c r="E46">
         <v>2134.944</v>
@@ -5059,37 +5059,37 @@
         <v>1052.8</v>
       </c>
       <c r="M46">
-        <v>412.4373196516241</v>
+        <v>395.4072208516241</v>
       </c>
       <c r="N46">
-        <v>640.3626803483758</v>
+        <v>657.3927791483759</v>
       </c>
       <c r="O46">
-        <v>64.03626803483758</v>
+        <v>65.73927791483759</v>
       </c>
       <c r="P46">
-        <v>576.3264123135382</v>
+        <v>591.6535012335383</v>
       </c>
       <c r="Q46">
-        <v>1801.626412313538</v>
+        <v>1816.953501233538</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09119728413740172</v>
+        <v>0.09117485994895355</v>
       </c>
       <c r="T46">
         <v>0.9094782643313728</v>
       </c>
       <c r="U46">
-        <v>0.06538897842796926</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V46">
         <v>0.1</v>
       </c>
       <c r="W46">
-        <v>0.05885008058517233</v>
+        <v>0.05642008058517232</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.552630302440319</v>
+        <v>2.662571507248881</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07816192282889495</v>
+        <v>0.07596237841887186</v>
       </c>
       <c r="C47">
-        <v>7502.655335210888</v>
+        <v>7690.239030839306</v>
       </c>
       <c r="D47">
-        <v>10410.05033521089</v>
+        <v>10597.63403083931</v>
       </c>
       <c r="E47">
         <v>2278.295</v>
@@ -5141,45 +5141,45 @@
         <v>1052.8</v>
       </c>
       <c r="M47">
-        <v>439.2280415982519</v>
+        <v>404.3937485982519</v>
       </c>
       <c r="N47">
-        <v>613.571958401748</v>
+        <v>648.406251401748</v>
       </c>
       <c r="O47">
-        <v>61.3571958401748</v>
+        <v>64.84062514017481</v>
       </c>
       <c r="P47">
-        <v>552.2147625615733</v>
+        <v>583.5656262615732</v>
       </c>
       <c r="Q47">
-        <v>1777.514762561573</v>
+        <v>1808.865626261573</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09197433921012255</v>
+        <v>0.09195153119189875</v>
       </c>
       <c r="T47">
         <v>0.9250455986390608</v>
       </c>
       <c r="U47">
-        <v>0.06808897842796925</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V47">
         <v>0.1</v>
       </c>
       <c r="W47">
-        <v>0.06128008058517233</v>
+        <v>0.05642008058517232</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.396932573268997</v>
+        <v>2.60340325153224</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07829013108336912</v>
+        <v>0.0760419998088539</v>
       </c>
       <c r="C48">
-        <v>7348.512325023625</v>
+        <v>7539.939402845519</v>
       </c>
       <c r="D48">
-        <v>10399.25832502363</v>
+        <v>10590.68540284552</v>
       </c>
       <c r="E48">
         <v>2421.646000000001</v>
@@ -5223,45 +5223,45 @@
         <v>1052.8</v>
       </c>
       <c r="M48">
-        <v>448.9886647448798</v>
+        <v>413.3802763448797</v>
       </c>
       <c r="N48">
-        <v>603.8113352551202</v>
+        <v>639.4197236551202</v>
       </c>
       <c r="O48">
-        <v>60.38113352551202</v>
+        <v>63.94197236551202</v>
       </c>
       <c r="P48">
-        <v>543.4302017296081</v>
+        <v>575.4777512896081</v>
       </c>
       <c r="Q48">
-        <v>1768.730201729608</v>
+        <v>1800.777751289608</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09278017410035157</v>
+        <v>0.0927569680364345</v>
       </c>
       <c r="T48">
         <v>0.9411895008840705</v>
       </c>
       <c r="U48">
-        <v>0.06808897842796925</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V48">
         <v>0.1</v>
       </c>
       <c r="W48">
-        <v>0.06128008058517233</v>
+        <v>0.05642008058517232</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.344825343415323</v>
+        <v>2.546807528672843</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07841833933784328</v>
+        <v>0.07760212119883596</v>
       </c>
       <c r="C49">
-        <v>7194.391667632813</v>
+        <v>7262.250431680174</v>
       </c>
       <c r="D49">
-        <v>10388.48866763281</v>
+        <v>10456.34743168017</v>
       </c>
       <c r="E49">
         <v>2564.997</v>
@@ -5305,37 +5305,37 @@
         <v>1052.8</v>
       </c>
       <c r="M49">
-        <v>458.7492878915075</v>
+        <v>445.9480435915076</v>
       </c>
       <c r="N49">
-        <v>594.0507121084925</v>
+        <v>606.8519564084924</v>
       </c>
       <c r="O49">
-        <v>59.40507121084925</v>
+        <v>60.68519564084924</v>
       </c>
       <c r="P49">
-        <v>534.6456408976433</v>
+        <v>546.1667607676432</v>
       </c>
       <c r="Q49">
-        <v>1759.945640897643</v>
+        <v>1771.466760767643</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09361641785436281</v>
+        <v>0.09359279872416029</v>
       </c>
       <c r="T49">
         <v>0.9579426069873826</v>
       </c>
       <c r="U49">
-        <v>0.06808897842796925</v>
+        <v>0.06618897842796925</v>
       </c>
       <c r="V49">
         <v>0.1</v>
       </c>
       <c r="W49">
-        <v>0.06128008058517233</v>
+        <v>0.05957008058517233</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.294935442491593</v>
+        <v>2.360813137604824</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08057694759231745</v>
+        <v>0.077713242588818</v>
       </c>
       <c r="C50">
-        <v>6873.006869473902</v>
+        <v>7109.460957295943</v>
       </c>
       <c r="D50">
-        <v>10210.4548694739</v>
+        <v>10446.90895729594</v>
       </c>
       <c r="E50">
         <v>2708.348</v>
@@ -5387,45 +5387,45 @@
         <v>1052.8</v>
       </c>
       <c r="M50">
-        <v>500.8498966381354</v>
+        <v>455.4362998381354</v>
       </c>
       <c r="N50">
-        <v>551.9501033618646</v>
+        <v>597.3637001618646</v>
       </c>
       <c r="O50">
-        <v>55.19501033618647</v>
+        <v>59.73637001618646</v>
       </c>
       <c r="P50">
-        <v>496.7550930256782</v>
+        <v>537.6273301456781</v>
       </c>
       <c r="Q50">
-        <v>1722.055093025678</v>
+        <v>1762.927330145678</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09448482482968218</v>
+        <v>0.09446077674602937</v>
       </c>
       <c r="T50">
         <v>0.9753400633254373</v>
       </c>
       <c r="U50">
-        <v>0.07278897842796925</v>
+        <v>0.06618897842796925</v>
       </c>
       <c r="V50">
         <v>0.1</v>
       </c>
       <c r="W50">
-        <v>0.06551008058517233</v>
+        <v>0.05957008058517233</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.102026988658139</v>
+        <v>2.31162953057139</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08074745584679162</v>
+        <v>0.07782436397880003</v>
       </c>
       <c r="C51">
-        <v>6715.852686467594</v>
+        <v>6956.688506917267</v>
       </c>
       <c r="D51">
-        <v>10196.65168646759</v>
+        <v>10437.48750691727</v>
       </c>
       <c r="E51">
         <v>2851.699</v>
@@ -5469,45 +5469,45 @@
         <v>1052.8</v>
       </c>
       <c r="M51">
-        <v>511.2842694847631</v>
+        <v>464.9245560847632</v>
       </c>
       <c r="N51">
-        <v>541.5157305152368</v>
+        <v>587.8754439152367</v>
       </c>
       <c r="O51">
-        <v>54.15157305152368</v>
+        <v>58.78754439152367</v>
       </c>
       <c r="P51">
-        <v>487.3641574637131</v>
+        <v>529.0878995237131</v>
       </c>
       <c r="Q51">
-        <v>1712.664157463713</v>
+        <v>1754.387899523713</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09538728698050428</v>
+        <v>0.09536279312169724</v>
       </c>
       <c r="T51">
         <v>0.9934197728532199</v>
       </c>
       <c r="U51">
-        <v>0.07278897842796925</v>
+        <v>0.06618897842796925</v>
       </c>
       <c r="V51">
         <v>0.1</v>
       </c>
       <c r="W51">
-        <v>0.06551008058517233</v>
+        <v>0.05957008058517233</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.059128478685524</v>
+        <v>2.264453417702587</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08091796410126578</v>
+        <v>0.07919548536878207</v>
       </c>
       <c r="C52">
-        <v>6558.735773228956</v>
+        <v>6698.469753857277</v>
       </c>
       <c r="D52">
-        <v>10182.88577322896</v>
+        <v>10322.61975385728</v>
       </c>
       <c r="E52">
         <v>2995.05</v>
@@ -5551,37 +5551,37 @@
         <v>1052.8</v>
       </c>
       <c r="M52">
-        <v>521.718642331391</v>
+        <v>494.481952331391</v>
       </c>
       <c r="N52">
-        <v>531.0813576686089</v>
+        <v>558.3180476686089</v>
       </c>
       <c r="O52">
-        <v>53.1081357668609</v>
+        <v>55.83180476686089</v>
       </c>
       <c r="P52">
-        <v>477.973221901748</v>
+        <v>502.486242901748</v>
       </c>
       <c r="Q52">
-        <v>1703.273221901748</v>
+        <v>1727.786242901748</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09632584761735924</v>
+        <v>0.09630089015239182</v>
       </c>
       <c r="T52">
         <v>1.012222670762114</v>
       </c>
       <c r="U52">
-        <v>0.07278897842796925</v>
+        <v>0.06898897842796925</v>
       </c>
       <c r="V52">
         <v>0.1</v>
       </c>
       <c r="W52">
-        <v>0.06551008058517233</v>
+        <v>0.06209008058517233</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.017945909111813</v>
+        <v>2.129096916553258</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08535717235573995</v>
+        <v>0.07933180675876411</v>
       </c>
       <c r="C53">
-        <v>6069.62398160204</v>
+        <v>6543.836256290419</v>
       </c>
       <c r="D53">
-        <v>9837.124981602041</v>
+        <v>10311.33725629042</v>
       </c>
       <c r="E53">
         <v>3138.401000000001</v>
@@ -5633,45 +5633,45 @@
         <v>1052.8</v>
       </c>
       <c r="M53">
-        <v>600.1443944780189</v>
+        <v>504.3715913780189</v>
       </c>
       <c r="N53">
-        <v>452.6556055219811</v>
+        <v>548.4284086219811</v>
       </c>
       <c r="O53">
-        <v>45.26556055219811</v>
+        <v>54.84284086219812</v>
       </c>
       <c r="P53">
-        <v>407.390044969783</v>
+        <v>493.585567759783</v>
       </c>
       <c r="Q53">
-        <v>1632.690044969783</v>
+        <v>1718.885567759783</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09730271685163686</v>
+        <v>0.09727727685780863</v>
       </c>
       <c r="T53">
         <v>1.031793033891778</v>
       </c>
       <c r="U53">
-        <v>0.08208897842796925</v>
+        <v>0.06898897842796925</v>
       </c>
       <c r="V53">
         <v>0.1</v>
       </c>
       <c r="W53">
-        <v>0.07388008058517233</v>
+        <v>0.06209008058517233</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.754244494636466</v>
+        <v>2.087349918189469</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08781098061021411</v>
+        <v>0.07946812814874615</v>
       </c>
       <c r="C54">
-        <v>5745.041990861904</v>
+        <v>6389.22739506098</v>
       </c>
       <c r="D54">
-        <v>9655.893990861905</v>
+        <v>10300.07939506098</v>
       </c>
       <c r="E54">
         <v>3281.752</v>
@@ -5715,45 +5715,45 @@
         <v>1052.8</v>
       </c>
       <c r="M54">
-        <v>646.9469160246467</v>
+        <v>514.2612304246467</v>
       </c>
       <c r="N54">
-        <v>405.8530839753532</v>
+        <v>538.5387695753533</v>
       </c>
       <c r="O54">
-        <v>40.58530839753533</v>
+        <v>53.85387695753533</v>
       </c>
       <c r="P54">
-        <v>365.2677755778179</v>
+        <v>484.6848926178179</v>
       </c>
       <c r="Q54">
-        <v>1590.567775577818</v>
+        <v>1709.984892617818</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09832028897067605</v>
+        <v>0.09829434634261781</v>
       </c>
       <c r="T54">
         <v>1.052178828818513</v>
       </c>
       <c r="U54">
-        <v>0.08678897842796926</v>
+        <v>0.06898897842796925</v>
       </c>
       <c r="V54">
         <v>0.1</v>
       </c>
       <c r="W54">
-        <v>0.07811008058517234</v>
+        <v>0.06209008058517233</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.62733598989734</v>
+        <v>2.047208573608902</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08810748886468828</v>
+        <v>0.07960444953872819</v>
       </c>
       <c r="C55">
-        <v>5580.242971838348</v>
+        <v>6234.643089563506</v>
       </c>
       <c r="D55">
-        <v>9634.44597183835</v>
+        <v>10288.84608956351</v>
       </c>
       <c r="E55">
         <v>3425.103000000001</v>
@@ -5797,45 +5797,45 @@
         <v>1052.8</v>
       </c>
       <c r="M55">
-        <v>659.3882028712746</v>
+        <v>524.1508694712745</v>
       </c>
       <c r="N55">
-        <v>393.4117971287253</v>
+        <v>528.6491305287254</v>
       </c>
       <c r="O55">
-        <v>39.34117971287253</v>
+        <v>52.86491305287255</v>
       </c>
       <c r="P55">
-        <v>354.0706174158528</v>
+        <v>475.7842174758529</v>
       </c>
       <c r="Q55">
-        <v>1579.370617415853</v>
+        <v>1701.084217475853</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09938116203095096</v>
+        <v>0.09935469537997207</v>
       </c>
       <c r="T55">
         <v>1.073432104380427</v>
       </c>
       <c r="U55">
-        <v>0.08678897842796926</v>
+        <v>0.06898897842796925</v>
       </c>
       <c r="V55">
         <v>0.1</v>
       </c>
       <c r="W55">
-        <v>0.07811008058517234</v>
+        <v>0.06209008058517233</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.596631537257768</v>
+        <v>2.008581996748357</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08840399711916246</v>
+        <v>0.08353157092871025</v>
       </c>
       <c r="C56">
-        <v>5415.539023862101</v>
+        <v>5777.884637127891</v>
       </c>
       <c r="D56">
-        <v>9613.093023862102</v>
+        <v>9975.438637127892</v>
       </c>
       <c r="E56">
         <v>3568.454000000001</v>
@@ -5879,45 +5879,45 @@
         <v>1052.8</v>
       </c>
       <c r="M56">
-        <v>671.8294897179024</v>
+        <v>594.4199497179023</v>
       </c>
       <c r="N56">
-        <v>380.9705102820975</v>
+        <v>458.3800502820976</v>
       </c>
       <c r="O56">
-        <v>38.09705102820975</v>
+        <v>45.83800502820976</v>
       </c>
       <c r="P56">
-        <v>342.8734592538877</v>
+        <v>412.5420452538879</v>
       </c>
       <c r="Q56">
-        <v>1568.173459253888</v>
+        <v>1637.842045253888</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.10048816000689</v>
+        <v>0.1004611465493852</v>
       </c>
       <c r="T56">
         <v>1.095609435401556</v>
       </c>
       <c r="U56">
-        <v>0.08678897842796926</v>
+        <v>0.07678897842796925</v>
       </c>
       <c r="V56">
         <v>0.1</v>
       </c>
       <c r="W56">
-        <v>0.07811008058517234</v>
+        <v>0.06911008058517233</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.567064286567809</v>
+        <v>1.771138402235043</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08870050537363662</v>
+        <v>0.0856685923186923</v>
       </c>
       <c r="C57">
-        <v>5250.929516209449</v>
+        <v>5471.877901373525</v>
       </c>
       <c r="D57">
-        <v>9591.83451620945</v>
+        <v>9812.782901373526</v>
       </c>
       <c r="E57">
         <v>3711.805000000001</v>
@@ -5961,37 +5961,37 @@
         <v>1052.8</v>
       </c>
       <c r="M57">
-        <v>684.2707765645303</v>
+        <v>636.1765160645302</v>
       </c>
       <c r="N57">
-        <v>368.5292234354697</v>
+        <v>416.6234839354697</v>
       </c>
       <c r="O57">
-        <v>36.85292234354697</v>
+        <v>41.66234839354698</v>
       </c>
       <c r="P57">
-        <v>331.6763010919227</v>
+        <v>374.9611355419228</v>
       </c>
       <c r="Q57">
-        <v>1556.976301091923</v>
+        <v>1600.261135541923</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1016443578928707</v>
+        <v>0.1016167733263278</v>
       </c>
       <c r="T57">
         <v>1.118772425579178</v>
       </c>
       <c r="U57">
-        <v>0.08678897842796926</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V57">
         <v>0.1</v>
       </c>
       <c r="W57">
-        <v>0.07811008058517234</v>
+        <v>0.07262008058517233</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.538572208630212</v>
+        <v>1.654886613094045</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08899701362811079</v>
+        <v>0.08591021370867434</v>
       </c>
       <c r="C58">
-        <v>5086.413823723526</v>
+        <v>5310.469462314471</v>
       </c>
       <c r="D58">
-        <v>9570.669823723527</v>
+        <v>9794.725462314473</v>
       </c>
       <c r="E58">
         <v>3855.156000000001</v>
@@ -6043,37 +6043,37 @@
         <v>1052.8</v>
       </c>
       <c r="M58">
-        <v>696.7120634111581</v>
+        <v>647.743361811158</v>
       </c>
       <c r="N58">
-        <v>356.0879365888419</v>
+        <v>405.0566381888419</v>
       </c>
       <c r="O58">
-        <v>35.60879365888419</v>
+        <v>40.50566381888419</v>
       </c>
       <c r="P58">
-        <v>320.4791429299577</v>
+        <v>364.5509743699577</v>
       </c>
       <c r="Q58">
-        <v>1545.779142929958</v>
+        <v>1589.850974369958</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1028531102282143</v>
+        <v>0.1028249285931314</v>
       </c>
       <c r="T58">
         <v>1.142988278946693</v>
       </c>
       <c r="U58">
-        <v>0.08678897842796926</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V58">
         <v>0.1</v>
       </c>
       <c r="W58">
-        <v>0.07811008058517234</v>
+        <v>0.07262008058517233</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.511097704904673</v>
+        <v>1.625335066431652</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1149037873121649</v>
+        <v>0.08615183509865638</v>
       </c>
       <c r="C59">
-        <v>3396.153714239623</v>
+        <v>5149.127359620179</v>
       </c>
       <c r="D59">
-        <v>8023.760714239624</v>
+        <v>9776.734359620181</v>
       </c>
       <c r="E59">
         <v>3998.507000000001</v>
@@ -6125,45 +6125,45 @@
         <v>1052.8</v>
       </c>
       <c r="M59">
-        <v>1109.532693257786</v>
+        <v>659.3102075577858</v>
       </c>
       <c r="N59">
-        <v>-56.73269325778597</v>
+        <v>393.4897924422141</v>
       </c>
       <c r="O59">
-        <v>-5.673269325778597</v>
+        <v>39.34897924422142</v>
       </c>
       <c r="P59">
-        <v>-51.05942393200737</v>
+        <v>354.1408131979927</v>
       </c>
       <c r="Q59">
-        <v>1174.240576067993</v>
+        <v>1579.440813197993</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1042983271408834</v>
+        <v>0.1040892771281585</v>
       </c>
       <c r="T59">
-        <v>1.171941406744789</v>
+        <v>1.168330451075487</v>
       </c>
       <c r="U59">
-        <v>0.1357889784279692</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V59">
-        <v>0.09488679390859511</v>
+        <v>0.1</v>
       </c>
       <c r="W59">
-        <v>0.1229043976168159</v>
+        <v>0.07262008058517233</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.948867939085951</v>
+        <v>1.596820416143377</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1158036770964446</v>
+        <v>0.08639345648863841</v>
       </c>
       <c r="C60">
-        <v>3208.006123221654</v>
+        <v>4987.851228417883</v>
       </c>
       <c r="D60">
-        <v>7978.964123221655</v>
+        <v>9758.809228417884</v>
       </c>
       <c r="E60">
         <v>4141.858</v>
@@ -6207,45 +6207,45 @@
         <v>1052.8</v>
       </c>
       <c r="M60">
-        <v>1128.998179104414</v>
+        <v>670.8770533044136</v>
       </c>
       <c r="N60">
-        <v>-76.19817910441361</v>
+        <v>381.9229466955863</v>
       </c>
       <c r="O60">
-        <v>-7.619817910441362</v>
+        <v>38.19229466955863</v>
       </c>
       <c r="P60">
-        <v>-68.57836119397226</v>
+        <v>343.7306520260277</v>
       </c>
       <c r="Q60">
-        <v>1156.721638806028</v>
+        <v>1569.030652026028</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1056911444537616</v>
+        <v>0.1054138327362821</v>
       </c>
       <c r="T60">
-        <v>1.199844773572046</v>
+        <v>1.194879393305653</v>
       </c>
       <c r="U60">
-        <v>0.1357889784279692</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V60">
-        <v>0.09325081470327451</v>
+        <v>0.1</v>
       </c>
       <c r="W60">
-        <v>0.1231265455618358</v>
+        <v>0.07262008058517233</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.9325081470327451</v>
+        <v>1.569289029658147</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1167035668807243</v>
+        <v>0.08663507787862046</v>
       </c>
       <c r="C61">
-        <v>3020.35595311573</v>
+        <v>4826.640706505817</v>
       </c>
       <c r="D61">
-        <v>7934.664953115729</v>
+        <v>9740.949706505817</v>
       </c>
       <c r="E61">
         <v>4285.208999999999</v>
@@ -6289,45 +6289,45 @@
         <v>1052.8</v>
       </c>
       <c r="M61">
-        <v>1148.463664951041</v>
+        <v>682.4438990510413</v>
       </c>
       <c r="N61">
-        <v>-95.66366495104126</v>
+        <v>370.3561009489587</v>
       </c>
       <c r="O61">
-        <v>-9.566366495104125</v>
+        <v>37.03561009489587</v>
       </c>
       <c r="P61">
-        <v>-86.09729845593714</v>
+        <v>333.3204908540628</v>
       </c>
       <c r="Q61">
-        <v>1139.202701544063</v>
+        <v>1558.620490854063</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.107151904074585</v>
+        <v>0.1068030008130946</v>
       </c>
       <c r="T61">
-        <v>1.229109280244534</v>
+        <v>1.222723405888509</v>
       </c>
       <c r="U61">
-        <v>0.1357889784279692</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V61">
-        <v>0.09167029242016818</v>
+        <v>0.1</v>
       </c>
       <c r="W61">
-        <v>0.1233411630680414</v>
+        <v>0.07262008058517233</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.9167029242016818</v>
+        <v>1.542690910511399</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.117603456665004</v>
+        <v>0.0868766992686025</v>
       </c>
       <c r="C62">
-        <v>2833.194964630879</v>
+        <v>4665.495434328823</v>
       </c>
       <c r="D62">
-        <v>7890.854964630878</v>
+        <v>9723.155434328823</v>
       </c>
       <c r="E62">
         <v>4428.559999999999</v>
@@ -6371,45 +6371,45 @@
         <v>1052.8</v>
       </c>
       <c r="M62">
-        <v>1167.929150797669</v>
+        <v>694.0107447976692</v>
       </c>
       <c r="N62">
-        <v>-115.1291507976691</v>
+        <v>358.7892552023308</v>
       </c>
       <c r="O62">
-        <v>-11.51291507976691</v>
+        <v>35.87892552023308</v>
       </c>
       <c r="P62">
-        <v>-103.6162357179022</v>
+        <v>322.9103296820977</v>
       </c>
       <c r="Q62">
-        <v>1121.683764282098</v>
+        <v>1548.210329682098</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1086857016764496</v>
+        <v>0.1082616272937478</v>
       </c>
       <c r="T62">
-        <v>1.259837012250648</v>
+        <v>1.251959619100509</v>
       </c>
       <c r="U62">
-        <v>0.1357889784279692</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V62">
-        <v>0.09014245421316537</v>
+        <v>0.1</v>
       </c>
       <c r="W62">
-        <v>0.1235486266573735</v>
+        <v>0.07262008058517233</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.9014245421316537</v>
+        <v>1.516979395336209</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1185033464492837</v>
+        <v>0.09491412065858455</v>
       </c>
       <c r="C63">
-        <v>2646.515099444678</v>
+        <v>3965.153731541428</v>
       </c>
       <c r="D63">
-        <v>7847.526099444677</v>
+        <v>9166.164731541428</v>
       </c>
       <c r="E63">
         <v>4571.911</v>
@@ -6453,45 +6453,45 @@
         <v>1052.8</v>
       </c>
       <c r="M63">
-        <v>1187.394636644297</v>
+        <v>829.7482267442971</v>
       </c>
       <c r="N63">
-        <v>-134.594636644297</v>
+        <v>223.0517732557029</v>
       </c>
       <c r="O63">
-        <v>-13.4594636644297</v>
+        <v>22.30517732557029</v>
       </c>
       <c r="P63">
-        <v>-121.1351729798673</v>
+        <v>200.7465959301326</v>
       </c>
       <c r="Q63">
-        <v>1104.164827020133</v>
+        <v>1426.046595930133</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1102981555655894</v>
+        <v>0.1097950551323832</v>
       </c>
       <c r="T63">
-        <v>1.29214052538528</v>
+        <v>1.282695125297739</v>
       </c>
       <c r="U63">
-        <v>0.1357889784279692</v>
+        <v>0.09488897842796926</v>
       </c>
       <c r="V63">
-        <v>0.08866470906212987</v>
+        <v>0.1</v>
       </c>
       <c r="W63">
-        <v>0.1237492881618095</v>
+        <v>0.08540008058517233</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.8866470906212987</v>
+        <v>1.268818619993798</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1194032362335634</v>
+        <v>0.111621624368868</v>
       </c>
       <c r="C64">
-        <v>2460.308475261858</v>
+        <v>2846.448396876716</v>
       </c>
       <c r="D64">
-        <v>7804.670475261859</v>
+        <v>8190.810396876716</v>
       </c>
       <c r="E64">
         <v>4715.262000000001</v>
@@ -6535,37 +6535,37 @@
         <v>1052.8</v>
       </c>
       <c r="M64">
-        <v>1206.860122490925</v>
+        <v>1097.540649890925</v>
       </c>
       <c r="N64">
-        <v>-154.0601224909249</v>
+        <v>-44.74064989092517</v>
       </c>
       <c r="O64">
-        <v>-15.40601224909249</v>
+        <v>-4.474064989092517</v>
       </c>
       <c r="P64">
-        <v>-138.6541102418324</v>
+        <v>-40.26658490183265</v>
       </c>
       <c r="Q64">
-        <v>1086.645889758168</v>
+        <v>1185.033415098167</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1119954754488944</v>
+        <v>0.1115859705418014</v>
       </c>
       <c r="T64">
-        <v>1.326144223421735</v>
+        <v>1.318591624812105</v>
       </c>
       <c r="U64">
-        <v>0.1357889784279692</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V64">
-        <v>0.08723463310951488</v>
+        <v>0.09592355418495238</v>
       </c>
       <c r="W64">
-        <v>0.1239434767144895</v>
+        <v>0.1116434767144895</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8723463310951487</v>
+        <v>0.9592355418495238</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1203031260178431</v>
+        <v>0.1123985141531478</v>
       </c>
       <c r="C65">
-        <v>2274.56738103397</v>
+        <v>2662.769467633068</v>
       </c>
       <c r="D65">
-        <v>7762.280381033972</v>
+        <v>8150.482467633069</v>
       </c>
       <c r="E65">
         <v>4858.613000000001</v>
@@ -6617,37 +6617,37 @@
         <v>1052.8</v>
       </c>
       <c r="M65">
-        <v>1226.325608337553</v>
+        <v>1115.242918437553</v>
       </c>
       <c r="N65">
-        <v>-173.5256083375527</v>
+        <v>-62.44291843755309</v>
       </c>
       <c r="O65">
-        <v>-17.35256083375527</v>
+        <v>-6.24429184375531</v>
       </c>
       <c r="P65">
-        <v>-156.1730475037975</v>
+        <v>-56.19862659379778</v>
       </c>
       <c r="Q65">
-        <v>1069.126952496202</v>
+        <v>1169.101373406202</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1137845423529185</v>
+        <v>0.1133639697456339</v>
       </c>
       <c r="T65">
-        <v>1.36198595918989</v>
+        <v>1.354229236293513</v>
       </c>
       <c r="U65">
-        <v>0.1357889784279692</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V65">
-        <v>0.08584995639349081</v>
+        <v>0.09440095808677852</v>
       </c>
       <c r="W65">
-        <v>0.1241315005512114</v>
+        <v>0.1118315005512115</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8584995639349081</v>
+        <v>0.9440095808677852</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1212030158021228</v>
+        <v>0.1131754039374274</v>
       </c>
       <c r="C66">
-        <v>2089.284272333975</v>
+        <v>2479.485706545427</v>
       </c>
       <c r="D66">
-        <v>7720.348272333975</v>
+        <v>8110.549706545427</v>
       </c>
       <c r="E66">
         <v>5001.964</v>
@@ -6699,37 +6699,37 @@
         <v>1052.8</v>
       </c>
       <c r="M66">
-        <v>1245.79109418418</v>
+        <v>1132.945186984181</v>
       </c>
       <c r="N66">
-        <v>-192.9910941841804</v>
+        <v>-80.14518698418078</v>
       </c>
       <c r="O66">
-        <v>-19.29910941841804</v>
+        <v>-8.014518698418078</v>
       </c>
       <c r="P66">
-        <v>-173.6919847657624</v>
+        <v>-72.13066828576271</v>
       </c>
       <c r="Q66">
-        <v>1051.608015234238</v>
+        <v>1153.169331714237</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1156730018627218</v>
+        <v>0.1152407466830126</v>
       </c>
       <c r="T66">
-        <v>1.39981890250072</v>
+        <v>1.391846715079444</v>
       </c>
       <c r="U66">
-        <v>0.1357889784279692</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V66">
-        <v>0.08450855082484254</v>
+        <v>0.09292594311667263</v>
       </c>
       <c r="W66">
-        <v>0.1243136486430358</v>
+        <v>0.1120136486430358</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8450855082484253</v>
+        <v>0.9292594311667262</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1221029055864024</v>
+        <v>0.1139522937217071</v>
       </c>
       <c r="C67">
-        <v>1904.45176687994</v>
+        <v>2296.591333630071</v>
       </c>
       <c r="D67">
-        <v>7678.866766879941</v>
+        <v>8071.006333630071</v>
       </c>
       <c r="E67">
         <v>5145.315000000001</v>
@@ -6781,37 +6781,37 @@
         <v>1052.8</v>
       </c>
       <c r="M67">
-        <v>1265.256580030808</v>
+        <v>1150.647455530809</v>
       </c>
       <c r="N67">
-        <v>-212.4565800308085</v>
+        <v>-97.8474555308087</v>
       </c>
       <c r="O67">
-        <v>-21.24565800308085</v>
+        <v>-9.784745553080871</v>
       </c>
       <c r="P67">
-        <v>-191.2109220277276</v>
+        <v>-88.06270997772783</v>
       </c>
       <c r="Q67">
-        <v>1034.089077972272</v>
+        <v>1137.237290022272</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1176693733445139</v>
+        <v>0.117224768016813</v>
       </c>
       <c r="T67">
-        <v>1.439813728286455</v>
+        <v>1.431613764081714</v>
       </c>
       <c r="U67">
-        <v>0.1357889784279692</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V67">
-        <v>0.0832084192736911</v>
+        <v>0.09149631322256996</v>
       </c>
       <c r="W67">
-        <v>0.1244901921781886</v>
+        <v>0.1121901921781886</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8320841927369109</v>
+        <v>0.9149631322256995</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1230027953706821</v>
+        <v>0.1147291835059868</v>
       </c>
       <c r="C68">
-        <v>1720.062640202301</v>
+        <v>2114.080681078709</v>
       </c>
       <c r="D68">
-        <v>7637.828640202302</v>
+        <v>8031.84668107871</v>
       </c>
       <c r="E68">
         <v>5288.666000000001</v>
@@ -6863,37 +6863,37 @@
         <v>1052.8</v>
       </c>
       <c r="M68">
-        <v>1284.722065877436</v>
+        <v>1168.349724077436</v>
       </c>
       <c r="N68">
-        <v>-231.9220658774364</v>
+        <v>-115.5497240774364</v>
       </c>
       <c r="O68">
-        <v>-23.19220658774364</v>
+        <v>-11.55497240774364</v>
       </c>
       <c r="P68">
-        <v>-208.7298592896927</v>
+        <v>-103.9947516696928</v>
       </c>
       <c r="Q68">
-        <v>1016.570140710307</v>
+        <v>1121.305248330307</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1197831784428819</v>
+        <v>0.1193254964878957</v>
       </c>
       <c r="T68">
-        <v>1.482161190883116</v>
+        <v>1.473720051260588</v>
       </c>
       <c r="U68">
-        <v>0.1357889784279692</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V68">
-        <v>0.08194768564833214</v>
+        <v>0.09011000544647041</v>
       </c>
       <c r="W68">
-        <v>0.1246613859092459</v>
+        <v>0.1123613859092459</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8194768564833214</v>
+        <v>0.9011000544647041</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1239026851549618</v>
+        <v>0.1155060732902665</v>
       </c>
       <c r="C69">
-        <v>1536.109821449289</v>
+        <v>1931.948190550309</v>
       </c>
       <c r="D69">
-        <v>7597.22682144929</v>
+        <v>7993.065190550311</v>
       </c>
       <c r="E69">
         <v>5432.017000000002</v>
@@ -6945,37 +6945,37 @@
         <v>1052.8</v>
       </c>
       <c r="M69">
-        <v>1304.187551724064</v>
+        <v>1186.051992624064</v>
       </c>
       <c r="N69">
-        <v>-251.3875517240642</v>
+        <v>-133.2519926240643</v>
       </c>
       <c r="O69">
-        <v>-25.13875517240642</v>
+        <v>-13.32519926240643</v>
       </c>
       <c r="P69">
-        <v>-226.2487965516578</v>
+        <v>-119.9267933616579</v>
       </c>
       <c r="Q69">
-        <v>999.0512034483422</v>
+        <v>1105.373206638342</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1220250929411511</v>
+        <v>0.1215535418360138</v>
       </c>
       <c r="T69">
-        <v>1.527075166364422</v>
+        <v>1.518378234632121</v>
       </c>
       <c r="U69">
-        <v>0.1357889784279692</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V69">
-        <v>0.08072458586253613</v>
+        <v>0.08876507999204547</v>
       </c>
       <c r="W69">
-        <v>0.1248274693796746</v>
+        <v>0.1125274693796746</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8072458586253612</v>
+        <v>0.8876507999204548</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1830878838715327</v>
+        <v>0.1162829630745462</v>
       </c>
       <c r="C70">
-        <v>-575.318473656811</v>
+        <v>1750.188410540999</v>
       </c>
       <c r="D70">
-        <v>5629.14952634319</v>
+        <v>7954.656410540999</v>
       </c>
       <c r="E70">
         <v>5575.368</v>
@@ -7027,45 +7027,45 @@
         <v>1052.8</v>
       </c>
       <c r="M70">
-        <v>2151.247030770692</v>
+        <v>1203.754261170692</v>
       </c>
       <c r="N70">
-        <v>-1098.447030770692</v>
+        <v>-150.954261170692</v>
       </c>
       <c r="O70">
-        <v>-109.8447030770692</v>
+        <v>-15.0954261170692</v>
       </c>
       <c r="P70">
-        <v>-988.602327693623</v>
+        <v>-135.8588350536228</v>
       </c>
       <c r="Q70">
-        <v>236.6976723063769</v>
+        <v>1089.441164946377</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1261362175089719</v>
+        <v>0.1239208400183892</v>
       </c>
       <c r="T70">
-        <v>1.609436446503453</v>
+        <v>1.565827554464375</v>
       </c>
       <c r="U70">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V70">
-        <v>0.04893905650727758</v>
+        <v>0.08745971116863305</v>
       </c>
       <c r="W70">
-        <v>0.2098886680421495</v>
+        <v>0.1126886680421495</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.4893905650727757</v>
+        <v>0.8745971116863305</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1848367736558124</v>
+        <v>0.1170598528588259</v>
       </c>
       <c r="C71">
-        <v>-761.4323960229794</v>
+        <v>1568.795993829433</v>
       </c>
       <c r="D71">
-        <v>5586.386603977021</v>
+        <v>7916.614993829435</v>
       </c>
       <c r="E71">
         <v>5718.719000000001</v>
@@ -7109,45 +7109,45 @@
         <v>1052.8</v>
       </c>
       <c r="M71">
-        <v>2182.88301651732</v>
+        <v>1221.45652971732</v>
       </c>
       <c r="N71">
-        <v>-1130.08301651732</v>
+        <v>-168.6565297173199</v>
       </c>
       <c r="O71">
-        <v>-113.008301651732</v>
+        <v>-16.86565297173199</v>
       </c>
       <c r="P71">
-        <v>-1017.074714865588</v>
+        <v>-151.7908767455879</v>
       </c>
       <c r="Q71">
-        <v>208.225285134412</v>
+        <v>1073.509123254412</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1287277083963581</v>
+        <v>0.1264408671157566</v>
       </c>
       <c r="T71">
-        <v>1.661353751229371</v>
+        <v>1.616338120737419</v>
       </c>
       <c r="U71">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V71">
-        <v>0.0482297948187663</v>
+        <v>0.08619217912271084</v>
       </c>
       <c r="W71">
-        <v>0.2100451942796252</v>
+        <v>0.1128451942796252</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.482297948187663</v>
+        <v>0.8619217912271082</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1865856634400921</v>
+        <v>0.1178367426431056</v>
       </c>
       <c r="C72">
-        <v>-946.9015032422885</v>
+        <v>1387.76569499514</v>
       </c>
       <c r="D72">
-        <v>5544.268496757713</v>
+        <v>7878.935694995141</v>
       </c>
       <c r="E72">
         <v>5862.070000000002</v>
@@ -7191,45 +7191,45 @@
         <v>1052.8</v>
       </c>
       <c r="M72">
-        <v>2214.519002263948</v>
+        <v>1239.158798263948</v>
       </c>
       <c r="N72">
-        <v>-1161.719002263948</v>
+        <v>-186.3587982639478</v>
       </c>
       <c r="O72">
-        <v>-116.1719002263948</v>
+        <v>-18.63587982639478</v>
       </c>
       <c r="P72">
-        <v>-1045.547102037553</v>
+        <v>-167.7229184375531</v>
       </c>
       <c r="Q72">
-        <v>179.7528979624467</v>
+        <v>1057.577081562447</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1314919653429033</v>
+        <v>0.1291288960196152</v>
       </c>
       <c r="T72">
-        <v>1.716732209603683</v>
+        <v>1.670216058095333</v>
       </c>
       <c r="U72">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V72">
-        <v>0.04754079774992678</v>
+        <v>0.08496086227810068</v>
       </c>
       <c r="W72">
-        <v>0.2101972483388872</v>
+        <v>0.1129972483388872</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.4754079774992678</v>
+        <v>0.8496086227810067</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1883345532243718</v>
+        <v>0.1186136324273853</v>
       </c>
       <c r="C73">
-        <v>-1131.740270772189</v>
+        <v>1207.09236800735</v>
       </c>
       <c r="D73">
-        <v>5502.780729227811</v>
+        <v>7841.61336800735</v>
       </c>
       <c r="E73">
         <v>6005.421</v>
@@ -7273,45 +7273,45 @@
         <v>1052.8</v>
       </c>
       <c r="M73">
-        <v>2246.154988010575</v>
+        <v>1256.861066810575</v>
       </c>
       <c r="N73">
-        <v>-1193.354988010575</v>
+        <v>-204.0610668105755</v>
       </c>
       <c r="O73">
-        <v>-119.3354988010576</v>
+        <v>-20.40610668105755</v>
       </c>
       <c r="P73">
-        <v>-1074.019489209518</v>
+        <v>-183.654960129518</v>
       </c>
       <c r="Q73">
-        <v>151.2805107904821</v>
+        <v>1041.645039870482</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1344468606995551</v>
+        <v>0.1320023062271881</v>
       </c>
       <c r="T73">
-        <v>1.775929872003809</v>
+        <v>1.727809715271034</v>
       </c>
       <c r="U73">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V73">
-        <v>0.04687120904922359</v>
+        <v>0.08376423041502884</v>
       </c>
       <c r="W73">
-        <v>0.2103450191852123</v>
+        <v>0.1131450191852123</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.4687120904922359</v>
+        <v>0.8376423041502883</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1900834430086514</v>
+        <v>0.119390522211665</v>
       </c>
       <c r="C74">
-        <v>-1315.962744008828</v>
+        <v>1026.770963882082</v>
       </c>
       <c r="D74">
-        <v>5461.909255991171</v>
+        <v>7804.642963882081</v>
       </c>
       <c r="E74">
         <v>6148.771999999999</v>
@@ -7355,45 +7355,45 @@
         <v>1052.8</v>
       </c>
       <c r="M74">
-        <v>2277.790973757203</v>
+        <v>1274.563335357203</v>
       </c>
       <c r="N74">
-        <v>-1224.990973757203</v>
+        <v>-221.7633353572032</v>
       </c>
       <c r="O74">
-        <v>-122.4990973757203</v>
+        <v>-22.17633353572032</v>
       </c>
       <c r="P74">
-        <v>-1102.491876381483</v>
+        <v>-199.5870018214829</v>
       </c>
       <c r="Q74">
-        <v>122.8081236185171</v>
+        <v>1025.712998178517</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1376128200102535</v>
+        <v>0.1350809600210162</v>
       </c>
       <c r="T74">
-        <v>1.839355938861088</v>
+        <v>1.789517205102142</v>
       </c>
       <c r="U74">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V74">
-        <v>0.04622022003465105</v>
+        <v>0.08260083832593124</v>
       </c>
       <c r="W74">
-        <v>0.2104886852858062</v>
+        <v>0.1132886852858062</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.4622022003465105</v>
+        <v>0.8260083832593121</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1918323327929311</v>
+        <v>0.1201674119959447</v>
       </c>
       <c r="C75">
-        <v>-1499.582554140527</v>
+        <v>846.7965284051697</v>
       </c>
       <c r="D75">
-        <v>5421.640445859473</v>
+        <v>7768.019528405169</v>
       </c>
       <c r="E75">
         <v>6292.123</v>
@@ -7437,45 +7437,45 @@
         <v>1052.8</v>
       </c>
       <c r="M75">
-        <v>2309.426959503831</v>
+        <v>1292.265603903831</v>
       </c>
       <c r="N75">
-        <v>-1256.626959503831</v>
+        <v>-239.4656039038312</v>
       </c>
       <c r="O75">
-        <v>-125.6626959503831</v>
+        <v>-23.94656039038312</v>
       </c>
       <c r="P75">
-        <v>-1130.964263553448</v>
+        <v>-215.519043513448</v>
       </c>
       <c r="Q75">
-        <v>94.33573644655212</v>
+        <v>1009.780956486552</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1410132948254481</v>
+        <v>0.1383876622440168</v>
       </c>
       <c r="T75">
-        <v>1.90748023289298</v>
+        <v>1.855795620105925</v>
       </c>
       <c r="U75">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V75">
-        <v>0.04558706633554624</v>
+        <v>0.08146931999269928</v>
       </c>
       <c r="W75">
-        <v>0.2106284153288495</v>
+        <v>0.1134284153288495</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4558706633554624</v>
+        <v>0.8146931999269929</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1935812225772108</v>
+        <v>0.1209443017802244</v>
       </c>
       <c r="C76">
-        <v>-1682.612933305092</v>
+        <v>667.1641999190961</v>
       </c>
       <c r="D76">
-        <v>5381.961066694908</v>
+        <v>7731.738199919096</v>
       </c>
       <c r="E76">
         <v>6435.474</v>
@@ -7519,45 +7519,45 @@
         <v>1052.8</v>
       </c>
       <c r="M76">
-        <v>2341.062945250459</v>
+        <v>1309.967872450459</v>
       </c>
       <c r="N76">
-        <v>-1288.262945250459</v>
+        <v>-257.1678724504591</v>
       </c>
       <c r="O76">
-        <v>-128.8262945250459</v>
+        <v>-25.71678724504591</v>
       </c>
       <c r="P76">
-        <v>-1159.436650725413</v>
+        <v>-231.4510852054132</v>
       </c>
       <c r="Q76">
-        <v>65.86334927458688</v>
+        <v>993.8489147945868</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1446753446264269</v>
+        <v>0.141948726176479</v>
       </c>
       <c r="T76">
-        <v>1.980844857235018</v>
+        <v>1.927172374725384</v>
       </c>
       <c r="U76">
-        <v>0.2206889784279693</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V76">
-        <v>0.0449710248985794</v>
+        <v>0.08036838323604117</v>
       </c>
       <c r="W76">
-        <v>0.210764368884243</v>
+        <v>0.113564368884243</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4497102489857939</v>
+        <v>0.8036838323604117</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1953301123614905</v>
+        <v>0.1840029094603148</v>
       </c>
       <c r="C77">
-        <v>-1865.066729086398</v>
+        <v>-1601.574221987163</v>
       </c>
       <c r="D77">
-        <v>5342.858270913602</v>
+        <v>5606.350778012838</v>
       </c>
       <c r="E77">
         <v>6578.825000000001</v>
@@ -7601,37 +7601,37 @@
         <v>1052.8</v>
       </c>
       <c r="M77">
-        <v>2372.698930997087</v>
+        <v>2211.429055997087</v>
       </c>
       <c r="N77">
-        <v>-1319.898930997087</v>
+        <v>-1158.629055997087</v>
       </c>
       <c r="O77">
-        <v>-131.9898930997087</v>
+        <v>-115.8629055997087</v>
       </c>
       <c r="P77">
-        <v>-1187.909037897378</v>
+        <v>-1042.766150397378</v>
       </c>
       <c r="Q77">
-        <v>37.39096210262187</v>
+        <v>182.5338496026218</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.148630358411484</v>
+        <v>0.1483215468067812</v>
       </c>
       <c r="T77">
-        <v>2.060078651524419</v>
+        <v>2.054907024535054</v>
       </c>
       <c r="U77">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V77">
-        <v>0.044371411233265</v>
+        <v>0.04760722471041761</v>
       </c>
       <c r="W77">
-        <v>0.2108966970114927</v>
+        <v>0.1958966970114927</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.44371411233265</v>
+        <v>0.4760722471041761</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1970790021457702</v>
+        <v>0.1856017992445945</v>
       </c>
       <c r="C78">
-        <v>-2046.956418383554</v>
+        <v>-1783.731218035547</v>
       </c>
       <c r="D78">
-        <v>5304.319581616448</v>
+        <v>5567.544781964454</v>
       </c>
       <c r="E78">
         <v>6722.176000000001</v>
@@ -7683,37 +7683,37 @@
         <v>1052.8</v>
       </c>
       <c r="M78">
-        <v>2404.334916743715</v>
+        <v>2240.914776743715</v>
       </c>
       <c r="N78">
-        <v>-1351.534916743715</v>
+        <v>-1188.114776743715</v>
       </c>
       <c r="O78">
-        <v>-135.1534916743715</v>
+        <v>-118.8114776743715</v>
       </c>
       <c r="P78">
-        <v>-1216.381425069344</v>
+        <v>-1069.303299069343</v>
       </c>
       <c r="Q78">
-        <v>8.918574930656405</v>
+        <v>155.9967009306565</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1529149566786292</v>
+        <v>0.1525932779237304</v>
       </c>
       <c r="T78">
-        <v>2.145915262004603</v>
+        <v>2.140528150557347</v>
       </c>
       <c r="U78">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V78">
-        <v>0.04378757687493257</v>
+        <v>0.04698081385896474</v>
       </c>
       <c r="W78">
-        <v>0.2110255428196043</v>
+        <v>0.1960255428196042</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4378757687493255</v>
+        <v>0.4698081385896474</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1988278919300499</v>
+        <v>0.1872006890288742</v>
       </c>
       <c r="C79">
-        <v>-2228.294120684122</v>
+        <v>-1965.354692911858</v>
       </c>
       <c r="D79">
-        <v>5266.332879315877</v>
+        <v>5529.272307088142</v>
       </c>
       <c r="E79">
         <v>6865.527</v>
@@ -7765,37 +7765,37 @@
         <v>1052.8</v>
       </c>
       <c r="M79">
-        <v>2435.970902490342</v>
+        <v>2270.400497490342</v>
       </c>
       <c r="N79">
-        <v>-1383.170902490342</v>
+        <v>-1217.600497490342</v>
       </c>
       <c r="O79">
-        <v>-138.3170902490342</v>
+        <v>-121.7600497490342</v>
       </c>
       <c r="P79">
-        <v>-1244.853812241308</v>
+        <v>-1095.840447741308</v>
       </c>
       <c r="Q79">
-        <v>-19.55381224130815</v>
+        <v>129.4595522586917</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1575721287081348</v>
+        <v>0.1572364639204143</v>
       </c>
       <c r="T79">
-        <v>2.239215925570021</v>
+        <v>2.233594591885927</v>
       </c>
       <c r="U79">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V79">
-        <v>0.04321890704538799</v>
+        <v>0.04637067341923794</v>
       </c>
       <c r="W79">
-        <v>0.2111510419833492</v>
+        <v>0.1961510419833492</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4321890704538799</v>
+        <v>0.4637067341923793</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2005767817143296</v>
+        <v>0.1887995788131539</v>
       </c>
       <c r="C80">
-        <v>-2409.0916107711</v>
+        <v>-2146.45557410877</v>
       </c>
       <c r="D80">
-        <v>5228.886389228901</v>
+        <v>5491.52242589123</v>
       </c>
       <c r="E80">
         <v>7008.878000000001</v>
@@ -7847,37 +7847,37 @@
         <v>1052.8</v>
       </c>
       <c r="M80">
-        <v>2467.60688823697</v>
+        <v>2299.88621823697</v>
       </c>
       <c r="N80">
-        <v>-1414.806888236971</v>
+        <v>-1247.08621823697</v>
       </c>
       <c r="O80">
-        <v>-141.4806888236971</v>
+        <v>-124.708621823697</v>
       </c>
       <c r="P80">
-        <v>-1273.326199413274</v>
+        <v>-1122.377596413273</v>
       </c>
       <c r="Q80">
-        <v>-48.02619941327362</v>
+        <v>102.9224035867267</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.16265268001305</v>
+        <v>0.1623017577349786</v>
       </c>
       <c r="T80">
-        <v>2.340998467641386</v>
+        <v>2.335121618789834</v>
       </c>
       <c r="U80">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V80">
-        <v>0.04266481849352404</v>
+        <v>0.04577617760617078</v>
       </c>
       <c r="W80">
-        <v>0.2112733232198187</v>
+        <v>0.1962733232198187</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4266481849352404</v>
+        <v>0.4577617760617078</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2023256714986093</v>
+        <v>0.1903984685974336</v>
       </c>
       <c r="C81">
-        <v>-2589.360330891539</v>
+        <v>-2327.044492722389</v>
       </c>
       <c r="D81">
-        <v>5191.968669108463</v>
+        <v>5454.284507277613</v>
       </c>
       <c r="E81">
         <v>7152.229000000001</v>
@@ -7929,37 +7929,37 @@
         <v>1052.8</v>
       </c>
       <c r="M81">
-        <v>2499.242873983598</v>
+        <v>2329.371938983598</v>
       </c>
       <c r="N81">
-        <v>-1446.442873983598</v>
+        <v>-1276.571938983598</v>
       </c>
       <c r="O81">
-        <v>-144.6442873983598</v>
+        <v>-127.6571938983598</v>
       </c>
       <c r="P81">
-        <v>-1301.798586585238</v>
+        <v>-1148.914745085239</v>
       </c>
       <c r="Q81">
-        <v>-76.4985865852384</v>
+        <v>76.38525491476139</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1682170933470047</v>
+        <v>0.1678494604842633</v>
       </c>
       <c r="T81">
-        <v>2.452474585148118</v>
+        <v>2.446317886351255</v>
       </c>
       <c r="U81">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V81">
-        <v>0.04212475749993513</v>
+        <v>0.04519673232001672</v>
       </c>
       <c r="W81">
-        <v>0.2113925087287827</v>
+        <v>0.1963925087287826</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4212475749993513</v>
+        <v>0.4519673232001671</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.204074561282889</v>
+        <v>0.1919973583817133</v>
       </c>
       <c r="C82">
-        <v>-2769.111402413366</v>
+        <v>-2507.131793433884</v>
       </c>
       <c r="D82">
-        <v>5155.568597586636</v>
+        <v>5417.548206566118</v>
       </c>
       <c r="E82">
         <v>7295.580000000002</v>
@@ -8011,37 +8011,37 @@
         <v>1052.8</v>
       </c>
       <c r="M82">
-        <v>2530.878859730226</v>
+        <v>2358.857659730226</v>
       </c>
       <c r="N82">
-        <v>-1478.078859730226</v>
+        <v>-1306.057659730226</v>
       </c>
       <c r="O82">
-        <v>-147.8078859730226</v>
+        <v>-130.6057659730226</v>
       </c>
       <c r="P82">
-        <v>-1330.270973757204</v>
+        <v>-1175.451893757204</v>
       </c>
       <c r="Q82">
-        <v>-104.9709737572039</v>
+        <v>49.84810624279635</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.174337948014355</v>
+        <v>0.1739519335084765</v>
       </c>
       <c r="T82">
-        <v>2.575098314405524</v>
+        <v>2.568633780668817</v>
       </c>
       <c r="U82">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V82">
-        <v>0.04159819803118593</v>
+        <v>0.04463177316601651</v>
       </c>
       <c r="W82">
-        <v>0.2115087146000225</v>
+        <v>0.1965087146000225</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4159819803118593</v>
+        <v>0.446317731660165</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2058234510671687</v>
+        <v>0.193596248165993</v>
       </c>
       <c r="C83">
-        <v>-2948.355636995211</v>
+        <v>-2686.727544090421</v>
       </c>
       <c r="D83">
-        <v>5119.67536300479</v>
+        <v>5381.303455909579</v>
       </c>
       <c r="E83">
         <v>7438.931</v>
@@ -8093,37 +8093,37 @@
         <v>1052.8</v>
       </c>
       <c r="M83">
-        <v>2562.514845476854</v>
+        <v>2388.343380476854</v>
       </c>
       <c r="N83">
-        <v>-1509.714845476854</v>
+        <v>-1335.543380476854</v>
       </c>
       <c r="O83">
-        <v>-150.9714845476854</v>
+        <v>-133.5543380476854</v>
       </c>
       <c r="P83">
-        <v>-1358.743360929168</v>
+        <v>-1201.989042429168</v>
       </c>
       <c r="Q83">
-        <v>-133.4433609291684</v>
+        <v>23.31095757083153</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1811031031730053</v>
+        <v>0.1806967721141858</v>
       </c>
       <c r="T83">
-        <v>2.710629804637394</v>
+        <v>2.703825032282966</v>
       </c>
       <c r="U83">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V83">
-        <v>0.04108464003080093</v>
+        <v>0.04408076362075705</v>
       </c>
       <c r="W83">
-        <v>0.211622051190491</v>
+        <v>0.1966220511904909</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4108464003080092</v>
+        <v>0.4408076362075705</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2075723408514484</v>
+        <v>0.1951951379502727</v>
       </c>
       <c r="C84">
-        <v>-3127.103547292914</v>
+        <v>-2865.841544904069</v>
       </c>
       <c r="D84">
-        <v>5084.278452707086</v>
+        <v>5345.540455095931</v>
       </c>
       <c r="E84">
         <v>7582.282000000001</v>
@@ -8175,37 +8175,37 @@
         <v>1052.8</v>
       </c>
       <c r="M84">
-        <v>2594.150831223482</v>
+        <v>2417.829101223482</v>
       </c>
       <c r="N84">
-        <v>-1541.350831223482</v>
+        <v>-1365.029101223482</v>
       </c>
       <c r="O84">
-        <v>-154.1350831223482</v>
+        <v>-136.5029101223482</v>
       </c>
       <c r="P84">
-        <v>-1387.215748101134</v>
+        <v>-1228.526191101134</v>
       </c>
       <c r="Q84">
-        <v>-161.9157481011337</v>
+        <v>-3.226191101133736</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1886199422381722</v>
+        <v>0.1881910372316405</v>
       </c>
       <c r="T84">
-        <v>2.861220349339471</v>
+        <v>2.854037534076463</v>
       </c>
       <c r="U84">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V84">
-        <v>0.04058360783530335</v>
+        <v>0.04354319333269903</v>
       </c>
       <c r="W84">
-        <v>0.2117326234738749</v>
+        <v>0.1967326234738748</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4058360783530335</v>
+        <v>0.4354319333269903</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2093212306357281</v>
+        <v>0.1967940277345523</v>
       </c>
       <c r="C85">
-        <v>-3305.365357224924</v>
+        <v>-3044.483337286303</v>
       </c>
       <c r="D85">
-        <v>5049.367642775077</v>
+        <v>5310.249662713699</v>
       </c>
       <c r="E85">
         <v>7725.633000000002</v>
@@ -8257,37 +8257,37 @@
         <v>1052.8</v>
       </c>
       <c r="M85">
-        <v>2625.78681697011</v>
+        <v>2447.31482197011</v>
       </c>
       <c r="N85">
-        <v>-1572.98681697011</v>
+        <v>-1394.51482197011</v>
       </c>
       <c r="O85">
-        <v>-157.298681697011</v>
+        <v>-139.451482197011</v>
       </c>
       <c r="P85">
-        <v>-1415.688135273099</v>
+        <v>-1255.063339773099</v>
       </c>
       <c r="Q85">
-        <v>-190.3881352730987</v>
+        <v>-29.76333977309878</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1970211153110059</v>
+        <v>0.1965669805982077</v>
       </c>
       <c r="T85">
-        <v>3.029527428712382</v>
+        <v>3.021922094904492</v>
       </c>
       <c r="U85">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V85">
-        <v>0.04009464870475753</v>
+        <v>0.04301857654555807</v>
       </c>
       <c r="W85">
-        <v>0.211840531364888</v>
+        <v>0.196840531364888</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4009464870475753</v>
+        <v>0.4301857654555807</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2110701204200078</v>
+        <v>0.198392917518832</v>
       </c>
       <c r="C86">
-        <v>-3483.151011817645</v>
+        <v>-3222.662212334879</v>
       </c>
       <c r="D86">
-        <v>5014.932988182356</v>
+        <v>5275.421787665121</v>
       </c>
       <c r="E86">
         <v>7868.984</v>
@@ -8339,37 +8339,37 @@
         <v>1052.8</v>
       </c>
       <c r="M86">
-        <v>2657.422802716737</v>
+        <v>2476.800542716737</v>
       </c>
       <c r="N86">
-        <v>-1604.622802716737</v>
+        <v>-1424.000542716737</v>
       </c>
       <c r="O86">
-        <v>-160.4622802716738</v>
+        <v>-142.4000542716737</v>
       </c>
       <c r="P86">
-        <v>-1444.160522445064</v>
+        <v>-1281.600488445064</v>
       </c>
       <c r="Q86">
-        <v>-218.8605224450637</v>
+        <v>-56.30048844506359</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2064724350179437</v>
+        <v>0.2059899168855955</v>
       </c>
       <c r="T86">
-        <v>3.218872893006904</v>
+        <v>3.21079222583602</v>
       </c>
       <c r="U86">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V86">
-        <v>0.03961733145827232</v>
+        <v>0.04250645063430144</v>
       </c>
       <c r="W86">
-        <v>0.2119458700204009</v>
+        <v>0.1969458700204009</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3961733145827232</v>
+        <v>0.4250645063430144</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2128190102042875</v>
+        <v>0.1999918073031117</v>
       </c>
       <c r="C87">
-        <v>-3660.470186650704</v>
+        <v>-3400.387218988908</v>
       </c>
       <c r="D87">
-        <v>4980.964813349295</v>
+        <v>5241.047781011092</v>
       </c>
       <c r="E87">
         <v>8012.334999999999</v>
@@ -8421,37 +8421,37 @@
         <v>1052.8</v>
       </c>
       <c r="M87">
-        <v>2689.058788463365</v>
+        <v>2506.286263463365</v>
       </c>
       <c r="N87">
-        <v>-1636.258788463365</v>
+        <v>-1453.486263463365</v>
       </c>
       <c r="O87">
-        <v>-163.6258788463365</v>
+        <v>-145.3486263463365</v>
       </c>
       <c r="P87">
-        <v>-1472.632909617028</v>
+        <v>-1308.137637117028</v>
       </c>
       <c r="Q87">
-        <v>-247.3329096170282</v>
+        <v>-82.83763711702841</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2171839306858066</v>
+        <v>0.2166692446779686</v>
       </c>
       <c r="T87">
-        <v>3.433464419207365</v>
+        <v>3.424845040891755</v>
       </c>
       <c r="U87">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V87">
-        <v>0.03915124520582207</v>
+        <v>0.04200637474448613</v>
       </c>
       <c r="W87">
-        <v>0.2120487301193135</v>
+        <v>0.1970487301193135</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3915124520582206</v>
+        <v>0.4200637474448613</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2145678999885671</v>
+        <v>0.2015906970873914</v>
       </c>
       <c r="C88">
-        <v>-3837.332296920909</v>
+        <v>-3577.667171867155</v>
       </c>
       <c r="D88">
-        <v>4947.45370307909</v>
+        <v>5207.118828132845</v>
       </c>
       <c r="E88">
         <v>8155.686</v>
@@ -8503,37 +8503,37 @@
         <v>1052.8</v>
       </c>
       <c r="M88">
-        <v>2720.694774209993</v>
+        <v>2535.771984209993</v>
       </c>
       <c r="N88">
-        <v>-1667.894774209993</v>
+        <v>-1482.971984209993</v>
       </c>
       <c r="O88">
-        <v>-166.7894774209993</v>
+        <v>-148.2971984209993</v>
       </c>
       <c r="P88">
-        <v>-1501.105296788994</v>
+        <v>-1334.674785788994</v>
       </c>
       <c r="Q88">
-        <v>-275.8052967889937</v>
+        <v>-109.3747857889937</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2294256400205071</v>
+        <v>0.2288741907263949</v>
       </c>
       <c r="T88">
-        <v>3.678711877722176</v>
+        <v>3.66947682952688</v>
       </c>
       <c r="U88">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V88">
-        <v>0.03869599816854506</v>
+        <v>0.04151792852652699</v>
       </c>
       <c r="W88">
-        <v>0.2121491981229025</v>
+        <v>0.1971491981229025</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3869599816854505</v>
+        <v>0.4151792852652698</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2163167897728468</v>
+        <v>0.2031895868716711</v>
       </c>
       <c r="C89">
-        <v>-4013.746506142772</v>
+        <v>-3754.510658803847</v>
       </c>
       <c r="D89">
-        <v>4914.390493857228</v>
+        <v>5173.626341196154</v>
       </c>
       <c r="E89">
         <v>8299.037</v>
@@ -8585,37 +8585,37 @@
         <v>1052.8</v>
       </c>
       <c r="M89">
-        <v>2752.330759956621</v>
+        <v>2565.257704956621</v>
       </c>
       <c r="N89">
-        <v>-1699.530759956621</v>
+        <v>-1512.457704956621</v>
       </c>
       <c r="O89">
-        <v>-169.9530759956621</v>
+        <v>-151.2457704956621</v>
       </c>
       <c r="P89">
-        <v>-1529.577683960958</v>
+        <v>-1361.211934460959</v>
       </c>
       <c r="Q89">
-        <v>-304.2776839609585</v>
+        <v>-135.9119344609587</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2435506892528538</v>
+        <v>0.2429568207822714</v>
       </c>
       <c r="T89">
-        <v>3.961689714470036</v>
+        <v>3.951744277952025</v>
       </c>
       <c r="U89">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V89">
-        <v>0.03825121658040087</v>
+        <v>0.04104071095725656</v>
       </c>
       <c r="W89">
-        <v>0.2122473565172136</v>
+        <v>0.1972473565172136</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3825121658040086</v>
+        <v>0.4104071095725655</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2180656795571266</v>
+        <v>0.2047884766559508</v>
       </c>
       <c r="C90">
-        <v>-4189.721734502489</v>
+        <v>-3930.926048095529</v>
       </c>
       <c r="D90">
-        <v>4881.766265497512</v>
+        <v>5140.561951904471</v>
       </c>
       <c r="E90">
         <v>8442.388000000001</v>
@@ -8667,37 +8667,37 @@
         <v>1052.8</v>
       </c>
       <c r="M90">
-        <v>2783.966745703249</v>
+        <v>2594.743425703249</v>
       </c>
       <c r="N90">
-        <v>-1731.166745703249</v>
+        <v>-1541.943425703249</v>
       </c>
       <c r="O90">
-        <v>-173.1166745703249</v>
+        <v>-154.1943425703249</v>
       </c>
       <c r="P90">
-        <v>-1558.050071132924</v>
+        <v>-1387.749083132924</v>
       </c>
       <c r="Q90">
-        <v>-332.7500711329239</v>
+        <v>-162.449083132924</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2600299133572583</v>
+        <v>0.2593865558474607</v>
       </c>
       <c r="T90">
-        <v>4.291830524009207</v>
+        <v>4.281056301114694</v>
       </c>
       <c r="U90">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V90">
-        <v>0.03781654366471449</v>
+        <v>0.04057433924183319</v>
       </c>
       <c r="W90">
-        <v>0.2123432840389267</v>
+        <v>0.1973432840389267</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3781654366471449</v>
+        <v>0.4057433924183319</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2198145693414062</v>
+        <v>0.2063873664402305</v>
       </c>
       <c r="C91">
-        <v>-4365.266666881362</v>
+        <v>-4106.921495471768</v>
       </c>
       <c r="D91">
-        <v>4849.572333118639</v>
+        <v>5107.917504528234</v>
       </c>
       <c r="E91">
         <v>8585.739000000001</v>
@@ -8749,37 +8749,37 @@
         <v>1052.8</v>
       </c>
       <c r="M91">
-        <v>2815.602731449877</v>
+        <v>2624.229146449877</v>
       </c>
       <c r="N91">
-        <v>-1762.802731449877</v>
+        <v>-1571.429146449877</v>
       </c>
       <c r="O91">
-        <v>-176.2802731449877</v>
+        <v>-157.1429146449877</v>
       </c>
       <c r="P91">
-        <v>-1586.522458304889</v>
+        <v>-1414.286231804889</v>
       </c>
       <c r="Q91">
-        <v>-361.222458304889</v>
+        <v>-188.986231804889</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2795053600260999</v>
+        <v>0.2788035154699572</v>
       </c>
       <c r="T91">
-        <v>4.68199693528277</v>
+        <v>4.670243237579667</v>
       </c>
       <c r="U91">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V91">
-        <v>0.0373916386797177</v>
+        <v>0.04011844778967776</v>
       </c>
       <c r="W91">
-        <v>0.2124370558859946</v>
+        <v>0.1974370558859946</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.373916386797177</v>
+        <v>0.4011844778967776</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2215634591256859</v>
+        <v>0.2079862562245102</v>
       </c>
       <c r="C92">
-        <v>-4540.389760563834</v>
+        <v>-4282.504950801973</v>
       </c>
       <c r="D92">
-        <v>4817.800239436167</v>
+        <v>5075.685049198028</v>
       </c>
       <c r="E92">
         <v>8729.09</v>
@@ -8831,37 +8831,37 @@
         <v>1052.8</v>
       </c>
       <c r="M92">
-        <v>2847.238717196504</v>
+        <v>2653.714867196504</v>
       </c>
       <c r="N92">
-        <v>-1794.438717196504</v>
+        <v>-1600.914867196504</v>
       </c>
       <c r="O92">
-        <v>-179.4438717196504</v>
+        <v>-160.0914867196504</v>
       </c>
       <c r="P92">
-        <v>-1614.994845476854</v>
+        <v>-1440.823380476854</v>
       </c>
       <c r="Q92">
-        <v>-389.694845476854</v>
+        <v>-215.5233804768538</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.30287589602871</v>
+        <v>0.302103867016953</v>
       </c>
       <c r="T92">
-        <v>5.150196628811048</v>
+        <v>5.137267561337635</v>
       </c>
       <c r="U92">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V92">
-        <v>0.03697617602772083</v>
+        <v>0.03967268725868134</v>
       </c>
       <c r="W92">
-        <v>0.2125287439142388</v>
+        <v>0.1975287439142388</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3697617602772083</v>
+        <v>0.3967268725868134</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2233123489099656</v>
+        <v>0.2095851460087899</v>
       </c>
       <c r="C93">
-        <v>-4715.099252644493</v>
+        <v>-4457.684164549843</v>
       </c>
       <c r="D93">
-        <v>4786.441747355507</v>
+        <v>5043.856835450159</v>
       </c>
       <c r="E93">
         <v>8872.441000000001</v>
@@ -8913,37 +8913,37 @@
         <v>1052.8</v>
       </c>
       <c r="M93">
-        <v>2878.874702943132</v>
+        <v>2683.200587943132</v>
       </c>
       <c r="N93">
-        <v>-1826.074702943132</v>
+        <v>-1630.400587943132</v>
       </c>
       <c r="O93">
-        <v>-182.6074702943132</v>
+        <v>-163.0400587943132</v>
       </c>
       <c r="P93">
-        <v>-1643.467232648819</v>
+        <v>-1467.360529148819</v>
       </c>
       <c r="Q93">
-        <v>-418.167232648819</v>
+        <v>-242.0605291488191</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3314398844763445</v>
+        <v>0.330582074463281</v>
       </c>
       <c r="T93">
-        <v>5.722440698678943</v>
+        <v>5.708075068152927</v>
       </c>
       <c r="U93">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V93">
-        <v>0.0365698444230206</v>
+        <v>0.0392367236624321</v>
       </c>
       <c r="W93">
-        <v>0.2126184168209831</v>
+        <v>0.1976184168209831</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.365698444230206</v>
+        <v>0.3923672366243209</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2250612386942453</v>
+        <v>0.2111840357930696</v>
       </c>
       <c r="C94">
-        <v>-4889.403167147673</v>
+        <v>-4632.466693986487</v>
       </c>
       <c r="D94">
-        <v>4755.488832852328</v>
+        <v>5012.425306013513</v>
       </c>
       <c r="E94">
         <v>9015.792000000001</v>
@@ -8995,37 +8995,37 @@
         <v>1052.8</v>
       </c>
       <c r="M94">
-        <v>2910.51068868976</v>
+        <v>2712.68630868976</v>
       </c>
       <c r="N94">
-        <v>-1857.71068868976</v>
+        <v>-1659.88630868976</v>
       </c>
       <c r="O94">
-        <v>-185.771068868976</v>
+        <v>-165.988630868976</v>
       </c>
       <c r="P94">
-        <v>-1671.939619820784</v>
+        <v>-1493.897677820784</v>
       </c>
       <c r="Q94">
-        <v>-446.6396198207842</v>
+        <v>-268.5976778207839</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3671448700358876</v>
+        <v>0.3661798337711913</v>
       </c>
       <c r="T94">
-        <v>6.437745786013813</v>
+        <v>6.421584451672046</v>
       </c>
       <c r="U94">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V94">
-        <v>0.03617234611407472</v>
+        <v>0.03881023753566654</v>
       </c>
       <c r="W94">
-        <v>0.2127061403167112</v>
+        <v>0.1977061403167112</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3617234611407473</v>
+        <v>0.3881023753566653</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.226810128478525</v>
+        <v>0.2127829255773493</v>
       </c>
       <c r="C95">
-        <v>-5063.309321872594</v>
+        <v>-4806.859909172714</v>
       </c>
       <c r="D95">
-        <v>4724.933678127408</v>
+        <v>4981.383090827288</v>
       </c>
       <c r="E95">
         <v>9159.143000000002</v>
@@ -9077,37 +9077,37 @@
         <v>1052.8</v>
       </c>
       <c r="M95">
-        <v>2942.146674436388</v>
+        <v>2742.172029436388</v>
       </c>
       <c r="N95">
-        <v>-1889.346674436388</v>
+        <v>-1689.372029436388</v>
       </c>
       <c r="O95">
-        <v>-188.9346674436388</v>
+        <v>-168.9372029436388</v>
       </c>
       <c r="P95">
-        <v>-1700.412006992749</v>
+        <v>-1520.434826492749</v>
       </c>
       <c r="Q95">
-        <v>-475.1120069927492</v>
+        <v>-295.134826492749</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4130512800410145</v>
+        <v>0.4119483814527901</v>
       </c>
       <c r="T95">
-        <v>7.357423755444358</v>
+        <v>7.338953659053767</v>
       </c>
       <c r="U95">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V95">
-        <v>0.03578339615585887</v>
+        <v>0.03839292315356259</v>
       </c>
       <c r="W95">
-        <v>0.2127919772856494</v>
+        <v>0.1977919772856495</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3578339615585887</v>
+        <v>0.3839292315356259</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2285590182628047</v>
+        <v>0.214381815361629</v>
       </c>
       <c r="C96">
-        <v>-5236.825334976296</v>
+        <v>-4980.870998720329</v>
       </c>
       <c r="D96">
-        <v>4694.768665023704</v>
+        <v>4950.723001279672</v>
       </c>
       <c r="E96">
         <v>9302.494000000001</v>
@@ -9159,37 +9159,37 @@
         <v>1052.8</v>
       </c>
       <c r="M96">
-        <v>2973.782660183016</v>
+        <v>2771.657750183015</v>
       </c>
       <c r="N96">
-        <v>-1920.982660183016</v>
+        <v>-1718.857750183015</v>
       </c>
       <c r="O96">
-        <v>-192.0982660183016</v>
+        <v>-171.8857750183015</v>
       </c>
       <c r="P96">
-        <v>-1728.884394164714</v>
+        <v>-1546.971975164714</v>
       </c>
       <c r="Q96">
-        <v>-503.5843941647142</v>
+        <v>-321.6719751647138</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.474259826714517</v>
+        <v>0.472973111694922</v>
       </c>
       <c r="T96">
-        <v>8.583661048018421</v>
+        <v>8.562112602229398</v>
       </c>
       <c r="U96">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V96">
-        <v>0.03540272172866888</v>
+        <v>0.03798448780086512</v>
       </c>
       <c r="W96">
-        <v>0.2128759879360997</v>
+        <v>0.1978759879360996</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3540272172866888</v>
+        <v>0.3798448780086512</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2303079080470844</v>
+        <v>0.2159807051459087</v>
       </c>
       <c r="C97">
-        <v>-5409.958631306015</v>
+        <v>-5154.506975342045</v>
       </c>
       <c r="D97">
-        <v>4664.986368693986</v>
+        <v>4920.438024657956</v>
       </c>
       <c r="E97">
         <v>9445.845000000001</v>
@@ -9241,37 +9241,37 @@
         <v>1052.8</v>
       </c>
       <c r="M97">
-        <v>3005.418645929643</v>
+        <v>2801.143470929643</v>
       </c>
       <c r="N97">
-        <v>-1952.618645929643</v>
+        <v>-1748.343470929643</v>
       </c>
       <c r="O97">
-        <v>-195.2618645929643</v>
+        <v>-174.8343470929643</v>
       </c>
       <c r="P97">
-        <v>-1757.356781336679</v>
+        <v>-1573.509123836679</v>
       </c>
       <c r="Q97">
-        <v>-532.056781336679</v>
+        <v>-348.2091238366791</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5599517920574206</v>
+        <v>0.5584077340339065</v>
       </c>
       <c r="T97">
-        <v>10.30039325762211</v>
+        <v>10.27453512267528</v>
       </c>
       <c r="U97">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V97">
-        <v>0.03503006149994605</v>
+        <v>0.0375846510871718</v>
       </c>
       <c r="W97">
-        <v>0.2129582299412772</v>
+        <v>0.1979582299412772</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3503006149994605</v>
+        <v>0.3758465108717179</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2320567978313641</v>
+        <v>0.2175795949301884</v>
       </c>
       <c r="C98">
-        <v>-5582.71644849203</v>
+        <v>-5327.774681198867</v>
       </c>
       <c r="D98">
-        <v>4635.579551507969</v>
+        <v>4890.521318801133</v>
       </c>
       <c r="E98">
         <v>9589.196</v>
@@ -9323,37 +9323,37 @@
         <v>1052.8</v>
       </c>
       <c r="M98">
-        <v>3037.054631676271</v>
+        <v>2830.629191676271</v>
       </c>
       <c r="N98">
-        <v>-1984.254631676271</v>
+        <v>-1777.829191676271</v>
       </c>
       <c r="O98">
-        <v>-198.4254631676271</v>
+        <v>-177.7829191676271</v>
       </c>
       <c r="P98">
-        <v>-1785.829168508644</v>
+        <v>-1600.046272508644</v>
       </c>
       <c r="Q98">
-        <v>-560.529168508644</v>
+        <v>-374.7462725086436</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6884897400717743</v>
+        <v>0.6865596675423817</v>
       </c>
       <c r="T98">
-        <v>12.87549157202761</v>
+        <v>12.84316890334407</v>
       </c>
       <c r="U98">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V98">
-        <v>0.03466516502598829</v>
+        <v>0.03719314430501377</v>
       </c>
       <c r="W98">
-        <v>0.213038758571347</v>
+        <v>0.198038758571347</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3466516502598828</v>
+        <v>0.3719314430501376</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2338056876156438</v>
+        <v>0.219178484714468</v>
       </c>
       <c r="C99">
-        <v>-5755.105842811547</v>
+        <v>-5500.680793053625</v>
       </c>
       <c r="D99">
-        <v>4606.541157188453</v>
+        <v>4860.966206946375</v>
       </c>
       <c r="E99">
         <v>9732.547</v>
@@ -9405,37 +9405,37 @@
         <v>1052.8</v>
       </c>
       <c r="M99">
-        <v>3068.690617422899</v>
+        <v>2860.114912422899</v>
       </c>
       <c r="N99">
-        <v>-2015.890617422899</v>
+        <v>-1807.314912422899</v>
       </c>
       <c r="O99">
-        <v>-201.5890617422899</v>
+        <v>-180.7314912422899</v>
       </c>
       <c r="P99">
-        <v>-1814.301555680609</v>
+        <v>-1626.583421180609</v>
       </c>
       <c r="Q99">
-        <v>-589.001555680609</v>
+        <v>-401.2834211806089</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.9027196534290326</v>
+        <v>0.9001462233898422</v>
       </c>
       <c r="T99">
-        <v>17.16732209603681</v>
+        <v>17.12422520445876</v>
       </c>
       <c r="U99">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V99">
-        <v>0.03430779219066882</v>
+        <v>0.03680970982764249</v>
       </c>
       <c r="W99">
-        <v>0.2131176268172915</v>
+        <v>0.1981176268172915</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3430779219066882</v>
+        <v>0.3680970982764249</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2355545773999235</v>
+        <v>0.2207773744987477</v>
       </c>
       <c r="C100">
-        <v>-5927.133694833514</v>
+        <v>-5673.231827238735</v>
       </c>
       <c r="D100">
-        <v>4577.864305166485</v>
+        <v>4831.766172761264</v>
       </c>
       <c r="E100">
         <v>9875.897999999999</v>
@@ -9487,37 +9487,37 @@
         <v>1052.8</v>
       </c>
       <c r="M100">
-        <v>3100.326603169527</v>
+        <v>2889.600633169526</v>
       </c>
       <c r="N100">
-        <v>-2047.526603169527</v>
+        <v>-1836.800633169526</v>
       </c>
       <c r="O100">
-        <v>-204.7526603169527</v>
+        <v>-183.6800633169526</v>
       </c>
       <c r="P100">
-        <v>-1842.773942852574</v>
+        <v>-1653.120569852574</v>
       </c>
       <c r="Q100">
-        <v>-617.4739428525741</v>
+        <v>-427.8205698525737</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.331179480143549</v>
+        <v>1.327319335084763</v>
       </c>
       <c r="T100">
-        <v>25.75098314405522</v>
+        <v>25.68633780668814</v>
       </c>
       <c r="U100">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V100">
-        <v>0.03395771267851914</v>
+        <v>0.03643410054368695</v>
       </c>
       <c r="W100">
-        <v>0.2131948855071964</v>
+        <v>0.1981948855071964</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3395771267851914</v>
+        <v>0.3643410054368695</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2373034671842031</v>
+        <v>0.2223762642830274</v>
       </c>
       <c r="C101">
-        <v>-6098.806714853945</v>
+        <v>-5845.434144445988</v>
       </c>
       <c r="D101">
-        <v>4549.542285146055</v>
+        <v>4802.914855554012</v>
       </c>
       <c r="E101">
         <v>10019.249</v>
@@ -9569,37 +9569,37 @@
         <v>1052.8</v>
       </c>
       <c r="M101">
-        <v>3131.962588916154</v>
+        <v>2919.086353916154</v>
       </c>
       <c r="N101">
-        <v>-2079.162588916154</v>
+        <v>-1866.286353916154</v>
       </c>
       <c r="O101">
-        <v>-207.9162588916154</v>
+        <v>-186.6286353916154</v>
       </c>
       <c r="P101">
-        <v>-1871.246330024539</v>
+        <v>-1679.657718524539</v>
       </c>
       <c r="Q101">
-        <v>-645.9463300245388</v>
+        <v>-454.3577185245388</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.616558960287097</v>
+        <v>2.608838670169527</v>
       </c>
       <c r="T101">
-        <v>51.50196628811043</v>
+        <v>51.37267561337629</v>
       </c>
       <c r="U101">
-        <v>0.2206889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V101">
-        <v>0.03361470547974622</v>
+        <v>0.03606607932607395</v>
       </c>
       <c r="W101">
-        <v>0.213270583415487</v>
+        <v>0.198270583415487</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3361470547974622</v>
+        <v>0.3606607932607395</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/qatar/qatar_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_telecom_services.xlsx
@@ -1133,43 +1133,43 @@
         <v>5.02529832935561</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>133.073872203357</v>
       </c>
       <c r="G2">
         <v>1.83157016812256</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0629256836837716</v>
       </c>
       <c r="I2">
         <v>0.291068775243982</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>10162.6</v>
       </c>
       <c r="L2">
-        <v>14463.446627001</v>
+        <v>14318.9718166338</v>
       </c>
       <c r="M2">
         <v>10791.7</v>
       </c>
       <c r="N2">
-        <v>10920.046627001</v>
+        <v>10918.9228166338</v>
       </c>
       <c r="O2">
         <v>4172.5</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>143.351</v>
       </c>
       <c r="Q2">
         <v>0.073780079274191</v>
       </c>
       <c r="R2">
-        <v>0.0723794158696799</v>
+        <v>0.07239153725966201</v>
       </c>
       <c r="S2">
         <v>0.0532700805851723</v>
@@ -1191,13 +1191,13 @@
         <v>0.082200952823276</v>
       </c>
       <c r="X2">
-        <v>0.0723794158696799</v>
+        <v>0.0726210469230406</v>
       </c>
       <c r="Y2">
         <v>0.729608321237027</v>
       </c>
       <c r="Z2">
-        <v>0.532748774085323</v>
+        <v>0.537591944758826</v>
       </c>
       <c r="AA2">
         <v>4172.5</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07237941586967991</v>
+        <v>0.07239153725966195</v>
       </c>
       <c r="C2">
-        <v>14463.44662700098</v>
+        <v>14318.97181663384</v>
       </c>
       <c r="D2">
-        <v>10920.04662700098</v>
+        <v>10918.92281663384</v>
       </c>
       <c r="E2">
-        <v>-4172.5</v>
+        <v>-4029.149</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>143.351</v>
       </c>
       <c r="G2">
         <v>3543.4</v>
@@ -1451,28 +1451,28 @@
         <v>1052.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>7.911395246627821</v>
       </c>
       <c r="N2">
-        <v>1052.8</v>
+        <v>1044.888604753372</v>
       </c>
       <c r="O2">
-        <v>105.28</v>
+        <v>104.4888604753372</v>
       </c>
       <c r="P2">
-        <v>947.52</v>
+        <v>940.399744278035</v>
       </c>
       <c r="Q2">
-        <v>2172.82</v>
+        <v>2165.699744278035</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07237941586967991</v>
+        <v>0.07262104692304064</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5375919447588259</v>
       </c>
       <c r="U2">
         <v>0.05518897842796926</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>133.0738722033574</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07239153725966195</v>
+        <v>0.07240365864964399</v>
       </c>
       <c r="C3">
-        <v>14318.97181663384</v>
+        <v>14174.49723755138</v>
       </c>
       <c r="D3">
-        <v>10918.92281663384</v>
+        <v>10917.79923755138</v>
       </c>
       <c r="E3">
-        <v>-4029.149</v>
+        <v>-3885.798</v>
       </c>
       <c r="F3">
-        <v>143.351</v>
+        <v>286.702</v>
       </c>
       <c r="G3">
         <v>3543.4</v>
@@ -1533,28 +1533,28 @@
         <v>1052.8</v>
       </c>
       <c r="M3">
-        <v>7.911395246627821</v>
+        <v>15.82279049325564</v>
       </c>
       <c r="N3">
-        <v>1044.888604753372</v>
+        <v>1036.977209506744</v>
       </c>
       <c r="O3">
-        <v>104.4888604753372</v>
+        <v>103.6977209506744</v>
       </c>
       <c r="P3">
-        <v>940.399744278035</v>
+        <v>933.2794885560697</v>
       </c>
       <c r="Q3">
-        <v>2165.699744278035</v>
+        <v>2158.57948855607</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07262104692304064</v>
+        <v>0.07286760922238832</v>
       </c>
       <c r="T3">
-        <v>0.5375919447588259</v>
+        <v>0.5425339556501554</v>
       </c>
       <c r="U3">
         <v>0.05518897842796926</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>133.0738722033574</v>
+        <v>66.53693610167871</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07240365864964399</v>
+        <v>0.07241578003962604</v>
       </c>
       <c r="C4">
-        <v>14174.49723755138</v>
+        <v>14030.02288968222</v>
       </c>
       <c r="D4">
-        <v>10917.79923755138</v>
+        <v>10916.67588968222</v>
       </c>
       <c r="E4">
-        <v>-3885.798</v>
+        <v>-3742.447</v>
       </c>
       <c r="F4">
-        <v>286.702</v>
+        <v>430.053</v>
       </c>
       <c r="G4">
         <v>3543.4</v>
@@ -1615,28 +1615,28 @@
         <v>1052.8</v>
       </c>
       <c r="M4">
-        <v>15.82279049325564</v>
+        <v>23.73418573988346</v>
       </c>
       <c r="N4">
-        <v>1036.977209506744</v>
+        <v>1029.065814260116</v>
       </c>
       <c r="O4">
-        <v>103.6977209506744</v>
+        <v>102.9065814260117</v>
       </c>
       <c r="P4">
-        <v>933.2794885560697</v>
+        <v>926.1592328341048</v>
       </c>
       <c r="Q4">
-        <v>2158.57948855607</v>
+        <v>2151.459232834105</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07286760922238832</v>
+        <v>0.07311925528048543</v>
       </c>
       <c r="T4">
-        <v>0.5425339556501554</v>
+        <v>0.5475778636732649</v>
       </c>
       <c r="U4">
         <v>0.05518897842796926</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>66.53693610167871</v>
+        <v>44.35795740111914</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07241578003962604</v>
+        <v>0.0724279014296081</v>
       </c>
       <c r="C5">
-        <v>14030.02288968222</v>
+        <v>13885.54877295499</v>
       </c>
       <c r="D5">
-        <v>10916.67588968222</v>
+        <v>10915.55277295499</v>
       </c>
       <c r="E5">
-        <v>-3742.447</v>
+        <v>-3599.096</v>
       </c>
       <c r="F5">
-        <v>430.053</v>
+        <v>573.404</v>
       </c>
       <c r="G5">
         <v>3543.4</v>
@@ -1697,28 +1697,28 @@
         <v>1052.8</v>
       </c>
       <c r="M5">
-        <v>23.73418573988346</v>
+        <v>31.64558098651128</v>
       </c>
       <c r="N5">
-        <v>1029.065814260116</v>
+        <v>1021.154419013489</v>
       </c>
       <c r="O5">
-        <v>102.9065814260117</v>
+        <v>102.1154419013489</v>
       </c>
       <c r="P5">
-        <v>926.1592328341048</v>
+        <v>919.0389771121398</v>
       </c>
       <c r="Q5">
-        <v>2151.459232834105</v>
+        <v>2144.33897711214</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07311925528048543</v>
+        <v>0.07337614396479292</v>
       </c>
       <c r="T5">
-        <v>0.5475778636732649</v>
+        <v>0.5527268531135227</v>
       </c>
       <c r="U5">
         <v>0.05518897842796926</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.35795740111914</v>
+        <v>33.26846805083935</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0724279014296081</v>
+        <v>0.07244002281959012</v>
       </c>
       <c r="C6">
-        <v>13885.54877295499</v>
+        <v>13741.07488729837</v>
       </c>
       <c r="D6">
-        <v>10915.55277295499</v>
+        <v>10914.42988729837</v>
       </c>
       <c r="E6">
-        <v>-3599.096</v>
+        <v>-3455.745</v>
       </c>
       <c r="F6">
-        <v>573.404</v>
+        <v>716.7550000000001</v>
       </c>
       <c r="G6">
         <v>3543.4</v>
@@ -1779,28 +1779,28 @@
         <v>1052.8</v>
       </c>
       <c r="M6">
-        <v>31.64558098651128</v>
+        <v>39.55697623313911</v>
       </c>
       <c r="N6">
-        <v>1021.154419013489</v>
+        <v>1013.243023766861</v>
       </c>
       <c r="O6">
-        <v>102.1154419013489</v>
+        <v>101.3243023766861</v>
       </c>
       <c r="P6">
-        <v>919.0389771121398</v>
+        <v>911.9187213901747</v>
       </c>
       <c r="Q6">
-        <v>2144.33897711214</v>
+        <v>2137.218721390175</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07337614396479292</v>
+        <v>0.0736384408319279</v>
       </c>
       <c r="T6">
-        <v>0.5527268531135227</v>
+        <v>0.5579842423314698</v>
       </c>
       <c r="U6">
         <v>0.05518897842796926</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.26846805083935</v>
+        <v>26.61477444067148</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07244002281959012</v>
+        <v>0.07245214420957218</v>
       </c>
       <c r="C7">
-        <v>13741.07488729837</v>
+        <v>13596.60123264103</v>
       </c>
       <c r="D7">
-        <v>10914.42988729837</v>
+        <v>10913.30723264103</v>
       </c>
       <c r="E7">
-        <v>-3455.745</v>
+        <v>-3312.394</v>
       </c>
       <c r="F7">
-        <v>716.7550000000001</v>
+        <v>860.1060000000001</v>
       </c>
       <c r="G7">
         <v>3543.4</v>
@@ -1861,28 +1861,28 @@
         <v>1052.8</v>
       </c>
       <c r="M7">
-        <v>39.55697623313911</v>
+        <v>47.46837147976693</v>
       </c>
       <c r="N7">
-        <v>1013.243023766861</v>
+        <v>1005.331628520233</v>
       </c>
       <c r="O7">
-        <v>101.3243023766861</v>
+        <v>100.5331628520233</v>
       </c>
       <c r="P7">
-        <v>911.9187213901747</v>
+        <v>904.7984656682097</v>
       </c>
       <c r="Q7">
-        <v>2137.218721390175</v>
+        <v>2130.098465668209</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0736384408319279</v>
+        <v>0.07390631848347004</v>
       </c>
       <c r="T7">
-        <v>0.5579842423314698</v>
+        <v>0.5633534908944798</v>
       </c>
       <c r="U7">
         <v>0.05518897842796926</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.61477444067148</v>
+        <v>22.17897870055957</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07245214420957218</v>
+        <v>0.07246426559955421</v>
       </c>
       <c r="C8">
-        <v>13596.60123264103</v>
+        <v>13452.12780891172</v>
       </c>
       <c r="D8">
-        <v>10913.30723264103</v>
+        <v>10912.18480891172</v>
       </c>
       <c r="E8">
-        <v>-3312.394</v>
+        <v>-3169.043</v>
       </c>
       <c r="F8">
-        <v>860.106</v>
+        <v>1003.457</v>
       </c>
       <c r="G8">
         <v>3543.4</v>
@@ -1943,28 +1943,28 @@
         <v>1052.8</v>
       </c>
       <c r="M8">
-        <v>47.46837147976692</v>
+        <v>55.37976672639474</v>
       </c>
       <c r="N8">
-        <v>1005.331628520233</v>
+        <v>997.4202332736052</v>
       </c>
       <c r="O8">
-        <v>100.5331628520233</v>
+        <v>99.74202332736053</v>
       </c>
       <c r="P8">
-        <v>904.7984656682097</v>
+        <v>897.6782099462446</v>
       </c>
       <c r="Q8">
-        <v>2130.098465668209</v>
+        <v>2122.978209946245</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07390631848347004</v>
+        <v>0.07417995694472274</v>
       </c>
       <c r="T8">
-        <v>0.5633534908944798</v>
+        <v>0.5688382071685222</v>
       </c>
       <c r="U8">
         <v>0.05518897842796926</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.17897870055957</v>
+        <v>19.0105531719082</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0724642655995542</v>
+        <v>0.07247638698953625</v>
       </c>
       <c r="C9">
-        <v>13452.12780891172</v>
+        <v>13307.65461603919</v>
       </c>
       <c r="D9">
-        <v>10912.18480891172</v>
+        <v>10911.06261603919</v>
       </c>
       <c r="E9">
-        <v>-3169.043</v>
+        <v>-3025.692</v>
       </c>
       <c r="F9">
-        <v>1003.457</v>
+        <v>1146.808</v>
       </c>
       <c r="G9">
         <v>3543.4</v>
@@ -2025,28 +2025,28 @@
         <v>1052.8</v>
       </c>
       <c r="M9">
-        <v>55.37976672639476</v>
+        <v>63.29116197302257</v>
       </c>
       <c r="N9">
-        <v>997.4202332736052</v>
+        <v>989.5088380269774</v>
       </c>
       <c r="O9">
-        <v>99.74202332736053</v>
+        <v>98.95088380269775</v>
       </c>
       <c r="P9">
-        <v>897.6782099462446</v>
+        <v>890.5579542242797</v>
       </c>
       <c r="Q9">
-        <v>2122.978209946245</v>
+        <v>2115.85795422428</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07417995694472274</v>
+        <v>0.07445954406817659</v>
       </c>
       <c r="T9">
-        <v>0.5688382071685223</v>
+        <v>0.5744421564050439</v>
       </c>
       <c r="U9">
         <v>0.05518897842796926</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.0105531719082</v>
+        <v>16.63423402541968</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07247638698953625</v>
+        <v>0.07248850837951828</v>
       </c>
       <c r="C10">
-        <v>13307.65461603919</v>
+        <v>13163.18165395222</v>
       </c>
       <c r="D10">
-        <v>10911.06261603919</v>
+        <v>10909.94065395222</v>
       </c>
       <c r="E10">
-        <v>-3025.692</v>
+        <v>-2882.341</v>
       </c>
       <c r="F10">
-        <v>1146.808</v>
+        <v>1290.159</v>
       </c>
       <c r="G10">
         <v>3543.4</v>
@@ -2107,28 +2107,28 @@
         <v>1052.8</v>
       </c>
       <c r="M10">
-        <v>63.29116197302257</v>
+        <v>71.20255721965039</v>
       </c>
       <c r="N10">
-        <v>989.5088380269774</v>
+        <v>981.5974427803495</v>
       </c>
       <c r="O10">
-        <v>98.95088380269775</v>
+        <v>98.15974427803496</v>
       </c>
       <c r="P10">
-        <v>890.5579542242797</v>
+        <v>883.4376985023146</v>
       </c>
       <c r="Q10">
-        <v>2115.85795422428</v>
+        <v>2108.737698502315</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07445954406817659</v>
+        <v>0.07474527596357448</v>
       </c>
       <c r="T10">
-        <v>0.5744421564050439</v>
+        <v>0.5801692693610494</v>
       </c>
       <c r="U10">
         <v>0.05518897842796926</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.63423402541968</v>
+        <v>14.78598580037305</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07248850837951828</v>
+        <v>0.07250062976950034</v>
       </c>
       <c r="C11">
-        <v>13163.18165395222</v>
+        <v>13018.70892257962</v>
       </c>
       <c r="D11">
-        <v>10909.94065395222</v>
+        <v>10908.81892257962</v>
       </c>
       <c r="E11">
-        <v>-2882.341</v>
+        <v>-2738.99</v>
       </c>
       <c r="F11">
-        <v>1290.159</v>
+        <v>1433.51</v>
       </c>
       <c r="G11">
         <v>3543.4</v>
@@ -2189,28 +2189,28 @@
         <v>1052.8</v>
       </c>
       <c r="M11">
-        <v>71.20255721965039</v>
+        <v>79.11395246627821</v>
       </c>
       <c r="N11">
-        <v>981.5974427803495</v>
+        <v>973.6860475337218</v>
       </c>
       <c r="O11">
-        <v>98.15974427803496</v>
+        <v>97.36860475337218</v>
       </c>
       <c r="P11">
-        <v>883.4376985023146</v>
+        <v>876.3174427803496</v>
       </c>
       <c r="Q11">
-        <v>2108.737698502315</v>
+        <v>2101.617442780349</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07474527596357448</v>
+        <v>0.0750373574566479</v>
       </c>
       <c r="T11">
-        <v>0.5801692693610494</v>
+        <v>0.5860236514938553</v>
       </c>
       <c r="U11">
         <v>0.05518897842796926</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.78598580037305</v>
+        <v>13.30738722033574</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07250062976950034</v>
+        <v>0.0725127511594824</v>
       </c>
       <c r="C12">
-        <v>13018.70892257962</v>
+        <v>12874.23642185024</v>
       </c>
       <c r="D12">
-        <v>10908.81892257962</v>
+        <v>10907.69742185025</v>
       </c>
       <c r="E12">
-        <v>-2738.99</v>
+        <v>-2595.639</v>
       </c>
       <c r="F12">
-        <v>1433.51</v>
+        <v>1576.861</v>
       </c>
       <c r="G12">
         <v>3543.4</v>
@@ -2271,28 +2271,28 @@
         <v>1052.8</v>
       </c>
       <c r="M12">
-        <v>79.11395246627822</v>
+        <v>87.02534771290604</v>
       </c>
       <c r="N12">
-        <v>973.6860475337218</v>
+        <v>965.7746522870939</v>
       </c>
       <c r="O12">
-        <v>97.36860475337218</v>
+        <v>96.5774652287094</v>
       </c>
       <c r="P12">
-        <v>876.3174427803496</v>
+        <v>869.1971870583845</v>
       </c>
       <c r="Q12">
-        <v>2101.617442780349</v>
+        <v>2094.497187058384</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0750373574566479</v>
+        <v>0.07533600257877913</v>
       </c>
       <c r="T12">
-        <v>0.5860236514938553</v>
+        <v>0.5920095927757127</v>
       </c>
       <c r="U12">
         <v>0.05518897842796926</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>13.30738722033574</v>
+        <v>12.09762474575976</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0725127511594824</v>
+        <v>0.07252487254946444</v>
       </c>
       <c r="C13">
-        <v>12874.23642185024</v>
+        <v>12729.76415169296</v>
       </c>
       <c r="D13">
-        <v>10907.69742185025</v>
+        <v>10906.57615169296</v>
       </c>
       <c r="E13">
-        <v>-2595.639</v>
+        <v>-2452.288</v>
       </c>
       <c r="F13">
-        <v>1576.861</v>
+        <v>1720.212</v>
       </c>
       <c r="G13">
         <v>3543.4</v>
@@ -2353,28 +2353,28 @@
         <v>1052.8</v>
       </c>
       <c r="M13">
-        <v>87.02534771290604</v>
+        <v>94.93674295953385</v>
       </c>
       <c r="N13">
-        <v>965.7746522870939</v>
+        <v>957.8632570404661</v>
       </c>
       <c r="O13">
-        <v>96.5774652287094</v>
+        <v>95.78632570404662</v>
       </c>
       <c r="P13">
-        <v>869.1971870583845</v>
+        <v>862.0769313364195</v>
       </c>
       <c r="Q13">
-        <v>2094.497187058384</v>
+        <v>2087.37693133642</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07533600257877913</v>
+        <v>0.07564143509004972</v>
       </c>
       <c r="T13">
-        <v>0.5920095927757127</v>
+        <v>0.5981315781776126</v>
       </c>
       <c r="U13">
         <v>0.05518897842796926</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.09762474575976</v>
+        <v>11.08948935027979</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07252487254946444</v>
+        <v>0.07253699393944649</v>
       </c>
       <c r="C14">
-        <v>12729.76415169296</v>
+        <v>12585.29211203666</v>
       </c>
       <c r="D14">
-        <v>10906.57615169296</v>
+        <v>10905.45511203666</v>
       </c>
       <c r="E14">
-        <v>-2452.288</v>
+        <v>-2308.937</v>
       </c>
       <c r="F14">
-        <v>1720.212</v>
+        <v>1863.563</v>
       </c>
       <c r="G14">
         <v>3543.4</v>
@@ -2435,28 +2435,28 @@
         <v>1052.8</v>
       </c>
       <c r="M14">
-        <v>94.93674295953385</v>
+        <v>102.8481382061617</v>
       </c>
       <c r="N14">
-        <v>957.8632570404661</v>
+        <v>949.9518617938382</v>
       </c>
       <c r="O14">
-        <v>95.78632570404662</v>
+        <v>94.99518617938384</v>
       </c>
       <c r="P14">
-        <v>862.0769313364195</v>
+        <v>854.9566756144544</v>
       </c>
       <c r="Q14">
-        <v>2087.37693133642</v>
+        <v>2080.256675614454</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07564143509004972</v>
+        <v>0.07595388903836101</v>
       </c>
       <c r="T14">
-        <v>0.5981315781776126</v>
+        <v>0.6043942988761077</v>
       </c>
       <c r="U14">
         <v>0.05518897842796926</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.08948935027979</v>
+        <v>10.23645170795057</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07253699393944649</v>
+        <v>0.07254911532942852</v>
       </c>
       <c r="C15">
-        <v>12585.29211203666</v>
+        <v>12440.82030281029</v>
       </c>
       <c r="D15">
-        <v>10905.45511203666</v>
+        <v>10904.33430281029</v>
       </c>
       <c r="E15">
-        <v>-2308.937</v>
+        <v>-2165.586</v>
       </c>
       <c r="F15">
-        <v>1863.563</v>
+        <v>2006.914</v>
       </c>
       <c r="G15">
         <v>3543.4</v>
@@ -2517,28 +2517,28 @@
         <v>1052.8</v>
       </c>
       <c r="M15">
-        <v>102.8481382061617</v>
+        <v>110.7595334527895</v>
       </c>
       <c r="N15">
-        <v>949.9518617938382</v>
+        <v>942.0404665472105</v>
       </c>
       <c r="O15">
-        <v>94.99518617938384</v>
+        <v>94.20404665472105</v>
       </c>
       <c r="P15">
-        <v>854.9566756144544</v>
+        <v>847.8364198924894</v>
       </c>
       <c r="Q15">
-        <v>2080.256675614454</v>
+        <v>2073.136419892489</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07595388903836101</v>
+        <v>0.07627360935756325</v>
       </c>
       <c r="T15">
-        <v>0.6043942988761077</v>
+        <v>0.6108026642420098</v>
       </c>
       <c r="U15">
         <v>0.05518897842796926</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.23645170795057</v>
+        <v>9.5052765859541</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07254911532942852</v>
+        <v>0.07256123671941056</v>
       </c>
       <c r="C16">
-        <v>12440.82030281029</v>
+        <v>12296.3487239428</v>
       </c>
       <c r="D16">
-        <v>10904.33430281029</v>
+        <v>10903.2137239428</v>
       </c>
       <c r="E16">
-        <v>-2165.586</v>
+        <v>-2022.235</v>
       </c>
       <c r="F16">
-        <v>2006.914</v>
+        <v>2150.265</v>
       </c>
       <c r="G16">
         <v>3543.4</v>
@@ -2599,28 +2599,28 @@
         <v>1052.8</v>
       </c>
       <c r="M16">
-        <v>110.7595334527895</v>
+        <v>118.6709286994173</v>
       </c>
       <c r="N16">
-        <v>942.0404665472105</v>
+        <v>934.1290713005826</v>
       </c>
       <c r="O16">
-        <v>94.20404665472105</v>
+        <v>93.41290713005827</v>
       </c>
       <c r="P16">
-        <v>847.8364198924894</v>
+        <v>840.7161641705243</v>
       </c>
       <c r="Q16">
-        <v>2073.136419892489</v>
+        <v>2066.016164170524</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07627360935756325</v>
+        <v>0.07660085250780554</v>
       </c>
       <c r="T16">
-        <v>0.6108026642420098</v>
+        <v>0.6173618146753449</v>
       </c>
       <c r="U16">
         <v>0.05518897842796926</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.5052765859541</v>
+        <v>8.871591480223827</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07256123671941056</v>
+        <v>0.0727893581093926</v>
       </c>
       <c r="C17">
-        <v>12296.3487239428</v>
+        <v>12131.95159311831</v>
       </c>
       <c r="D17">
-        <v>10903.2137239428</v>
+        <v>10882.16759311831</v>
       </c>
       <c r="E17">
-        <v>-2022.235</v>
+        <v>-1878.884</v>
       </c>
       <c r="F17">
-        <v>2150.265</v>
+        <v>2293.616</v>
       </c>
       <c r="G17">
         <v>3543.4</v>
@@ -2681,45 +2681,45 @@
         <v>1052.8</v>
       </c>
       <c r="M17">
-        <v>118.6709286994173</v>
+        <v>130.0227479460451</v>
       </c>
       <c r="N17">
-        <v>934.1290713005826</v>
+        <v>922.7772520539548</v>
       </c>
       <c r="O17">
-        <v>93.41290713005827</v>
+        <v>92.27772520539548</v>
       </c>
       <c r="P17">
-        <v>840.7161641705243</v>
+        <v>830.4995268485593</v>
       </c>
       <c r="Q17">
-        <v>2066.016164170524</v>
+        <v>2055.799526848559</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07660085250780554</v>
+        <v>0.07693588716162504</v>
       </c>
       <c r="T17">
-        <v>0.6173618146753449</v>
+        <v>0.6240771353570926</v>
       </c>
       <c r="U17">
-        <v>0.05518897842796926</v>
+        <v>0.05668897842796925</v>
       </c>
       <c r="V17">
         <v>0.1</v>
       </c>
       <c r="W17">
-        <v>0.04967008058517233</v>
+        <v>0.05102008058517233</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>8.871591480223827</v>
+        <v>8.09704468357241</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0727893581093926</v>
+        <v>0.07281497949937464</v>
       </c>
       <c r="C18">
-        <v>12131.95159311831</v>
+        <v>11986.24187694724</v>
       </c>
       <c r="D18">
-        <v>10882.16759311831</v>
+        <v>10879.80887694724</v>
       </c>
       <c r="E18">
-        <v>-1878.884</v>
+        <v>-1735.533</v>
       </c>
       <c r="F18">
-        <v>2293.616</v>
+        <v>2436.967</v>
       </c>
       <c r="G18">
         <v>3543.4</v>
@@ -2763,28 +2763,28 @@
         <v>1052.8</v>
       </c>
       <c r="M18">
-        <v>130.0227479460451</v>
+        <v>138.149169692673</v>
       </c>
       <c r="N18">
-        <v>922.7772520539548</v>
+        <v>914.6508303073269</v>
       </c>
       <c r="O18">
-        <v>92.27772520539548</v>
+        <v>91.4650830307327</v>
       </c>
       <c r="P18">
-        <v>830.4995268485593</v>
+        <v>823.1857472765943</v>
       </c>
       <c r="Q18">
-        <v>2055.799526848559</v>
+        <v>2048.485747276594</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07693588716162504</v>
+        <v>0.07727899493963294</v>
       </c>
       <c r="T18">
-        <v>0.6240771353570926</v>
+        <v>0.6309542709950271</v>
       </c>
       <c r="U18">
         <v>0.05668897842796925</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.09704468357241</v>
+        <v>7.620747937479913</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07281497949937464</v>
+        <v>0.07284060088935669</v>
       </c>
       <c r="C19">
-        <v>11986.24187694724</v>
+        <v>11840.5331830608</v>
       </c>
       <c r="D19">
-        <v>10879.80887694724</v>
+        <v>10877.4511830608</v>
       </c>
       <c r="E19">
-        <v>-1735.533</v>
+        <v>-1592.182</v>
       </c>
       <c r="F19">
-        <v>2436.967</v>
+        <v>2580.318</v>
       </c>
       <c r="G19">
         <v>3543.4</v>
@@ -2845,28 +2845,28 @@
         <v>1052.8</v>
       </c>
       <c r="M19">
-        <v>138.149169692673</v>
+        <v>146.2755914393008</v>
       </c>
       <c r="N19">
-        <v>914.6508303073269</v>
+        <v>906.5244085606992</v>
       </c>
       <c r="O19">
-        <v>91.4650830307327</v>
+        <v>90.65244085606992</v>
       </c>
       <c r="P19">
-        <v>823.1857472765943</v>
+        <v>815.8719677046292</v>
       </c>
       <c r="Q19">
-        <v>2048.485747276594</v>
+        <v>2041.171967704629</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07727899493963294</v>
+        <v>0.0776304712000313</v>
       </c>
       <c r="T19">
-        <v>0.6309542709950271</v>
+        <v>0.6379991416485209</v>
       </c>
       <c r="U19">
         <v>0.05668897842796925</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.620747937479913</v>
+        <v>7.197373052064362</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07284060088935669</v>
+        <v>0.07286622227933874</v>
       </c>
       <c r="C20">
-        <v>11840.5331830608</v>
+        <v>11694.82551079454</v>
       </c>
       <c r="D20">
-        <v>10877.4511830608</v>
+        <v>10875.09451079454</v>
       </c>
       <c r="E20">
-        <v>-1592.182</v>
+        <v>-1448.831</v>
       </c>
       <c r="F20">
-        <v>2580.318</v>
+        <v>2723.669</v>
       </c>
       <c r="G20">
         <v>3543.4</v>
@@ -2927,28 +2927,28 @@
         <v>1052.8</v>
       </c>
       <c r="M20">
-        <v>146.2755914393007</v>
+        <v>154.4020131859286</v>
       </c>
       <c r="N20">
-        <v>906.5244085606992</v>
+        <v>898.3979868140714</v>
       </c>
       <c r="O20">
-        <v>90.65244085606992</v>
+        <v>89.83979868140715</v>
       </c>
       <c r="P20">
-        <v>815.8719677046292</v>
+        <v>808.5581881326642</v>
       </c>
       <c r="Q20">
-        <v>2041.171967704629</v>
+        <v>2033.858188132664</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0776304712000313</v>
+        <v>0.07799062588661233</v>
       </c>
       <c r="T20">
-        <v>0.6379991416485209</v>
+        <v>0.6452179597255577</v>
       </c>
       <c r="U20">
         <v>0.05668897842796925</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.197373052064364</v>
+        <v>6.818563944060974</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07286622227933874</v>
+        <v>0.07319784366932076</v>
       </c>
       <c r="C21">
-        <v>11694.82551079454</v>
+        <v>11521.06364504187</v>
       </c>
       <c r="D21">
-        <v>10875.09451079454</v>
+        <v>10844.68364504187</v>
       </c>
       <c r="E21">
-        <v>-1448.831</v>
+        <v>-1305.48</v>
       </c>
       <c r="F21">
-        <v>2723.669</v>
+        <v>2867.02</v>
       </c>
       <c r="G21">
         <v>3543.4</v>
@@ -3009,45 +3009,45 @@
         <v>1052.8</v>
       </c>
       <c r="M21">
-        <v>154.4020131859286</v>
+        <v>167.4023689325564</v>
       </c>
       <c r="N21">
-        <v>898.3979868140714</v>
+        <v>885.3976310674435</v>
       </c>
       <c r="O21">
-        <v>89.83979868140715</v>
+        <v>88.53976310674436</v>
       </c>
       <c r="P21">
-        <v>808.5581881326642</v>
+        <v>796.8578679606992</v>
       </c>
       <c r="Q21">
-        <v>2033.858188132664</v>
+        <v>2022.157867960699</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07799062588661233</v>
+        <v>0.07835978444035788</v>
       </c>
       <c r="T21">
-        <v>0.6452179597255577</v>
+        <v>0.6526172482545206</v>
       </c>
       <c r="U21">
-        <v>0.05668897842796925</v>
+        <v>0.05838897842796925</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.05102008058517233</v>
+        <v>0.05255008058517233</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.818563944060974</v>
+        <v>6.289038839254151</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07319784366932076</v>
+        <v>0.07323876505930282</v>
       </c>
       <c r="C22">
-        <v>11521.06364504187</v>
+        <v>11373.97179207683</v>
       </c>
       <c r="D22">
-        <v>10844.68364504187</v>
+        <v>10840.94279207683</v>
       </c>
       <c r="E22">
-        <v>-1305.48</v>
+        <v>-1162.128999999999</v>
       </c>
       <c r="F22">
-        <v>2867.02</v>
+        <v>3010.371000000001</v>
       </c>
       <c r="G22">
         <v>3543.4</v>
@@ -3091,28 +3091,28 @@
         <v>1052.8</v>
       </c>
       <c r="M22">
-        <v>167.4023689325564</v>
+        <v>175.7724873791842</v>
       </c>
       <c r="N22">
-        <v>885.3976310674435</v>
+        <v>877.0275126208157</v>
       </c>
       <c r="O22">
-        <v>88.53976310674436</v>
+        <v>87.70275126208158</v>
       </c>
       <c r="P22">
-        <v>796.8578679606992</v>
+        <v>789.3247613587341</v>
       </c>
       <c r="Q22">
-        <v>2022.157867960699</v>
+        <v>2014.624761358734</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07835978444035788</v>
+        <v>0.07873828878027421</v>
       </c>
       <c r="T22">
-        <v>0.6526172482545206</v>
+        <v>0.6602038605437103</v>
       </c>
       <c r="U22">
         <v>0.05838897842796925</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.289038839254151</v>
+        <v>5.989560799289669</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07323876505930282</v>
+        <v>0.07327968644928487</v>
       </c>
       <c r="C23">
-        <v>11373.97179207683</v>
+        <v>11226.88251902207</v>
       </c>
       <c r="D23">
-        <v>10840.94279207683</v>
+        <v>10837.20451902207</v>
       </c>
       <c r="E23">
-        <v>-1162.129</v>
+        <v>-1018.778</v>
       </c>
       <c r="F23">
-        <v>3010.371</v>
+        <v>3153.722</v>
       </c>
       <c r="G23">
         <v>3543.4</v>
@@ -3173,28 +3173,28 @@
         <v>1052.8</v>
       </c>
       <c r="M23">
-        <v>175.7724873791842</v>
+        <v>184.1426058258121</v>
       </c>
       <c r="N23">
-        <v>877.0275126208157</v>
+        <v>868.6573941741879</v>
       </c>
       <c r="O23">
-        <v>87.70275126208158</v>
+        <v>86.86573941741879</v>
       </c>
       <c r="P23">
-        <v>789.3247613587341</v>
+        <v>781.791654756769</v>
       </c>
       <c r="Q23">
-        <v>2014.624761358734</v>
+        <v>2007.091654756769</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07873828878027421</v>
+        <v>0.07912649835967558</v>
       </c>
       <c r="T23">
-        <v>0.6602038605437103</v>
+        <v>0.6679850013531357</v>
       </c>
       <c r="U23">
         <v>0.05838897842796925</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.989560799289669</v>
+        <v>5.717308035685592</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07327968644928487</v>
+        <v>0.0734862078392669</v>
       </c>
       <c r="C24">
-        <v>11226.88251902207</v>
+        <v>11064.70453459964</v>
       </c>
       <c r="D24">
-        <v>10837.20451902207</v>
+        <v>10818.37753459964</v>
       </c>
       <c r="E24">
-        <v>-1018.778</v>
+        <v>-875.4269999999997</v>
       </c>
       <c r="F24">
-        <v>3153.722</v>
+        <v>3297.073</v>
       </c>
       <c r="G24">
         <v>3543.4</v>
@@ -3255,45 +3255,45 @@
         <v>1052.8</v>
       </c>
       <c r="M24">
-        <v>184.1426058258121</v>
+        <v>195.1503826724399</v>
       </c>
       <c r="N24">
-        <v>868.6573941741879</v>
+        <v>857.64961732756</v>
       </c>
       <c r="O24">
-        <v>86.86573941741879</v>
+        <v>85.76496173275601</v>
       </c>
       <c r="P24">
-        <v>781.791654756769</v>
+        <v>771.884655594804</v>
       </c>
       <c r="Q24">
-        <v>2007.091654756769</v>
+        <v>1997.184655594804</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07912649835967558</v>
+        <v>0.07952479130477567</v>
       </c>
       <c r="T24">
-        <v>0.6679850013531357</v>
+        <v>0.6759682497160526</v>
       </c>
       <c r="U24">
-        <v>0.05838897842796925</v>
+        <v>0.05918897842796925</v>
       </c>
       <c r="V24">
         <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.05255008058517233</v>
+        <v>0.05327008058517233</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>5.717308035685592</v>
+        <v>5.394813915210844</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0734862078392669</v>
+        <v>0.07353432922924896</v>
       </c>
       <c r="C25">
-        <v>11064.70453459964</v>
+        <v>10916.97606654141</v>
       </c>
       <c r="D25">
-        <v>10818.37753459964</v>
+        <v>10814.00006654141</v>
       </c>
       <c r="E25">
-        <v>-875.4269999999997</v>
+        <v>-732.0759999999996</v>
       </c>
       <c r="F25">
-        <v>3297.073</v>
+        <v>3440.424</v>
       </c>
       <c r="G25">
         <v>3543.4</v>
@@ -3337,28 +3337,28 @@
         <v>1052.8</v>
       </c>
       <c r="M25">
-        <v>195.1503826724399</v>
+        <v>203.6351819190677</v>
       </c>
       <c r="N25">
-        <v>857.64961732756</v>
+        <v>849.1648180809323</v>
       </c>
       <c r="O25">
-        <v>85.76496173275601</v>
+        <v>84.91648180809324</v>
       </c>
       <c r="P25">
-        <v>771.884655594804</v>
+        <v>764.248336272839</v>
       </c>
       <c r="Q25">
-        <v>1997.184655594804</v>
+        <v>1989.548336272839</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07952479130477567</v>
+        <v>0.07993356564316789</v>
       </c>
       <c r="T25">
-        <v>0.6759682497160526</v>
+        <v>0.6841615835622042</v>
       </c>
       <c r="U25">
         <v>0.05918897842796925</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.394813915210844</v>
+        <v>5.170030002077059</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07353432922924896</v>
+        <v>0.07358245061923099</v>
       </c>
       <c r="C26">
-        <v>10916.97606654141</v>
+        <v>10769.25113958277</v>
       </c>
       <c r="D26">
-        <v>10814.00006654141</v>
+        <v>10809.62613958277</v>
       </c>
       <c r="E26">
-        <v>-732.076</v>
+        <v>-588.7249999999999</v>
       </c>
       <c r="F26">
-        <v>3440.424</v>
+        <v>3583.775</v>
       </c>
       <c r="G26">
         <v>3543.4</v>
@@ -3419,28 +3419,28 @@
         <v>1052.8</v>
       </c>
       <c r="M26">
-        <v>203.6351819190677</v>
+        <v>212.1199811656955</v>
       </c>
       <c r="N26">
-        <v>849.1648180809323</v>
+        <v>840.6800188343044</v>
       </c>
       <c r="O26">
-        <v>84.91648180809324</v>
+        <v>84.06800188343044</v>
       </c>
       <c r="P26">
-        <v>764.248336272839</v>
+        <v>756.612016950874</v>
       </c>
       <c r="Q26">
-        <v>1989.548336272839</v>
+        <v>1981.912016950874</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07993356564316789</v>
+        <v>0.08035324063058388</v>
       </c>
       <c r="T26">
-        <v>0.6841615835622042</v>
+        <v>0.6925734063109199</v>
       </c>
       <c r="U26">
         <v>0.05918897842796925</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.17003000207706</v>
+        <v>4.963228801993977</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07358245061923099</v>
+        <v>0.07363057200921304</v>
       </c>
       <c r="C27">
-        <v>10769.25113958277</v>
+        <v>10621.52974942864</v>
       </c>
       <c r="D27">
-        <v>10809.62613958277</v>
+        <v>10805.25574942864</v>
       </c>
       <c r="E27">
-        <v>-588.7249999999999</v>
+        <v>-445.3739999999998</v>
       </c>
       <c r="F27">
-        <v>3583.775</v>
+        <v>3727.126</v>
       </c>
       <c r="G27">
         <v>3543.4</v>
@@ -3501,28 +3501,28 @@
         <v>1052.8</v>
       </c>
       <c r="M27">
-        <v>212.1199811656955</v>
+        <v>220.6047804123234</v>
       </c>
       <c r="N27">
-        <v>840.6800188343044</v>
+        <v>832.1952195876765</v>
       </c>
       <c r="O27">
-        <v>84.06800188343044</v>
+        <v>83.21952195876766</v>
       </c>
       <c r="P27">
-        <v>756.612016950874</v>
+        <v>748.9756976289088</v>
       </c>
       <c r="Q27">
-        <v>1981.912016950874</v>
+        <v>1974.275697628909</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08035324063058388</v>
+        <v>0.08078425818522733</v>
       </c>
       <c r="T27">
-        <v>0.6925734063109199</v>
+        <v>0.7012125756204116</v>
       </c>
       <c r="U27">
         <v>0.05918897842796925</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.963228801993977</v>
+        <v>4.77233538653267</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07363057200921304</v>
+        <v>0.07367869339919508</v>
       </c>
       <c r="C28">
-        <v>10621.52974942864</v>
+        <v>10473.81189179093</v>
       </c>
       <c r="D28">
-        <v>10805.25574942864</v>
+        <v>10800.88889179093</v>
       </c>
       <c r="E28">
-        <v>-445.3739999999998</v>
+        <v>-302.0229999999997</v>
       </c>
       <c r="F28">
-        <v>3727.126</v>
+        <v>3870.477</v>
       </c>
       <c r="G28">
         <v>3543.4</v>
@@ -3583,28 +3583,28 @@
         <v>1052.8</v>
       </c>
       <c r="M28">
-        <v>220.6047804123234</v>
+        <v>229.0895796589512</v>
       </c>
       <c r="N28">
-        <v>832.1952195876765</v>
+        <v>823.7104203410488</v>
       </c>
       <c r="O28">
-        <v>83.21952195876766</v>
+        <v>82.37104203410489</v>
       </c>
       <c r="P28">
-        <v>748.9756976289088</v>
+        <v>741.3393783069439</v>
       </c>
       <c r="Q28">
-        <v>1974.275697628909</v>
+        <v>1966.639378306944</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08078425818522733</v>
+        <v>0.08122708443999802</v>
       </c>
       <c r="T28">
-        <v>0.7012125756204116</v>
+        <v>0.7100884345000265</v>
       </c>
       <c r="U28">
         <v>0.05918897842796925</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.77233538653267</v>
+        <v>4.595582224068497</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07367869339919508</v>
+        <v>0.07372681478917713</v>
       </c>
       <c r="C29">
-        <v>10473.81189179093</v>
+        <v>10326.09756238844</v>
       </c>
       <c r="D29">
-        <v>10800.88889179093</v>
+        <v>10796.52556238844</v>
       </c>
       <c r="E29">
-        <v>-302.0229999999997</v>
+        <v>-158.6719999999996</v>
       </c>
       <c r="F29">
-        <v>3870.477</v>
+        <v>4013.828</v>
       </c>
       <c r="G29">
         <v>3543.4</v>
@@ -3665,28 +3665,28 @@
         <v>1052.8</v>
       </c>
       <c r="M29">
-        <v>229.0895796589512</v>
+        <v>237.574378905579</v>
       </c>
       <c r="N29">
-        <v>823.7104203410488</v>
+        <v>815.2256210944209</v>
       </c>
       <c r="O29">
-        <v>82.37104203410489</v>
+        <v>81.52256210944211</v>
       </c>
       <c r="P29">
-        <v>741.3393783069439</v>
+        <v>733.7030589849788</v>
       </c>
       <c r="Q29">
-        <v>1966.639378306944</v>
+        <v>1959.003058984979</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08122708443999802</v>
+        <v>0.08168221142406788</v>
       </c>
       <c r="T29">
-        <v>0.7100884345000265</v>
+        <v>0.7192108450151861</v>
       </c>
       <c r="U29">
         <v>0.05918897842796925</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.595582224068497</v>
+        <v>4.431454287494622</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07372681478917713</v>
+        <v>0.07377493617915917</v>
       </c>
       <c r="C30">
-        <v>10326.09756238844</v>
+        <v>10178.38675694691</v>
       </c>
       <c r="D30">
-        <v>10796.52556238844</v>
+        <v>10792.16575694691</v>
       </c>
       <c r="E30">
-        <v>-158.6719999999996</v>
+        <v>-15.320999999999</v>
       </c>
       <c r="F30">
-        <v>4013.828</v>
+        <v>4157.179000000001</v>
       </c>
       <c r="G30">
         <v>3543.4</v>
@@ -3747,28 +3747,28 @@
         <v>1052.8</v>
       </c>
       <c r="M30">
-        <v>237.574378905579</v>
+        <v>246.0591781522068</v>
       </c>
       <c r="N30">
-        <v>815.2256210944209</v>
+        <v>806.7408218477931</v>
       </c>
       <c r="O30">
-        <v>81.52256210944211</v>
+        <v>80.67408218477931</v>
       </c>
       <c r="P30">
-        <v>733.7030589849788</v>
+        <v>726.0667396630138</v>
       </c>
       <c r="Q30">
-        <v>1959.003058984979</v>
+        <v>1951.366739663014</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08168221142406788</v>
+        <v>0.08215015888656224</v>
       </c>
       <c r="T30">
-        <v>0.7192108450151861</v>
+        <v>0.7285902248406319</v>
       </c>
       <c r="U30">
         <v>0.05918897842796925</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.431454287494622</v>
+        <v>4.278645518960325</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07377493617915916</v>
+        <v>0.0740930575691412</v>
       </c>
       <c r="C31">
-        <v>10178.38675694691</v>
+        <v>10006.30225356264</v>
       </c>
       <c r="D31">
-        <v>10792.16575694691</v>
+        <v>10763.43225356264</v>
       </c>
       <c r="E31">
-        <v>-15.32099999999991</v>
+        <v>128.0299999999997</v>
       </c>
       <c r="F31">
-        <v>4157.179</v>
+        <v>4300.53</v>
       </c>
       <c r="G31">
         <v>3543.4</v>
@@ -3829,45 +3829,45 @@
         <v>1052.8</v>
       </c>
       <c r="M31">
-        <v>246.0591781522068</v>
+        <v>258.8445073988346</v>
       </c>
       <c r="N31">
-        <v>806.7408218477931</v>
+        <v>793.9554926011654</v>
       </c>
       <c r="O31">
-        <v>80.67408218477931</v>
+        <v>79.39554926011654</v>
       </c>
       <c r="P31">
-        <v>726.0667396630138</v>
+        <v>714.5599433410488</v>
       </c>
       <c r="Q31">
-        <v>1951.366739663014</v>
+        <v>1939.859943341049</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08215015888656224</v>
+        <v>0.08263147627655644</v>
       </c>
       <c r="T31">
-        <v>0.7285902248406317</v>
+        <v>0.7382375869468046</v>
       </c>
       <c r="U31">
-        <v>0.05918897842796925</v>
+        <v>0.06018897842796925</v>
       </c>
       <c r="V31">
         <v>0.1</v>
       </c>
       <c r="W31">
-        <v>0.05327008058517233</v>
+        <v>0.05417008058517233</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.278645518960325</v>
+        <v>4.067306703084943</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0740930575691412</v>
+        <v>0.07415017895912325</v>
       </c>
       <c r="C32">
-        <v>10006.30225356264</v>
+        <v>9857.808104865635</v>
       </c>
       <c r="D32">
-        <v>10763.43225356264</v>
+        <v>10758.28910486563</v>
       </c>
       <c r="E32">
-        <v>128.0299999999997</v>
+        <v>271.3810000000003</v>
       </c>
       <c r="F32">
-        <v>4300.53</v>
+        <v>4443.881</v>
       </c>
       <c r="G32">
         <v>3543.4</v>
@@ -3911,28 +3911,28 @@
         <v>1052.8</v>
       </c>
       <c r="M32">
-        <v>258.8445073988346</v>
+        <v>267.4726576454624</v>
       </c>
       <c r="N32">
-        <v>793.9554926011654</v>
+        <v>785.3273423545374</v>
       </c>
       <c r="O32">
-        <v>79.39554926011654</v>
+        <v>78.53273423545374</v>
       </c>
       <c r="P32">
-        <v>714.5599433410488</v>
+        <v>706.7946081190837</v>
       </c>
       <c r="Q32">
-        <v>1939.859943341049</v>
+        <v>1932.094608119084</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08263147627655644</v>
+        <v>0.08312674489524613</v>
       </c>
       <c r="T32">
-        <v>0.7382375869468046</v>
+        <v>0.7481645827372144</v>
       </c>
       <c r="U32">
         <v>0.06018897842796925</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.067306703084943</v>
+        <v>3.936103261049944</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07415017895912325</v>
+        <v>0.07420730034910529</v>
       </c>
       <c r="C33">
-        <v>9857.808104865635</v>
+        <v>9709.318868977896</v>
       </c>
       <c r="D33">
-        <v>10758.28910486563</v>
+        <v>10753.1508689779</v>
       </c>
       <c r="E33">
-        <v>271.3810000000003</v>
+        <v>414.732</v>
       </c>
       <c r="F33">
-        <v>4443.881</v>
+        <v>4587.232</v>
       </c>
       <c r="G33">
         <v>3543.4</v>
@@ -3993,28 +3993,28 @@
         <v>1052.8</v>
       </c>
       <c r="M33">
-        <v>267.4726576454624</v>
+        <v>276.1008078920902</v>
       </c>
       <c r="N33">
-        <v>785.3273423545374</v>
+        <v>776.6991921079098</v>
       </c>
       <c r="O33">
-        <v>78.53273423545374</v>
+        <v>77.66991921079098</v>
       </c>
       <c r="P33">
-        <v>706.7946081190837</v>
+        <v>699.0292728971187</v>
       </c>
       <c r="Q33">
-        <v>1932.094608119084</v>
+        <v>1924.329272897119</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08312674489524613</v>
+        <v>0.08363658023801493</v>
       </c>
       <c r="T33">
-        <v>0.7481645827372144</v>
+        <v>0.758383548992048</v>
       </c>
       <c r="U33">
         <v>0.06018897842796925</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.936103261049944</v>
+        <v>3.813100034142133</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07420730034910529</v>
+        <v>0.07426442173908734</v>
       </c>
       <c r="C34">
-        <v>9709.318868977896</v>
+        <v>9560.834538863608</v>
       </c>
       <c r="D34">
-        <v>10753.1508689779</v>
+        <v>10748.01753886361</v>
       </c>
       <c r="E34">
-        <v>414.732</v>
+        <v>558.0830000000005</v>
       </c>
       <c r="F34">
-        <v>4587.232</v>
+        <v>4730.583000000001</v>
       </c>
       <c r="G34">
         <v>3543.4</v>
@@ -4075,28 +4075,28 @@
         <v>1052.8</v>
       </c>
       <c r="M34">
-        <v>276.1008078920902</v>
+        <v>284.7289581387181</v>
       </c>
       <c r="N34">
-        <v>776.6991921079098</v>
+        <v>768.0710418612819</v>
       </c>
       <c r="O34">
-        <v>77.66991921079098</v>
+        <v>76.80710418612819</v>
       </c>
       <c r="P34">
-        <v>699.0292728971187</v>
+        <v>691.2639376751537</v>
       </c>
       <c r="Q34">
-        <v>1924.329272897119</v>
+        <v>1916.563937675154</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08363658023801493</v>
+        <v>0.08416163454623951</v>
       </c>
       <c r="T34">
-        <v>0.758383548992048</v>
+        <v>0.7689075590156825</v>
       </c>
       <c r="U34">
         <v>0.06018897842796925</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.813100034142133</v>
+        <v>3.697551548259038</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07426442173908734</v>
+        <v>0.07432154312906938</v>
       </c>
       <c r="C35">
-        <v>9560.834538863608</v>
+        <v>9412.355107500382</v>
       </c>
       <c r="D35">
-        <v>10748.01753886361</v>
+        <v>10742.88910750038</v>
       </c>
       <c r="E35">
-        <v>558.0830000000005</v>
+        <v>701.4340000000002</v>
       </c>
       <c r="F35">
-        <v>4730.583000000001</v>
+        <v>4873.934</v>
       </c>
       <c r="G35">
         <v>3543.4</v>
@@ -4157,28 +4157,28 @@
         <v>1052.8</v>
       </c>
       <c r="M35">
-        <v>284.7289581387181</v>
+        <v>293.3571083853459</v>
       </c>
       <c r="N35">
-        <v>768.0710418612819</v>
+        <v>759.4428916146541</v>
       </c>
       <c r="O35">
-        <v>76.80710418612819</v>
+        <v>75.94428916146541</v>
       </c>
       <c r="P35">
-        <v>691.2639376751537</v>
+        <v>683.4986024531886</v>
       </c>
       <c r="Q35">
-        <v>1916.563937675154</v>
+        <v>1908.798602453189</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08416163454623951</v>
+        <v>0.08470259959107695</v>
       </c>
       <c r="T35">
-        <v>0.7689075590156825</v>
+        <v>0.7797504784339728</v>
       </c>
       <c r="U35">
         <v>0.06018897842796925</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.697551548259038</v>
+        <v>3.588800032133773</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07432154312906938</v>
+        <v>0.07437866451905142</v>
       </c>
       <c r="C36">
-        <v>9412.355107500382</v>
+        <v>9263.88056787922</v>
       </c>
       <c r="D36">
-        <v>10742.88910750038</v>
+        <v>10737.76556787922</v>
       </c>
       <c r="E36">
-        <v>701.4340000000002</v>
+        <v>844.7850000000008</v>
       </c>
       <c r="F36">
-        <v>4873.934</v>
+        <v>5017.285000000001</v>
       </c>
       <c r="G36">
         <v>3543.4</v>
@@ -4239,28 +4239,28 @@
         <v>1052.8</v>
       </c>
       <c r="M36">
-        <v>293.3571083853459</v>
+        <v>301.9852586319737</v>
       </c>
       <c r="N36">
-        <v>759.4428916146541</v>
+        <v>750.8147413680263</v>
       </c>
       <c r="O36">
-        <v>75.94428916146541</v>
+        <v>75.08147413680263</v>
       </c>
       <c r="P36">
-        <v>683.4986024531886</v>
+        <v>675.7332672312236</v>
       </c>
       <c r="Q36">
-        <v>1908.798602453189</v>
+        <v>1901.033267231224</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08470259959107695</v>
+        <v>0.08526020971421711</v>
       </c>
       <c r="T36">
-        <v>0.7797504784339728</v>
+        <v>0.7909270261420565</v>
       </c>
       <c r="U36">
         <v>0.06018897842796925</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.588800032133773</v>
+        <v>3.486262888358522</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07437866451905142</v>
+        <v>0.07443578590903346</v>
       </c>
       <c r="C37">
-        <v>9263.88056787922</v>
+        <v>9115.410913004496</v>
       </c>
       <c r="D37">
-        <v>10737.76556787922</v>
+        <v>10732.6469130045</v>
       </c>
       <c r="E37">
-        <v>844.7850000000008</v>
+        <v>988.1360000000004</v>
       </c>
       <c r="F37">
-        <v>5017.285000000001</v>
+        <v>5160.636</v>
       </c>
       <c r="G37">
         <v>3543.4</v>
@@ -4321,28 +4321,28 @@
         <v>1052.8</v>
       </c>
       <c r="M37">
-        <v>301.9852586319737</v>
+        <v>310.6134088786015</v>
       </c>
       <c r="N37">
-        <v>750.8147413680263</v>
+        <v>742.1865911213984</v>
       </c>
       <c r="O37">
-        <v>75.08147413680263</v>
+        <v>74.21865911213983</v>
       </c>
       <c r="P37">
-        <v>675.7332672312236</v>
+        <v>667.9679320092586</v>
       </c>
       <c r="Q37">
-        <v>1901.033267231224</v>
+        <v>1893.267932009258</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08526020971421711</v>
+        <v>0.08583524515370536</v>
       </c>
       <c r="T37">
-        <v>0.7909270261420565</v>
+        <v>0.8024528409660178</v>
       </c>
       <c r="U37">
         <v>0.06018897842796925</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.486262888358522</v>
+        <v>3.389422252570785</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07443578590903346</v>
+        <v>0.0744929072990155</v>
       </c>
       <c r="C38">
-        <v>9115.410913004496</v>
+        <v>8966.946135893919</v>
       </c>
       <c r="D38">
-        <v>10732.6469130045</v>
+        <v>10727.53313589392</v>
       </c>
       <c r="E38">
-        <v>988.1359999999995</v>
+        <v>1131.487</v>
       </c>
       <c r="F38">
-        <v>5160.636</v>
+        <v>5303.987</v>
       </c>
       <c r="G38">
         <v>3543.4</v>
@@ -4403,28 +4403,28 @@
         <v>1052.8</v>
       </c>
       <c r="M38">
-        <v>310.6134088786015</v>
+        <v>319.2415591252293</v>
       </c>
       <c r="N38">
-        <v>742.1865911213985</v>
+        <v>733.5584408747707</v>
       </c>
       <c r="O38">
-        <v>74.21865911213985</v>
+        <v>73.35584408747707</v>
       </c>
       <c r="P38">
-        <v>667.9679320092587</v>
+        <v>660.2025967872936</v>
       </c>
       <c r="Q38">
-        <v>1893.267932009259</v>
+        <v>1885.502596787293</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08583524515370536</v>
+        <v>0.08642853568651071</v>
       </c>
       <c r="T38">
-        <v>0.8024528409660178</v>
+        <v>0.8143445546732793</v>
       </c>
       <c r="U38">
         <v>0.06018897842796925</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.389422252570786</v>
+        <v>3.297816245744548</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0744929072990155</v>
+        <v>0.07455002868899756</v>
       </c>
       <c r="C39">
-        <v>8966.946135893919</v>
+        <v>8818.486229578484</v>
       </c>
       <c r="D39">
-        <v>10727.53313589392</v>
+        <v>10722.42422957849</v>
       </c>
       <c r="E39">
-        <v>1131.487</v>
+        <v>1274.838000000001</v>
       </c>
       <c r="F39">
-        <v>5303.987</v>
+        <v>5447.338000000001</v>
       </c>
       <c r="G39">
         <v>3543.4</v>
@@ -4485,28 +4485,28 @@
         <v>1052.8</v>
       </c>
       <c r="M39">
-        <v>319.2415591252293</v>
+        <v>327.8697093718572</v>
       </c>
       <c r="N39">
-        <v>733.5584408747707</v>
+        <v>724.9302906281428</v>
       </c>
       <c r="O39">
-        <v>73.35584408747707</v>
+        <v>72.49302906281427</v>
       </c>
       <c r="P39">
-        <v>660.2025967872936</v>
+        <v>652.4372615653285</v>
       </c>
       <c r="Q39">
-        <v>1885.502596787293</v>
+        <v>1877.737261565328</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08642853568651071</v>
+        <v>0.08704096462360011</v>
       </c>
       <c r="T39">
-        <v>0.8143445546732793</v>
+        <v>0.8266198720485173</v>
       </c>
       <c r="U39">
         <v>0.06018897842796925</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.297816245744548</v>
+        <v>3.211031607698638</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07455002868899756</v>
+        <v>0.07460715007897961</v>
       </c>
       <c r="C40">
-        <v>8818.486229578484</v>
+        <v>8670.031187102477</v>
       </c>
       <c r="D40">
-        <v>10722.42422957849</v>
+        <v>10717.32018710248</v>
       </c>
       <c r="E40">
-        <v>1274.838000000001</v>
+        <v>1418.189</v>
       </c>
       <c r="F40">
-        <v>5447.338000000001</v>
+        <v>5590.689</v>
       </c>
       <c r="G40">
         <v>3543.4</v>
@@ -4567,28 +4567,28 @@
         <v>1052.8</v>
       </c>
       <c r="M40">
-        <v>327.8697093718572</v>
+        <v>336.497859618485</v>
       </c>
       <c r="N40">
-        <v>724.9302906281428</v>
+        <v>716.302140381515</v>
       </c>
       <c r="O40">
-        <v>72.49302906281427</v>
+        <v>71.63021403815149</v>
       </c>
       <c r="P40">
-        <v>652.4372615653285</v>
+        <v>644.6719263433635</v>
       </c>
       <c r="Q40">
-        <v>1877.737261565328</v>
+        <v>1869.971926343364</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08704096462360011</v>
+        <v>0.08767347319797114</v>
       </c>
       <c r="T40">
-        <v>0.8266198720485173</v>
+        <v>0.839297658845894</v>
       </c>
       <c r="U40">
         <v>0.06018897842796925</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.211031607698638</v>
+        <v>3.128697463911494</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07460715007897961</v>
+        <v>0.07466427146896165</v>
       </c>
       <c r="C41">
-        <v>8670.031187102477</v>
+        <v>8521.581001523404</v>
       </c>
       <c r="D41">
-        <v>10717.32018710248</v>
+        <v>10712.2210015234</v>
       </c>
       <c r="E41">
-        <v>1418.189</v>
+        <v>1561.540000000001</v>
       </c>
       <c r="F41">
-        <v>5590.689</v>
+        <v>5734.040000000001</v>
       </c>
       <c r="G41">
         <v>3543.4</v>
@@ -4649,28 +4649,28 @@
         <v>1052.8</v>
       </c>
       <c r="M41">
-        <v>336.497859618485</v>
+        <v>345.1260098651128</v>
       </c>
       <c r="N41">
-        <v>716.302140381515</v>
+        <v>707.6739901348872</v>
       </c>
       <c r="O41">
-        <v>71.63021403815149</v>
+        <v>70.76739901348871</v>
       </c>
       <c r="P41">
-        <v>644.6719263433635</v>
+        <v>636.9065911213985</v>
       </c>
       <c r="Q41">
-        <v>1869.971926343364</v>
+        <v>1862.206591121399</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08767347319797114</v>
+        <v>0.08832706539148785</v>
       </c>
       <c r="T41">
-        <v>0.839297658845894</v>
+        <v>0.8523980385365167</v>
       </c>
       <c r="U41">
         <v>0.06018897842796925</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.128697463911494</v>
+        <v>3.050480027313707</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07466427146896165</v>
+        <v>0.07564389285894368</v>
       </c>
       <c r="C42">
-        <v>8521.581001523404</v>
+        <v>8291.528963679244</v>
       </c>
       <c r="D42">
-        <v>10712.2210015234</v>
+        <v>10625.51996367925</v>
       </c>
       <c r="E42">
-        <v>1561.540000000001</v>
+        <v>1704.891000000001</v>
       </c>
       <c r="F42">
-        <v>5734.040000000001</v>
+        <v>5877.391000000001</v>
       </c>
       <c r="G42">
         <v>3543.4</v>
@@ -4731,45 +4731,45 @@
         <v>1052.8</v>
       </c>
       <c r="M42">
-        <v>345.1260098651128</v>
+        <v>368.4476376117407</v>
       </c>
       <c r="N42">
-        <v>707.6739901348872</v>
+        <v>684.3523623882593</v>
       </c>
       <c r="O42">
-        <v>70.76739901348871</v>
+        <v>68.43523623882594</v>
       </c>
       <c r="P42">
-        <v>636.9065911213985</v>
+        <v>615.9171261494333</v>
       </c>
       <c r="Q42">
-        <v>1862.206591121399</v>
+        <v>1841.217126149433</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08832706539148785</v>
+        <v>0.08900281325258141</v>
       </c>
       <c r="T42">
-        <v>0.8523980385365167</v>
+        <v>0.8659424988946182</v>
       </c>
       <c r="U42">
-        <v>0.06018897842796925</v>
+        <v>0.06268897842796925</v>
       </c>
       <c r="V42">
         <v>0.1</v>
       </c>
       <c r="W42">
-        <v>0.05417008058517233</v>
+        <v>0.05642008058517232</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.050480027313707</v>
+        <v>2.857393812657335</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07564389285894368</v>
+        <v>0.07572351424892573</v>
       </c>
       <c r="C43">
-        <v>8291.528963679244</v>
+        <v>8141.192731279415</v>
       </c>
       <c r="D43">
-        <v>10625.51996367925</v>
+        <v>10618.53473127942</v>
       </c>
       <c r="E43">
-        <v>1704.891000000001</v>
+        <v>1848.242000000001</v>
       </c>
       <c r="F43">
-        <v>5877.391000000001</v>
+        <v>6020.742000000001</v>
       </c>
       <c r="G43">
         <v>3543.4</v>
@@ -4813,28 +4813,28 @@
         <v>1052.8</v>
       </c>
       <c r="M43">
-        <v>368.4476376117407</v>
+        <v>377.4341653583685</v>
       </c>
       <c r="N43">
-        <v>684.3523623882593</v>
+        <v>675.3658346416314</v>
       </c>
       <c r="O43">
-        <v>68.43523623882594</v>
+        <v>67.53658346416314</v>
       </c>
       <c r="P43">
-        <v>615.9171261494333</v>
+        <v>607.8292511774682</v>
       </c>
       <c r="Q43">
-        <v>1841.217126149433</v>
+        <v>1833.129251177468</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08900281325258141</v>
+        <v>0.08970186276405751</v>
       </c>
       <c r="T43">
-        <v>0.8659424988946182</v>
+        <v>0.8799540096098956</v>
       </c>
       <c r="U43">
         <v>0.06268897842796925</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.857393812657335</v>
+        <v>2.789360626641685</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07572351424892573</v>
+        <v>0.07580313563890777</v>
       </c>
       <c r="C44">
-        <v>8141.192731279416</v>
+        <v>7990.865677049883</v>
       </c>
       <c r="D44">
-        <v>10618.53473127942</v>
+        <v>10611.55867704988</v>
       </c>
       <c r="E44">
-        <v>1848.242</v>
+        <v>1991.593</v>
       </c>
       <c r="F44">
-        <v>6020.742</v>
+        <v>6164.093</v>
       </c>
       <c r="G44">
         <v>3543.4</v>
@@ -4895,28 +4895,28 @@
         <v>1052.8</v>
       </c>
       <c r="M44">
-        <v>377.4341653583684</v>
+        <v>386.4206931049962</v>
       </c>
       <c r="N44">
-        <v>675.3658346416315</v>
+        <v>666.3793068950038</v>
       </c>
       <c r="O44">
-        <v>67.53658346416316</v>
+        <v>66.63793068950038</v>
       </c>
       <c r="P44">
-        <v>607.8292511774683</v>
+        <v>599.7413762055033</v>
       </c>
       <c r="Q44">
-        <v>1833.129251177468</v>
+        <v>1825.041376205503</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08970186276405751</v>
+        <v>0.09042544032856784</v>
       </c>
       <c r="T44">
-        <v>0.8799540096098954</v>
+        <v>0.8944571522800948</v>
       </c>
       <c r="U44">
         <v>0.06268897842796925</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.789360626641685</v>
+        <v>2.72449177485932</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07580313563890777</v>
+        <v>0.07588275702888982</v>
       </c>
       <c r="C45">
-        <v>7990.865677049883</v>
+        <v>7840.547782913184</v>
       </c>
       <c r="D45">
-        <v>10611.55867704988</v>
+        <v>10604.59178291318</v>
       </c>
       <c r="E45">
-        <v>1991.593</v>
+        <v>2134.944</v>
       </c>
       <c r="F45">
-        <v>6164.093</v>
+        <v>6307.444</v>
       </c>
       <c r="G45">
         <v>3543.4</v>
@@ -4977,28 +4977,28 @@
         <v>1052.8</v>
       </c>
       <c r="M45">
-        <v>386.4206931049962</v>
+        <v>395.4072208516241</v>
       </c>
       <c r="N45">
-        <v>666.3793068950038</v>
+        <v>657.3927791483759</v>
       </c>
       <c r="O45">
-        <v>66.63793068950038</v>
+        <v>65.73927791483759</v>
       </c>
       <c r="P45">
-        <v>599.7413762055033</v>
+        <v>591.6535012335383</v>
       </c>
       <c r="Q45">
-        <v>1825.041376205503</v>
+        <v>1816.953501233538</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09042544032856784</v>
+        <v>0.09117485994895355</v>
       </c>
       <c r="T45">
-        <v>0.8944571522800948</v>
+        <v>0.9094782643313728</v>
       </c>
       <c r="U45">
         <v>0.06268897842796925</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.72449177485932</v>
+        <v>2.662571507248881</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07588275702888982</v>
+        <v>0.07596237841887186</v>
       </c>
       <c r="C46">
-        <v>7840.547782913184</v>
+        <v>7690.239030839306</v>
       </c>
       <c r="D46">
-        <v>10604.59178291318</v>
+        <v>10597.63403083931</v>
       </c>
       <c r="E46">
-        <v>2134.944</v>
+        <v>2278.295</v>
       </c>
       <c r="F46">
-        <v>6307.444</v>
+        <v>6450.795</v>
       </c>
       <c r="G46">
         <v>3543.4</v>
@@ -5059,28 +5059,28 @@
         <v>1052.8</v>
       </c>
       <c r="M46">
-        <v>395.4072208516241</v>
+        <v>404.3937485982519</v>
       </c>
       <c r="N46">
-        <v>657.3927791483759</v>
+        <v>648.406251401748</v>
       </c>
       <c r="O46">
-        <v>65.73927791483759</v>
+        <v>64.84062514017481</v>
       </c>
       <c r="P46">
-        <v>591.6535012335383</v>
+        <v>583.5656262615732</v>
       </c>
       <c r="Q46">
-        <v>1816.953501233538</v>
+        <v>1808.865626261573</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09117485994895355</v>
+        <v>0.09195153119189875</v>
       </c>
       <c r="T46">
-        <v>0.9094782643313728</v>
+        <v>0.9250455986390608</v>
       </c>
       <c r="U46">
         <v>0.06268897842796925</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.662571507248881</v>
+        <v>2.60340325153224</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07596237841887186</v>
+        <v>0.0760419998088539</v>
       </c>
       <c r="C47">
-        <v>7690.239030839306</v>
+        <v>7539.939402845519</v>
       </c>
       <c r="D47">
-        <v>10597.63403083931</v>
+        <v>10590.68540284552</v>
       </c>
       <c r="E47">
-        <v>2278.295</v>
+        <v>2421.646000000001</v>
       </c>
       <c r="F47">
-        <v>6450.795</v>
+        <v>6594.146000000001</v>
       </c>
       <c r="G47">
         <v>3543.4</v>
@@ -5141,28 +5141,28 @@
         <v>1052.8</v>
       </c>
       <c r="M47">
-        <v>404.3937485982519</v>
+        <v>413.3802763448797</v>
       </c>
       <c r="N47">
-        <v>648.406251401748</v>
+        <v>639.4197236551202</v>
       </c>
       <c r="O47">
-        <v>64.84062514017481</v>
+        <v>63.94197236551202</v>
       </c>
       <c r="P47">
-        <v>583.5656262615732</v>
+        <v>575.4777512896081</v>
       </c>
       <c r="Q47">
-        <v>1808.865626261573</v>
+        <v>1800.777751289608</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09195153119189875</v>
+        <v>0.0927569680364345</v>
       </c>
       <c r="T47">
-        <v>0.9250455986390608</v>
+        <v>0.9411895008840705</v>
       </c>
       <c r="U47">
         <v>0.06268897842796925</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.60340325153224</v>
+        <v>2.546807528672843</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0760419998088539</v>
+        <v>0.07760212119883596</v>
       </c>
       <c r="C48">
-        <v>7539.939402845519</v>
+        <v>7262.250431680174</v>
       </c>
       <c r="D48">
-        <v>10590.68540284552</v>
+        <v>10456.34743168017</v>
       </c>
       <c r="E48">
-        <v>2421.646000000001</v>
+        <v>2564.997</v>
       </c>
       <c r="F48">
-        <v>6594.146000000001</v>
+        <v>6737.497</v>
       </c>
       <c r="G48">
         <v>3543.4</v>
@@ -5223,45 +5223,45 @@
         <v>1052.8</v>
       </c>
       <c r="M48">
-        <v>413.3802763448797</v>
+        <v>445.9480435915076</v>
       </c>
       <c r="N48">
-        <v>639.4197236551202</v>
+        <v>606.8519564084924</v>
       </c>
       <c r="O48">
-        <v>63.94197236551202</v>
+        <v>60.68519564084924</v>
       </c>
       <c r="P48">
-        <v>575.4777512896081</v>
+        <v>546.1667607676432</v>
       </c>
       <c r="Q48">
-        <v>1800.777751289608</v>
+        <v>1771.466760767643</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0927569680364345</v>
+        <v>0.09359279872416029</v>
       </c>
       <c r="T48">
-        <v>0.9411895008840705</v>
+        <v>0.9579426069873826</v>
       </c>
       <c r="U48">
-        <v>0.06268897842796925</v>
+        <v>0.06618897842796925</v>
       </c>
       <c r="V48">
         <v>0.1</v>
       </c>
       <c r="W48">
-        <v>0.05642008058517232</v>
+        <v>0.05957008058517233</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.546807528672843</v>
+        <v>2.360813137604824</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07760212119883596</v>
+        <v>0.077713242588818</v>
       </c>
       <c r="C49">
-        <v>7262.250431680174</v>
+        <v>7109.460957295943</v>
       </c>
       <c r="D49">
-        <v>10456.34743168017</v>
+        <v>10446.90895729594</v>
       </c>
       <c r="E49">
-        <v>2564.997</v>
+        <v>2708.348000000001</v>
       </c>
       <c r="F49">
-        <v>6737.497</v>
+        <v>6880.848000000001</v>
       </c>
       <c r="G49">
         <v>3543.4</v>
@@ -5305,28 +5305,28 @@
         <v>1052.8</v>
       </c>
       <c r="M49">
-        <v>445.9480435915076</v>
+        <v>455.4362998381354</v>
       </c>
       <c r="N49">
-        <v>606.8519564084924</v>
+        <v>597.3637001618645</v>
       </c>
       <c r="O49">
-        <v>60.68519564084924</v>
+        <v>59.73637001618645</v>
       </c>
       <c r="P49">
-        <v>546.1667607676432</v>
+        <v>537.627330145678</v>
       </c>
       <c r="Q49">
-        <v>1771.466760767643</v>
+        <v>1762.927330145678</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09359279872416029</v>
+        <v>0.09446077674602937</v>
       </c>
       <c r="T49">
-        <v>0.9579426069873826</v>
+        <v>0.9753400633254374</v>
       </c>
       <c r="U49">
         <v>0.06618897842796925</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.360813137604824</v>
+        <v>2.31162953057139</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.077713242588818</v>
+        <v>0.07782436397880003</v>
       </c>
       <c r="C50">
-        <v>7109.460957295943</v>
+        <v>6956.688506917267</v>
       </c>
       <c r="D50">
-        <v>10446.90895729594</v>
+        <v>10437.48750691727</v>
       </c>
       <c r="E50">
-        <v>2708.348</v>
+        <v>2851.699</v>
       </c>
       <c r="F50">
-        <v>6880.848</v>
+        <v>7024.199</v>
       </c>
       <c r="G50">
         <v>3543.4</v>
@@ -5387,28 +5387,28 @@
         <v>1052.8</v>
       </c>
       <c r="M50">
-        <v>455.4362998381354</v>
+        <v>464.9245560847632</v>
       </c>
       <c r="N50">
-        <v>597.3637001618646</v>
+        <v>587.8754439152367</v>
       </c>
       <c r="O50">
-        <v>59.73637001618646</v>
+        <v>58.78754439152367</v>
       </c>
       <c r="P50">
-        <v>537.6273301456781</v>
+        <v>529.0878995237131</v>
       </c>
       <c r="Q50">
-        <v>1762.927330145678</v>
+        <v>1754.387899523713</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09446077674602937</v>
+        <v>0.09536279312169724</v>
       </c>
       <c r="T50">
-        <v>0.9753400633254373</v>
+        <v>0.9934197728532199</v>
       </c>
       <c r="U50">
         <v>0.06618897842796925</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.31162953057139</v>
+        <v>2.264453417702587</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07782436397880003</v>
+        <v>0.07919548536878207</v>
       </c>
       <c r="C51">
-        <v>6956.688506917267</v>
+        <v>6698.469753857277</v>
       </c>
       <c r="D51">
-        <v>10437.48750691727</v>
+        <v>10322.61975385728</v>
       </c>
       <c r="E51">
-        <v>2851.699</v>
+        <v>2995.05</v>
       </c>
       <c r="F51">
-        <v>7024.199</v>
+        <v>7167.55</v>
       </c>
       <c r="G51">
         <v>3543.4</v>
@@ -5469,45 +5469,45 @@
         <v>1052.8</v>
       </c>
       <c r="M51">
-        <v>464.9245560847632</v>
+        <v>494.481952331391</v>
       </c>
       <c r="N51">
-        <v>587.8754439152367</v>
+        <v>558.3180476686089</v>
       </c>
       <c r="O51">
-        <v>58.78754439152367</v>
+        <v>55.83180476686089</v>
       </c>
       <c r="P51">
-        <v>529.0878995237131</v>
+        <v>502.486242901748</v>
       </c>
       <c r="Q51">
-        <v>1754.387899523713</v>
+        <v>1727.786242901748</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09536279312169724</v>
+        <v>0.09630089015239182</v>
       </c>
       <c r="T51">
-        <v>0.9934197728532199</v>
+        <v>1.012222670762114</v>
       </c>
       <c r="U51">
-        <v>0.06618897842796925</v>
+        <v>0.06898897842796925</v>
       </c>
       <c r="V51">
         <v>0.1</v>
       </c>
       <c r="W51">
-        <v>0.05957008058517233</v>
+        <v>0.06209008058517233</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.264453417702587</v>
+        <v>2.129096916553258</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07919548536878207</v>
+        <v>0.07933180675876411</v>
       </c>
       <c r="C52">
-        <v>6698.469753857277</v>
+        <v>6543.836256290419</v>
       </c>
       <c r="D52">
-        <v>10322.61975385728</v>
+        <v>10311.33725629042</v>
       </c>
       <c r="E52">
-        <v>2995.05</v>
+        <v>3138.401000000001</v>
       </c>
       <c r="F52">
-        <v>7167.55</v>
+        <v>7310.901000000001</v>
       </c>
       <c r="G52">
         <v>3543.4</v>
@@ -5551,28 +5551,28 @@
         <v>1052.8</v>
       </c>
       <c r="M52">
-        <v>494.481952331391</v>
+        <v>504.3715913780189</v>
       </c>
       <c r="N52">
-        <v>558.3180476686089</v>
+        <v>548.4284086219811</v>
       </c>
       <c r="O52">
-        <v>55.83180476686089</v>
+        <v>54.84284086219812</v>
       </c>
       <c r="P52">
-        <v>502.486242901748</v>
+        <v>493.585567759783</v>
       </c>
       <c r="Q52">
-        <v>1727.786242901748</v>
+        <v>1718.885567759783</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09630089015239182</v>
+        <v>0.09727727685780863</v>
       </c>
       <c r="T52">
-        <v>1.012222670762114</v>
+        <v>1.031793033891778</v>
       </c>
       <c r="U52">
         <v>0.06898897842796925</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.129096916553258</v>
+        <v>2.087349918189469</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07933180675876411</v>
+        <v>0.07946812814874615</v>
       </c>
       <c r="C53">
-        <v>6543.836256290419</v>
+        <v>6389.22739506098</v>
       </c>
       <c r="D53">
-        <v>10311.33725629042</v>
+        <v>10300.07939506098</v>
       </c>
       <c r="E53">
-        <v>3138.401000000001</v>
+        <v>3281.752</v>
       </c>
       <c r="F53">
-        <v>7310.901000000001</v>
+        <v>7454.252</v>
       </c>
       <c r="G53">
         <v>3543.4</v>
@@ -5633,28 +5633,28 @@
         <v>1052.8</v>
       </c>
       <c r="M53">
-        <v>504.3715913780189</v>
+        <v>514.2612304246467</v>
       </c>
       <c r="N53">
-        <v>548.4284086219811</v>
+        <v>538.5387695753533</v>
       </c>
       <c r="O53">
-        <v>54.84284086219812</v>
+        <v>53.85387695753533</v>
       </c>
       <c r="P53">
-        <v>493.585567759783</v>
+        <v>484.6848926178179</v>
       </c>
       <c r="Q53">
-        <v>1718.885567759783</v>
+        <v>1709.984892617818</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09727727685780863</v>
+        <v>0.09829434634261781</v>
       </c>
       <c r="T53">
-        <v>1.031793033891778</v>
+        <v>1.052178828818513</v>
       </c>
       <c r="U53">
         <v>0.06898897842796925</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.087349918189469</v>
+        <v>2.047208573608902</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07946812814874615</v>
+        <v>0.07960444953872819</v>
       </c>
       <c r="C54">
-        <v>6389.22739506098</v>
+        <v>6234.643089563506</v>
       </c>
       <c r="D54">
-        <v>10300.07939506098</v>
+        <v>10288.84608956351</v>
       </c>
       <c r="E54">
-        <v>3281.752</v>
+        <v>3425.103000000001</v>
       </c>
       <c r="F54">
-        <v>7454.252</v>
+        <v>7597.603000000001</v>
       </c>
       <c r="G54">
         <v>3543.4</v>
@@ -5715,28 +5715,28 @@
         <v>1052.8</v>
       </c>
       <c r="M54">
-        <v>514.2612304246467</v>
+        <v>524.1508694712745</v>
       </c>
       <c r="N54">
-        <v>538.5387695753533</v>
+        <v>528.6491305287254</v>
       </c>
       <c r="O54">
-        <v>53.85387695753533</v>
+        <v>52.86491305287255</v>
       </c>
       <c r="P54">
-        <v>484.6848926178179</v>
+        <v>475.7842174758529</v>
       </c>
       <c r="Q54">
-        <v>1709.984892617818</v>
+        <v>1701.084217475853</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09829434634261781</v>
+        <v>0.09935469537997207</v>
       </c>
       <c r="T54">
-        <v>1.052178828818513</v>
+        <v>1.073432104380427</v>
       </c>
       <c r="U54">
         <v>0.06898897842796925</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.047208573608902</v>
+        <v>2.008581996748357</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07960444953872819</v>
+        <v>0.08353157092871025</v>
       </c>
       <c r="C55">
-        <v>6234.643089563506</v>
+        <v>5777.884637127891</v>
       </c>
       <c r="D55">
-        <v>10288.84608956351</v>
+        <v>9975.438637127892</v>
       </c>
       <c r="E55">
-        <v>3425.103000000001</v>
+        <v>3568.454000000001</v>
       </c>
       <c r="F55">
-        <v>7597.603000000001</v>
+        <v>7740.954000000001</v>
       </c>
       <c r="G55">
         <v>3543.4</v>
@@ -5797,45 +5797,45 @@
         <v>1052.8</v>
       </c>
       <c r="M55">
-        <v>524.1508694712745</v>
+        <v>594.4199497179023</v>
       </c>
       <c r="N55">
-        <v>528.6491305287254</v>
+        <v>458.3800502820976</v>
       </c>
       <c r="O55">
-        <v>52.86491305287255</v>
+        <v>45.83800502820976</v>
       </c>
       <c r="P55">
-        <v>475.7842174758529</v>
+        <v>412.5420452538879</v>
       </c>
       <c r="Q55">
-        <v>1701.084217475853</v>
+        <v>1637.842045253888</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09935469537997207</v>
+        <v>0.1004611465493852</v>
       </c>
       <c r="T55">
-        <v>1.073432104380427</v>
+        <v>1.095609435401556</v>
       </c>
       <c r="U55">
-        <v>0.06898897842796925</v>
+        <v>0.07678897842796925</v>
       </c>
       <c r="V55">
         <v>0.1</v>
       </c>
       <c r="W55">
-        <v>0.06209008058517233</v>
+        <v>0.06911008058517233</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.008581996748357</v>
+        <v>1.771138402235043</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08353157092871025</v>
+        <v>0.0856685923186923</v>
       </c>
       <c r="C56">
-        <v>5777.884637127891</v>
+        <v>5471.877901373525</v>
       </c>
       <c r="D56">
-        <v>9975.438637127892</v>
+        <v>9812.782901373526</v>
       </c>
       <c r="E56">
-        <v>3568.454000000001</v>
+        <v>3711.805000000001</v>
       </c>
       <c r="F56">
-        <v>7740.954000000001</v>
+        <v>7884.305000000001</v>
       </c>
       <c r="G56">
         <v>3543.4</v>
@@ -5879,45 +5879,45 @@
         <v>1052.8</v>
       </c>
       <c r="M56">
-        <v>594.4199497179023</v>
+        <v>636.1765160645302</v>
       </c>
       <c r="N56">
-        <v>458.3800502820976</v>
+        <v>416.6234839354697</v>
       </c>
       <c r="O56">
-        <v>45.83800502820976</v>
+        <v>41.66234839354698</v>
       </c>
       <c r="P56">
-        <v>412.5420452538879</v>
+        <v>374.9611355419228</v>
       </c>
       <c r="Q56">
-        <v>1637.842045253888</v>
+        <v>1600.261135541923</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1004611465493852</v>
+        <v>0.1016167733263278</v>
       </c>
       <c r="T56">
-        <v>1.095609435401556</v>
+        <v>1.118772425579178</v>
       </c>
       <c r="U56">
-        <v>0.07678897842796925</v>
+        <v>0.08068897842796925</v>
       </c>
       <c r="V56">
         <v>0.1</v>
       </c>
       <c r="W56">
-        <v>0.06911008058517233</v>
+        <v>0.07262008058517233</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.771138402235043</v>
+        <v>1.654886613094045</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0856685923186923</v>
+        <v>0.08591021370867434</v>
       </c>
       <c r="C57">
-        <v>5471.877901373525</v>
+        <v>5310.469462314471</v>
       </c>
       <c r="D57">
-        <v>9812.782901373526</v>
+        <v>9794.725462314473</v>
       </c>
       <c r="E57">
-        <v>3711.805000000001</v>
+        <v>3855.156000000001</v>
       </c>
       <c r="F57">
-        <v>7884.305000000001</v>
+        <v>8027.656000000001</v>
       </c>
       <c r="G57">
         <v>3543.4</v>
@@ -5961,28 +5961,28 @@
         <v>1052.8</v>
       </c>
       <c r="M57">
-        <v>636.1765160645302</v>
+        <v>647.743361811158</v>
       </c>
       <c r="N57">
-        <v>416.6234839354697</v>
+        <v>405.0566381888419</v>
       </c>
       <c r="O57">
-        <v>41.66234839354698</v>
+        <v>40.50566381888419</v>
       </c>
       <c r="P57">
-        <v>374.9611355419228</v>
+        <v>364.5509743699577</v>
       </c>
       <c r="Q57">
-        <v>1600.261135541923</v>
+        <v>1589.850974369958</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1016167733263278</v>
+        <v>0.1028249285931314</v>
       </c>
       <c r="T57">
-        <v>1.118772425579178</v>
+        <v>1.142988278946693</v>
       </c>
       <c r="U57">
         <v>0.08068897842796925</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.654886613094045</v>
+        <v>1.625335066431652</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08591021370867434</v>
+        <v>0.08615183509865638</v>
       </c>
       <c r="C58">
-        <v>5310.469462314471</v>
+        <v>5149.127359620179</v>
       </c>
       <c r="D58">
-        <v>9794.725462314473</v>
+        <v>9776.734359620181</v>
       </c>
       <c r="E58">
-        <v>3855.156000000001</v>
+        <v>3998.507000000001</v>
       </c>
       <c r="F58">
-        <v>8027.656000000001</v>
+        <v>8171.007000000001</v>
       </c>
       <c r="G58">
         <v>3543.4</v>
@@ -6043,28 +6043,28 @@
         <v>1052.8</v>
       </c>
       <c r="M58">
-        <v>647.743361811158</v>
+        <v>659.3102075577858</v>
       </c>
       <c r="N58">
-        <v>405.0566381888419</v>
+        <v>393.4897924422141</v>
       </c>
       <c r="O58">
-        <v>40.50566381888419</v>
+        <v>39.34897924422142</v>
       </c>
       <c r="P58">
-        <v>364.5509743699577</v>
+        <v>354.1408131979927</v>
       </c>
       <c r="Q58">
-        <v>1589.850974369958</v>
+        <v>1579.440813197993</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1028249285931314</v>
+        <v>0.1040892771281585</v>
       </c>
       <c r="T58">
-        <v>1.142988278946693</v>
+        <v>1.168330451075487</v>
       </c>
       <c r="U58">
         <v>0.08068897842796925</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.625335066431652</v>
+        <v>1.596820416143377</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08615183509865638</v>
+        <v>0.08639345648863843</v>
       </c>
       <c r="C59">
-        <v>5149.127359620179</v>
+        <v>4987.851228417881</v>
       </c>
       <c r="D59">
-        <v>9776.734359620181</v>
+        <v>9758.809228417884</v>
       </c>
       <c r="E59">
-        <v>3998.507000000001</v>
+        <v>4141.858000000002</v>
       </c>
       <c r="F59">
-        <v>8171.007000000001</v>
+        <v>8314.358000000002</v>
       </c>
       <c r="G59">
         <v>3543.4</v>
@@ -6125,28 +6125,28 @@
         <v>1052.8</v>
       </c>
       <c r="M59">
-        <v>659.3102075577858</v>
+        <v>670.8770533044137</v>
       </c>
       <c r="N59">
-        <v>393.4897924422141</v>
+        <v>381.9229466955862</v>
       </c>
       <c r="O59">
-        <v>39.34897924422142</v>
+        <v>38.19229466955863</v>
       </c>
       <c r="P59">
-        <v>354.1408131979927</v>
+        <v>343.7306520260276</v>
       </c>
       <c r="Q59">
-        <v>1579.440813197993</v>
+        <v>1569.030652026028</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1040892771281585</v>
+        <v>0.1054138327362821</v>
       </c>
       <c r="T59">
-        <v>1.168330451075487</v>
+        <v>1.194879393305653</v>
       </c>
       <c r="U59">
         <v>0.08068897842796925</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.596820416143377</v>
+        <v>1.569289029658147</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08639345648863841</v>
+        <v>0.08663507787862046</v>
       </c>
       <c r="C60">
-        <v>4987.851228417883</v>
+        <v>4826.640706505817</v>
       </c>
       <c r="D60">
-        <v>9758.809228417884</v>
+        <v>9740.949706505817</v>
       </c>
       <c r="E60">
-        <v>4141.858</v>
+        <v>4285.208999999999</v>
       </c>
       <c r="F60">
-        <v>8314.358</v>
+        <v>8457.708999999999</v>
       </c>
       <c r="G60">
         <v>3543.4</v>
@@ -6207,28 +6207,28 @@
         <v>1052.8</v>
       </c>
       <c r="M60">
-        <v>670.8770533044136</v>
+        <v>682.4438990510413</v>
       </c>
       <c r="N60">
-        <v>381.9229466955863</v>
+        <v>370.3561009489587</v>
       </c>
       <c r="O60">
-        <v>38.19229466955863</v>
+        <v>37.03561009489587</v>
       </c>
       <c r="P60">
-        <v>343.7306520260277</v>
+        <v>333.3204908540628</v>
       </c>
       <c r="Q60">
-        <v>1569.030652026028</v>
+        <v>1558.620490854063</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1054138327362821</v>
+        <v>0.1068030008130946</v>
       </c>
       <c r="T60">
-        <v>1.194879393305653</v>
+        <v>1.222723405888509</v>
       </c>
       <c r="U60">
         <v>0.08068897842796925</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.569289029658147</v>
+        <v>1.542690910511399</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08663507787862046</v>
+        <v>0.0868766992686025</v>
       </c>
       <c r="C61">
-        <v>4826.640706505817</v>
+        <v>4665.495434328823</v>
       </c>
       <c r="D61">
-        <v>9740.949706505817</v>
+        <v>9723.155434328823</v>
       </c>
       <c r="E61">
-        <v>4285.208999999999</v>
+        <v>4428.559999999999</v>
       </c>
       <c r="F61">
-        <v>8457.708999999999</v>
+        <v>8601.059999999999</v>
       </c>
       <c r="G61">
         <v>3543.4</v>
@@ -6289,28 +6289,28 @@
         <v>1052.8</v>
       </c>
       <c r="M61">
-        <v>682.4438990510413</v>
+        <v>694.0107447976692</v>
       </c>
       <c r="N61">
-        <v>370.3561009489587</v>
+        <v>358.7892552023308</v>
       </c>
       <c r="O61">
-        <v>37.03561009489587</v>
+        <v>35.87892552023308</v>
       </c>
       <c r="P61">
-        <v>333.3204908540628</v>
+        <v>322.9103296820977</v>
       </c>
       <c r="Q61">
-        <v>1558.620490854063</v>
+        <v>1548.210329682098</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1068030008130946</v>
+        <v>0.1082616272937478</v>
       </c>
       <c r="T61">
-        <v>1.222723405888509</v>
+        <v>1.251959619100509</v>
       </c>
       <c r="U61">
         <v>0.08068897842796925</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.542690910511399</v>
+        <v>1.516979395336209</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0868766992686025</v>
+        <v>0.09491412065858455</v>
       </c>
       <c r="C62">
-        <v>4665.495434328823</v>
+        <v>3965.153731541428</v>
       </c>
       <c r="D62">
-        <v>9723.155434328823</v>
+        <v>9166.164731541428</v>
       </c>
       <c r="E62">
-        <v>4428.559999999999</v>
+        <v>4571.911</v>
       </c>
       <c r="F62">
-        <v>8601.059999999999</v>
+        <v>8744.411</v>
       </c>
       <c r="G62">
         <v>3543.4</v>
@@ -6371,45 +6371,45 @@
         <v>1052.8</v>
       </c>
       <c r="M62">
-        <v>694.0107447976692</v>
+        <v>829.7482267442971</v>
       </c>
       <c r="N62">
-        <v>358.7892552023308</v>
+        <v>223.0517732557029</v>
       </c>
       <c r="O62">
-        <v>35.87892552023308</v>
+        <v>22.30517732557029</v>
       </c>
       <c r="P62">
-        <v>322.9103296820977</v>
+        <v>200.7465959301326</v>
       </c>
       <c r="Q62">
-        <v>1548.210329682098</v>
+        <v>1426.046595930133</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1082616272937478</v>
+        <v>0.1097950551323832</v>
       </c>
       <c r="T62">
-        <v>1.251959619100509</v>
+        <v>1.282695125297739</v>
       </c>
       <c r="U62">
-        <v>0.08068897842796925</v>
+        <v>0.09488897842796926</v>
       </c>
       <c r="V62">
         <v>0.1</v>
       </c>
       <c r="W62">
-        <v>0.07262008058517233</v>
+        <v>0.08540008058517233</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.516979395336209</v>
+        <v>1.268818619993798</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09491412065858455</v>
+        <v>0.111621624368868</v>
       </c>
       <c r="C63">
-        <v>3965.153731541428</v>
+        <v>2846.448396876716</v>
       </c>
       <c r="D63">
-        <v>9166.164731541428</v>
+        <v>8190.810396876716</v>
       </c>
       <c r="E63">
-        <v>4571.911</v>
+        <v>4715.262000000001</v>
       </c>
       <c r="F63">
-        <v>8744.411</v>
+        <v>8887.762000000001</v>
       </c>
       <c r="G63">
         <v>3543.4</v>
@@ -6453,45 +6453,45 @@
         <v>1052.8</v>
       </c>
       <c r="M63">
-        <v>829.7482267442971</v>
+        <v>1097.540649890925</v>
       </c>
       <c r="N63">
-        <v>223.0517732557029</v>
+        <v>-44.74064989092517</v>
       </c>
       <c r="O63">
-        <v>22.30517732557029</v>
+        <v>-4.474064989092517</v>
       </c>
       <c r="P63">
-        <v>200.7465959301326</v>
+        <v>-40.26658490183265</v>
       </c>
       <c r="Q63">
-        <v>1426.046595930133</v>
+        <v>1185.033415098167</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1097950551323832</v>
+        <v>0.1115859705418014</v>
       </c>
       <c r="T63">
-        <v>1.282695125297739</v>
+        <v>1.318591624812105</v>
       </c>
       <c r="U63">
-        <v>0.09488897842796926</v>
+        <v>0.1234889784279693</v>
       </c>
       <c r="V63">
-        <v>0.1</v>
+        <v>0.09592355418495238</v>
       </c>
       <c r="W63">
-        <v>0.08540008058517233</v>
+        <v>0.1116434767144895</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.268818619993798</v>
+        <v>0.9592355418495238</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.111621624368868</v>
+        <v>0.1123985141531478</v>
       </c>
       <c r="C64">
-        <v>2846.448396876716</v>
+        <v>2662.769467633068</v>
       </c>
       <c r="D64">
-        <v>8190.810396876716</v>
+        <v>8150.482467633069</v>
       </c>
       <c r="E64">
-        <v>4715.262000000001</v>
+        <v>4858.613000000001</v>
       </c>
       <c r="F64">
-        <v>8887.762000000001</v>
+        <v>9031.113000000001</v>
       </c>
       <c r="G64">
         <v>3543.4</v>
@@ -6535,37 +6535,37 @@
         <v>1052.8</v>
       </c>
       <c r="M64">
-        <v>1097.540649890925</v>
+        <v>1115.242918437553</v>
       </c>
       <c r="N64">
-        <v>-44.74064989092517</v>
+        <v>-62.44291843755309</v>
       </c>
       <c r="O64">
-        <v>-4.474064989092517</v>
+        <v>-6.24429184375531</v>
       </c>
       <c r="P64">
-        <v>-40.26658490183265</v>
+        <v>-56.19862659379778</v>
       </c>
       <c r="Q64">
-        <v>1185.033415098167</v>
+        <v>1169.101373406202</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1115859705418014</v>
+        <v>0.1133639697456339</v>
       </c>
       <c r="T64">
-        <v>1.318591624812105</v>
+        <v>1.354229236293513</v>
       </c>
       <c r="U64">
         <v>0.1234889784279693</v>
       </c>
       <c r="V64">
-        <v>0.09592355418495238</v>
+        <v>0.09440095808677852</v>
       </c>
       <c r="W64">
-        <v>0.1116434767144895</v>
+        <v>0.1118315005512115</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9592355418495238</v>
+        <v>0.9440095808677852</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1123985141531478</v>
+        <v>0.1131754039374274</v>
       </c>
       <c r="C65">
-        <v>2662.769467633068</v>
+        <v>2479.485706545427</v>
       </c>
       <c r="D65">
-        <v>8150.482467633069</v>
+        <v>8110.549706545427</v>
       </c>
       <c r="E65">
-        <v>4858.613000000001</v>
+        <v>5001.964</v>
       </c>
       <c r="F65">
-        <v>9031.113000000001</v>
+        <v>9174.464</v>
       </c>
       <c r="G65">
         <v>3543.4</v>
@@ -6617,37 +6617,37 @@
         <v>1052.8</v>
       </c>
       <c r="M65">
-        <v>1115.242918437553</v>
+        <v>1132.945186984181</v>
       </c>
       <c r="N65">
-        <v>-62.44291843755309</v>
+        <v>-80.14518698418078</v>
       </c>
       <c r="O65">
-        <v>-6.24429184375531</v>
+        <v>-8.014518698418078</v>
       </c>
       <c r="P65">
-        <v>-56.19862659379778</v>
+        <v>-72.13066828576271</v>
       </c>
       <c r="Q65">
-        <v>1169.101373406202</v>
+        <v>1153.169331714237</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1133639697456339</v>
+        <v>0.1152407466830126</v>
       </c>
       <c r="T65">
-        <v>1.354229236293513</v>
+        <v>1.391846715079444</v>
       </c>
       <c r="U65">
         <v>0.1234889784279693</v>
       </c>
       <c r="V65">
-        <v>0.09440095808677852</v>
+        <v>0.09292594311667263</v>
       </c>
       <c r="W65">
-        <v>0.1118315005512115</v>
+        <v>0.1120136486430358</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9440095808677852</v>
+        <v>0.9292594311667262</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1131754039374274</v>
+        <v>0.1139522937217071</v>
       </c>
       <c r="C66">
-        <v>2479.485706545427</v>
+        <v>2296.591333630071</v>
       </c>
       <c r="D66">
-        <v>8110.549706545427</v>
+        <v>8071.006333630071</v>
       </c>
       <c r="E66">
-        <v>5001.964</v>
+        <v>5145.315000000001</v>
       </c>
       <c r="F66">
-        <v>9174.464</v>
+        <v>9317.815000000001</v>
       </c>
       <c r="G66">
         <v>3543.4</v>
@@ -6699,37 +6699,37 @@
         <v>1052.8</v>
       </c>
       <c r="M66">
-        <v>1132.945186984181</v>
+        <v>1150.647455530809</v>
       </c>
       <c r="N66">
-        <v>-80.14518698418078</v>
+        <v>-97.8474555308087</v>
       </c>
       <c r="O66">
-        <v>-8.014518698418078</v>
+        <v>-9.784745553080871</v>
       </c>
       <c r="P66">
-        <v>-72.13066828576271</v>
+        <v>-88.06270997772783</v>
       </c>
       <c r="Q66">
-        <v>1153.169331714237</v>
+        <v>1137.237290022272</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1152407466830126</v>
+        <v>0.117224768016813</v>
       </c>
       <c r="T66">
-        <v>1.391846715079444</v>
+        <v>1.431613764081714</v>
       </c>
       <c r="U66">
         <v>0.1234889784279693</v>
       </c>
       <c r="V66">
-        <v>0.09292594311667263</v>
+        <v>0.09149631322256996</v>
       </c>
       <c r="W66">
-        <v>0.1120136486430358</v>
+        <v>0.1121901921781886</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9292594311667262</v>
+        <v>0.9149631322256995</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1139522937217071</v>
+        <v>0.1147291835059868</v>
       </c>
       <c r="C67">
-        <v>2296.591333630071</v>
+        <v>2114.080681078709</v>
       </c>
       <c r="D67">
-        <v>8071.006333630071</v>
+        <v>8031.84668107871</v>
       </c>
       <c r="E67">
-        <v>5145.315000000001</v>
+        <v>5288.666000000001</v>
       </c>
       <c r="F67">
-        <v>9317.815000000001</v>
+        <v>9461.166000000001</v>
       </c>
       <c r="G67">
         <v>3543.4</v>
@@ -6781,37 +6781,37 @@
         <v>1052.8</v>
       </c>
       <c r="M67">
-        <v>1150.647455530809</v>
+        <v>1168.349724077436</v>
       </c>
       <c r="N67">
-        <v>-97.8474555308087</v>
+        <v>-115.5497240774364</v>
       </c>
       <c r="O67">
-        <v>-9.784745553080871</v>
+        <v>-11.55497240774364</v>
       </c>
       <c r="P67">
-        <v>-88.06270997772783</v>
+        <v>-103.9947516696928</v>
       </c>
       <c r="Q67">
-        <v>1137.237290022272</v>
+        <v>1121.305248330307</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.117224768016813</v>
+        <v>0.1193254964878957</v>
       </c>
       <c r="T67">
-        <v>1.431613764081714</v>
+        <v>1.473720051260588</v>
       </c>
       <c r="U67">
         <v>0.1234889784279693</v>
       </c>
       <c r="V67">
-        <v>0.09149631322256996</v>
+        <v>0.09011000544647041</v>
       </c>
       <c r="W67">
-        <v>0.1121901921781886</v>
+        <v>0.1123613859092459</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9149631322256995</v>
+        <v>0.9011000544647041</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1147291835059868</v>
+        <v>0.1155060732902665</v>
       </c>
       <c r="C68">
-        <v>2114.080681078709</v>
+        <v>1931.948190550309</v>
       </c>
       <c r="D68">
-        <v>8031.84668107871</v>
+        <v>7993.065190550311</v>
       </c>
       <c r="E68">
-        <v>5288.666000000001</v>
+        <v>5432.017000000002</v>
       </c>
       <c r="F68">
-        <v>9461.166000000001</v>
+        <v>9604.517000000002</v>
       </c>
       <c r="G68">
         <v>3543.4</v>
@@ -6863,37 +6863,37 @@
         <v>1052.8</v>
       </c>
       <c r="M68">
-        <v>1168.349724077436</v>
+        <v>1186.051992624064</v>
       </c>
       <c r="N68">
-        <v>-115.5497240774364</v>
+        <v>-133.2519926240643</v>
       </c>
       <c r="O68">
-        <v>-11.55497240774364</v>
+        <v>-13.32519926240643</v>
       </c>
       <c r="P68">
-        <v>-103.9947516696928</v>
+        <v>-119.9267933616579</v>
       </c>
       <c r="Q68">
-        <v>1121.305248330307</v>
+        <v>1105.373206638342</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1193254964878957</v>
+        <v>0.1215535418360138</v>
       </c>
       <c r="T68">
-        <v>1.473720051260588</v>
+        <v>1.518378234632121</v>
       </c>
       <c r="U68">
         <v>0.1234889784279693</v>
       </c>
       <c r="V68">
-        <v>0.09011000544647041</v>
+        <v>0.08876507999204547</v>
       </c>
       <c r="W68">
-        <v>0.1123613859092459</v>
+        <v>0.1125274693796746</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9011000544647041</v>
+        <v>0.8876507999204548</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1155060732902665</v>
+        <v>0.1162829630745462</v>
       </c>
       <c r="C69">
-        <v>1931.948190550309</v>
+        <v>1750.188410540999</v>
       </c>
       <c r="D69">
-        <v>7993.065190550311</v>
+        <v>7954.656410540999</v>
       </c>
       <c r="E69">
-        <v>5432.017000000002</v>
+        <v>5575.368</v>
       </c>
       <c r="F69">
-        <v>9604.517000000002</v>
+        <v>9747.868</v>
       </c>
       <c r="G69">
         <v>3543.4</v>
@@ -6945,37 +6945,37 @@
         <v>1052.8</v>
       </c>
       <c r="M69">
-        <v>1186.051992624064</v>
+        <v>1203.754261170692</v>
       </c>
       <c r="N69">
-        <v>-133.2519926240643</v>
+        <v>-150.954261170692</v>
       </c>
       <c r="O69">
-        <v>-13.32519926240643</v>
+        <v>-15.0954261170692</v>
       </c>
       <c r="P69">
-        <v>-119.9267933616579</v>
+        <v>-135.8588350536228</v>
       </c>
       <c r="Q69">
-        <v>1105.373206638342</v>
+        <v>1089.441164946377</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1215535418360138</v>
+        <v>0.1239208400183892</v>
       </c>
       <c r="T69">
-        <v>1.518378234632121</v>
+        <v>1.565827554464375</v>
       </c>
       <c r="U69">
         <v>0.1234889784279693</v>
       </c>
       <c r="V69">
-        <v>0.08876507999204547</v>
+        <v>0.08745971116863305</v>
       </c>
       <c r="W69">
-        <v>0.1125274693796746</v>
+        <v>0.1126886680421495</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8876507999204548</v>
+        <v>0.8745971116863305</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1162829630745462</v>
+        <v>0.1170598528588259</v>
       </c>
       <c r="C70">
-        <v>1750.188410540999</v>
+        <v>1568.795993829433</v>
       </c>
       <c r="D70">
-        <v>7954.656410540999</v>
+        <v>7916.614993829435</v>
       </c>
       <c r="E70">
-        <v>5575.368</v>
+        <v>5718.719000000001</v>
       </c>
       <c r="F70">
-        <v>9747.868</v>
+        <v>9891.219000000001</v>
       </c>
       <c r="G70">
         <v>3543.4</v>
@@ -7027,37 +7027,37 @@
         <v>1052.8</v>
       </c>
       <c r="M70">
-        <v>1203.754261170692</v>
+        <v>1221.45652971732</v>
       </c>
       <c r="N70">
-        <v>-150.954261170692</v>
+        <v>-168.6565297173199</v>
       </c>
       <c r="O70">
-        <v>-15.0954261170692</v>
+        <v>-16.86565297173199</v>
       </c>
       <c r="P70">
-        <v>-135.8588350536228</v>
+        <v>-151.7908767455879</v>
       </c>
       <c r="Q70">
-        <v>1089.441164946377</v>
+        <v>1073.509123254412</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1239208400183892</v>
+        <v>0.1264408671157566</v>
       </c>
       <c r="T70">
-        <v>1.565827554464375</v>
+        <v>1.616338120737419</v>
       </c>
       <c r="U70">
         <v>0.1234889784279693</v>
       </c>
       <c r="V70">
-        <v>0.08745971116863305</v>
+        <v>0.08619217912271084</v>
       </c>
       <c r="W70">
-        <v>0.1126886680421495</v>
+        <v>0.1128451942796252</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8745971116863305</v>
+        <v>0.8619217912271082</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1170598528588259</v>
+        <v>0.1178367426431056</v>
       </c>
       <c r="C71">
-        <v>1568.795993829433</v>
+        <v>1387.76569499514</v>
       </c>
       <c r="D71">
-        <v>7916.614993829435</v>
+        <v>7878.935694995141</v>
       </c>
       <c r="E71">
-        <v>5718.719000000001</v>
+        <v>5862.070000000002</v>
       </c>
       <c r="F71">
-        <v>9891.219000000001</v>
+        <v>10034.57</v>
       </c>
       <c r="G71">
         <v>3543.4</v>
@@ -7109,37 +7109,37 @@
         <v>1052.8</v>
       </c>
       <c r="M71">
-        <v>1221.45652971732</v>
+        <v>1239.158798263948</v>
       </c>
       <c r="N71">
-        <v>-168.6565297173199</v>
+        <v>-186.3587982639478</v>
       </c>
       <c r="O71">
-        <v>-16.86565297173199</v>
+        <v>-18.63587982639478</v>
       </c>
       <c r="P71">
-        <v>-151.7908767455879</v>
+        <v>-167.7229184375531</v>
       </c>
       <c r="Q71">
-        <v>1073.509123254412</v>
+        <v>1057.577081562447</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1264408671157566</v>
+        <v>0.1291288960196152</v>
       </c>
       <c r="T71">
-        <v>1.616338120737419</v>
+        <v>1.670216058095333</v>
       </c>
       <c r="U71">
         <v>0.1234889784279693</v>
       </c>
       <c r="V71">
-        <v>0.08619217912271084</v>
+        <v>0.08496086227810068</v>
       </c>
       <c r="W71">
-        <v>0.1128451942796252</v>
+        <v>0.1129972483388872</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8619217912271082</v>
+        <v>0.8496086227810067</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1178367426431056</v>
+        <v>0.1186136324273853</v>
       </c>
       <c r="C72">
-        <v>1387.76569499514</v>
+        <v>1207.092368007348</v>
       </c>
       <c r="D72">
-        <v>7878.935694995141</v>
+        <v>7841.61336800735</v>
       </c>
       <c r="E72">
-        <v>5862.070000000002</v>
+        <v>6005.421000000002</v>
       </c>
       <c r="F72">
-        <v>10034.57</v>
+        <v>10177.921</v>
       </c>
       <c r="G72">
         <v>3543.4</v>
@@ -7191,37 +7191,37 @@
         <v>1052.8</v>
       </c>
       <c r="M72">
-        <v>1239.158798263948</v>
+        <v>1256.861066810576</v>
       </c>
       <c r="N72">
-        <v>-186.3587982639478</v>
+        <v>-204.0610668105758</v>
       </c>
       <c r="O72">
-        <v>-18.63587982639478</v>
+        <v>-20.40610668105758</v>
       </c>
       <c r="P72">
-        <v>-167.7229184375531</v>
+        <v>-183.6549601295182</v>
       </c>
       <c r="Q72">
-        <v>1057.577081562447</v>
+        <v>1041.645039870482</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1291288960196152</v>
+        <v>0.1320023062271881</v>
       </c>
       <c r="T72">
-        <v>1.670216058095333</v>
+        <v>1.727809715271035</v>
       </c>
       <c r="U72">
         <v>0.1234889784279693</v>
       </c>
       <c r="V72">
-        <v>0.08496086227810068</v>
+        <v>0.08376423041502883</v>
       </c>
       <c r="W72">
-        <v>0.1129972483388872</v>
+        <v>0.1131450191852123</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8496086227810067</v>
+        <v>0.8376423041502882</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1186136324273853</v>
+        <v>0.119390522211665</v>
       </c>
       <c r="C73">
-        <v>1207.09236800735</v>
+        <v>1026.770963882082</v>
       </c>
       <c r="D73">
-        <v>7841.61336800735</v>
+        <v>7804.642963882081</v>
       </c>
       <c r="E73">
-        <v>6005.421</v>
+        <v>6148.771999999999</v>
       </c>
       <c r="F73">
-        <v>10177.921</v>
+        <v>10321.272</v>
       </c>
       <c r="G73">
         <v>3543.4</v>
@@ -7273,37 +7273,37 @@
         <v>1052.8</v>
       </c>
       <c r="M73">
-        <v>1256.861066810575</v>
+        <v>1274.563335357203</v>
       </c>
       <c r="N73">
-        <v>-204.0610668105755</v>
+        <v>-221.7633353572032</v>
       </c>
       <c r="O73">
-        <v>-20.40610668105755</v>
+        <v>-22.17633353572032</v>
       </c>
       <c r="P73">
-        <v>-183.654960129518</v>
+        <v>-199.5870018214829</v>
       </c>
       <c r="Q73">
-        <v>1041.645039870482</v>
+        <v>1025.712998178517</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1320023062271881</v>
+        <v>0.1350809600210162</v>
       </c>
       <c r="T73">
-        <v>1.727809715271034</v>
+        <v>1.789517205102142</v>
       </c>
       <c r="U73">
         <v>0.1234889784279693</v>
       </c>
       <c r="V73">
-        <v>0.08376423041502884</v>
+        <v>0.08260083832593124</v>
       </c>
       <c r="W73">
-        <v>0.1131450191852123</v>
+        <v>0.1132886852858062</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8376423041502883</v>
+        <v>0.8260083832593121</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.119390522211665</v>
+        <v>0.1201674119959447</v>
       </c>
       <c r="C74">
-        <v>1026.770963882082</v>
+        <v>846.7965284051697</v>
       </c>
       <c r="D74">
-        <v>7804.642963882081</v>
+        <v>7768.019528405169</v>
       </c>
       <c r="E74">
-        <v>6148.771999999999</v>
+        <v>6292.123</v>
       </c>
       <c r="F74">
-        <v>10321.272</v>
+        <v>10464.623</v>
       </c>
       <c r="G74">
         <v>3543.4</v>
@@ -7355,37 +7355,37 @@
         <v>1052.8</v>
       </c>
       <c r="M74">
-        <v>1274.563335357203</v>
+        <v>1292.265603903831</v>
       </c>
       <c r="N74">
-        <v>-221.7633353572032</v>
+        <v>-239.4656039038312</v>
       </c>
       <c r="O74">
-        <v>-22.17633353572032</v>
+        <v>-23.94656039038312</v>
       </c>
       <c r="P74">
-        <v>-199.5870018214829</v>
+        <v>-215.519043513448</v>
       </c>
       <c r="Q74">
-        <v>1025.712998178517</v>
+        <v>1009.780956486552</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1350809600210162</v>
+        <v>0.1383876622440168</v>
       </c>
       <c r="T74">
-        <v>1.789517205102142</v>
+        <v>1.855795620105925</v>
       </c>
       <c r="U74">
         <v>0.1234889784279693</v>
       </c>
       <c r="V74">
-        <v>0.08260083832593124</v>
+        <v>0.08146931999269928</v>
       </c>
       <c r="W74">
-        <v>0.1132886852858062</v>
+        <v>0.1134284153288495</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8260083832593121</v>
+        <v>0.8146931999269929</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1201674119959447</v>
+        <v>0.1209443017802244</v>
       </c>
       <c r="C75">
-        <v>846.7965284051697</v>
+        <v>667.1641999190961</v>
       </c>
       <c r="D75">
-        <v>7768.019528405169</v>
+        <v>7731.738199919096</v>
       </c>
       <c r="E75">
-        <v>6292.123</v>
+        <v>6435.474</v>
       </c>
       <c r="F75">
-        <v>10464.623</v>
+        <v>10607.974</v>
       </c>
       <c r="G75">
         <v>3543.4</v>
@@ -7437,37 +7437,37 @@
         <v>1052.8</v>
       </c>
       <c r="M75">
-        <v>1292.265603903831</v>
+        <v>1309.967872450459</v>
       </c>
       <c r="N75">
-        <v>-239.4656039038312</v>
+        <v>-257.1678724504591</v>
       </c>
       <c r="O75">
-        <v>-23.94656039038312</v>
+        <v>-25.71678724504591</v>
       </c>
       <c r="P75">
-        <v>-215.519043513448</v>
+        <v>-231.4510852054132</v>
       </c>
       <c r="Q75">
-        <v>1009.780956486552</v>
+        <v>993.8489147945868</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1383876622440168</v>
+        <v>0.141948726176479</v>
       </c>
       <c r="T75">
-        <v>1.855795620105925</v>
+        <v>1.927172374725384</v>
       </c>
       <c r="U75">
         <v>0.1234889784279693</v>
       </c>
       <c r="V75">
-        <v>0.08146931999269928</v>
+        <v>0.08036838323604117</v>
       </c>
       <c r="W75">
-        <v>0.1134284153288495</v>
+        <v>0.113564368884243</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8146931999269929</v>
+        <v>0.8036838323604117</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1209443017802244</v>
+        <v>0.1840029094603148</v>
       </c>
       <c r="C76">
-        <v>667.1641999190961</v>
+        <v>-1601.574221987163</v>
       </c>
       <c r="D76">
-        <v>7731.738199919096</v>
+        <v>5606.350778012838</v>
       </c>
       <c r="E76">
-        <v>6435.474</v>
+        <v>6578.825000000001</v>
       </c>
       <c r="F76">
-        <v>10607.974</v>
+        <v>10751.325</v>
       </c>
       <c r="G76">
         <v>3543.4</v>
@@ -7519,45 +7519,45 @@
         <v>1052.8</v>
       </c>
       <c r="M76">
-        <v>1309.967872450459</v>
+        <v>2211.429055997087</v>
       </c>
       <c r="N76">
-        <v>-257.1678724504591</v>
+        <v>-1158.629055997087</v>
       </c>
       <c r="O76">
-        <v>-25.71678724504591</v>
+        <v>-115.8629055997087</v>
       </c>
       <c r="P76">
-        <v>-231.4510852054132</v>
+        <v>-1042.766150397378</v>
       </c>
       <c r="Q76">
-        <v>993.8489147945868</v>
+        <v>182.5338496026218</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.141948726176479</v>
+        <v>0.1483215468067812</v>
       </c>
       <c r="T76">
-        <v>1.927172374725384</v>
+        <v>2.054907024535054</v>
       </c>
       <c r="U76">
-        <v>0.1234889784279693</v>
+        <v>0.2056889784279693</v>
       </c>
       <c r="V76">
-        <v>0.08036838323604117</v>
+        <v>0.04760722471041761</v>
       </c>
       <c r="W76">
-        <v>0.113564368884243</v>
+        <v>0.1958966970114927</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.8036838323604117</v>
+        <v>0.4760722471041761</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1840029094603148</v>
+        <v>0.1856017992445945</v>
       </c>
       <c r="C77">
-        <v>-1601.574221987163</v>
+        <v>-1783.731218035547</v>
       </c>
       <c r="D77">
-        <v>5606.350778012838</v>
+        <v>5567.544781964454</v>
       </c>
       <c r="E77">
-        <v>6578.825000000001</v>
+        <v>6722.176000000001</v>
       </c>
       <c r="F77">
-        <v>10751.325</v>
+        <v>10894.676</v>
       </c>
       <c r="G77">
         <v>3543.4</v>
@@ -7601,37 +7601,37 @@
         <v>1052.8</v>
       </c>
       <c r="M77">
-        <v>2211.429055997087</v>
+        <v>2240.914776743715</v>
       </c>
       <c r="N77">
-        <v>-1158.629055997087</v>
+        <v>-1188.114776743715</v>
       </c>
       <c r="O77">
-        <v>-115.8629055997087</v>
+        <v>-118.8114776743715</v>
       </c>
       <c r="P77">
-        <v>-1042.766150397378</v>
+        <v>-1069.303299069343</v>
       </c>
       <c r="Q77">
-        <v>182.5338496026218</v>
+        <v>155.9967009306565</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1483215468067812</v>
+        <v>0.1525932779237304</v>
       </c>
       <c r="T77">
-        <v>2.054907024535054</v>
+        <v>2.140528150557347</v>
       </c>
       <c r="U77">
         <v>0.2056889784279693</v>
       </c>
       <c r="V77">
-        <v>0.04760722471041761</v>
+        <v>0.04698081385896474</v>
       </c>
       <c r="W77">
-        <v>0.1958966970114927</v>
+        <v>0.1960255428196042</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4760722471041761</v>
+        <v>0.4698081385896474</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1856017992445945</v>
+        <v>0.1872006890288742</v>
       </c>
       <c r="C78">
-        <v>-1783.731218035547</v>
+        <v>-1965.354692911858</v>
       </c>
       <c r="D78">
-        <v>5567.544781964454</v>
+        <v>5529.272307088142</v>
       </c>
       <c r="E78">
-        <v>6722.176000000001</v>
+        <v>6865.527</v>
       </c>
       <c r="F78">
-        <v>10894.676</v>
+        <v>11038.027</v>
       </c>
       <c r="G78">
         <v>3543.4</v>
@@ -7683,37 +7683,37 @@
         <v>1052.8</v>
       </c>
       <c r="M78">
-        <v>2240.914776743715</v>
+        <v>2270.400497490342</v>
       </c>
       <c r="N78">
-        <v>-1188.114776743715</v>
+        <v>-1217.600497490342</v>
       </c>
       <c r="O78">
-        <v>-118.8114776743715</v>
+        <v>-121.7600497490342</v>
       </c>
       <c r="P78">
-        <v>-1069.303299069343</v>
+        <v>-1095.840447741308</v>
       </c>
       <c r="Q78">
-        <v>155.9967009306565</v>
+        <v>129.4595522586917</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1525932779237304</v>
+        <v>0.1572364639204143</v>
       </c>
       <c r="T78">
-        <v>2.140528150557347</v>
+        <v>2.233594591885927</v>
       </c>
       <c r="U78">
         <v>0.2056889784279693</v>
       </c>
       <c r="V78">
-        <v>0.04698081385896474</v>
+        <v>0.04637067341923794</v>
       </c>
       <c r="W78">
-        <v>0.1960255428196042</v>
+        <v>0.1961510419833492</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4698081385896474</v>
+        <v>0.4637067341923793</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1872006890288742</v>
+        <v>0.1887995788131539</v>
       </c>
       <c r="C79">
-        <v>-1965.354692911858</v>
+        <v>-2146.45557410877</v>
       </c>
       <c r="D79">
-        <v>5529.272307088142</v>
+        <v>5491.52242589123</v>
       </c>
       <c r="E79">
-        <v>6865.527</v>
+        <v>7008.878000000001</v>
       </c>
       <c r="F79">
-        <v>11038.027</v>
+        <v>11181.378</v>
       </c>
       <c r="G79">
         <v>3543.4</v>
@@ -7765,37 +7765,37 @@
         <v>1052.8</v>
       </c>
       <c r="M79">
-        <v>2270.400497490342</v>
+        <v>2299.88621823697</v>
       </c>
       <c r="N79">
-        <v>-1217.600497490342</v>
+        <v>-1247.08621823697</v>
       </c>
       <c r="O79">
-        <v>-121.7600497490342</v>
+        <v>-124.708621823697</v>
       </c>
       <c r="P79">
-        <v>-1095.840447741308</v>
+        <v>-1122.377596413273</v>
       </c>
       <c r="Q79">
-        <v>129.4595522586917</v>
+        <v>102.9224035867267</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1572364639204143</v>
+        <v>0.1623017577349786</v>
       </c>
       <c r="T79">
-        <v>2.233594591885927</v>
+        <v>2.335121618789834</v>
       </c>
       <c r="U79">
         <v>0.2056889784279693</v>
       </c>
       <c r="V79">
-        <v>0.04637067341923794</v>
+        <v>0.04577617760617078</v>
       </c>
       <c r="W79">
-        <v>0.1961510419833492</v>
+        <v>0.1962733232198187</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4637067341923793</v>
+        <v>0.4577617760617078</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1887995788131539</v>
+        <v>0.1903984685974336</v>
       </c>
       <c r="C80">
-        <v>-2146.45557410877</v>
+        <v>-2327.044492722389</v>
       </c>
       <c r="D80">
-        <v>5491.52242589123</v>
+        <v>5454.284507277613</v>
       </c>
       <c r="E80">
-        <v>7008.878000000001</v>
+        <v>7152.229000000001</v>
       </c>
       <c r="F80">
-        <v>11181.378</v>
+        <v>11324.729</v>
       </c>
       <c r="G80">
         <v>3543.4</v>
@@ -7847,37 +7847,37 @@
         <v>1052.8</v>
       </c>
       <c r="M80">
-        <v>2299.88621823697</v>
+        <v>2329.371938983598</v>
       </c>
       <c r="N80">
-        <v>-1247.08621823697</v>
+        <v>-1276.571938983598</v>
       </c>
       <c r="O80">
-        <v>-124.708621823697</v>
+        <v>-127.6571938983598</v>
       </c>
       <c r="P80">
-        <v>-1122.377596413273</v>
+        <v>-1148.914745085239</v>
       </c>
       <c r="Q80">
-        <v>102.9224035867267</v>
+        <v>76.38525491476139</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1623017577349786</v>
+        <v>0.1678494604842633</v>
       </c>
       <c r="T80">
-        <v>2.335121618789834</v>
+        <v>2.446317886351255</v>
       </c>
       <c r="U80">
         <v>0.2056889784279693</v>
       </c>
       <c r="V80">
-        <v>0.04577617760617078</v>
+        <v>0.04519673232001672</v>
       </c>
       <c r="W80">
-        <v>0.1962733232198187</v>
+        <v>0.1963925087287826</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4577617760617078</v>
+        <v>0.4519673232001671</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1903984685974336</v>
+        <v>0.1919973583817133</v>
       </c>
       <c r="C81">
-        <v>-2327.044492722389</v>
+        <v>-2507.131793433884</v>
       </c>
       <c r="D81">
-        <v>5454.284507277613</v>
+        <v>5417.548206566118</v>
       </c>
       <c r="E81">
-        <v>7152.229000000001</v>
+        <v>7295.580000000002</v>
       </c>
       <c r="F81">
-        <v>11324.729</v>
+        <v>11468.08</v>
       </c>
       <c r="G81">
         <v>3543.4</v>
@@ -7929,37 +7929,37 @@
         <v>1052.8</v>
       </c>
       <c r="M81">
-        <v>2329.371938983598</v>
+        <v>2358.857659730226</v>
       </c>
       <c r="N81">
-        <v>-1276.571938983598</v>
+        <v>-1306.057659730226</v>
       </c>
       <c r="O81">
-        <v>-127.6571938983598</v>
+        <v>-130.6057659730226</v>
       </c>
       <c r="P81">
-        <v>-1148.914745085239</v>
+        <v>-1175.451893757204</v>
       </c>
       <c r="Q81">
-        <v>76.38525491476139</v>
+        <v>49.84810624279635</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1678494604842633</v>
+        <v>0.1739519335084765</v>
       </c>
       <c r="T81">
-        <v>2.446317886351255</v>
+        <v>2.568633780668817</v>
       </c>
       <c r="U81">
         <v>0.2056889784279693</v>
       </c>
       <c r="V81">
-        <v>0.04519673232001672</v>
+        <v>0.04463177316601651</v>
       </c>
       <c r="W81">
-        <v>0.1963925087287826</v>
+        <v>0.1965087146000225</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4519673232001671</v>
+        <v>0.446317731660165</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1919973583817133</v>
+        <v>0.193596248165993</v>
       </c>
       <c r="C82">
-        <v>-2507.131793433884</v>
+        <v>-2686.727544090421</v>
       </c>
       <c r="D82">
-        <v>5417.548206566118</v>
+        <v>5381.303455909579</v>
       </c>
       <c r="E82">
-        <v>7295.580000000002</v>
+        <v>7438.931</v>
       </c>
       <c r="F82">
-        <v>11468.08</v>
+        <v>11611.431</v>
       </c>
       <c r="G82">
         <v>3543.4</v>
@@ -8011,37 +8011,37 @@
         <v>1052.8</v>
       </c>
       <c r="M82">
-        <v>2358.857659730226</v>
+        <v>2388.343380476854</v>
       </c>
       <c r="N82">
-        <v>-1306.057659730226</v>
+        <v>-1335.543380476854</v>
       </c>
       <c r="O82">
-        <v>-130.6057659730226</v>
+        <v>-133.5543380476854</v>
       </c>
       <c r="P82">
-        <v>-1175.451893757204</v>
+        <v>-1201.989042429168</v>
       </c>
       <c r="Q82">
-        <v>49.84810624279635</v>
+        <v>23.31095757083153</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1739519335084765</v>
+        <v>0.1806967721141858</v>
       </c>
       <c r="T82">
-        <v>2.568633780668817</v>
+        <v>2.703825032282966</v>
       </c>
       <c r="U82">
         <v>0.2056889784279693</v>
       </c>
       <c r="V82">
-        <v>0.04463177316601651</v>
+        <v>0.04408076362075705</v>
       </c>
       <c r="W82">
-        <v>0.1965087146000225</v>
+        <v>0.1966220511904909</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.446317731660165</v>
+        <v>0.4408076362075705</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.193596248165993</v>
+        <v>0.1951951379502727</v>
       </c>
       <c r="C83">
-        <v>-2686.727544090421</v>
+        <v>-2865.841544904069</v>
       </c>
       <c r="D83">
-        <v>5381.303455909579</v>
+        <v>5345.540455095931</v>
       </c>
       <c r="E83">
-        <v>7438.931</v>
+        <v>7582.282000000001</v>
       </c>
       <c r="F83">
-        <v>11611.431</v>
+        <v>11754.782</v>
       </c>
       <c r="G83">
         <v>3543.4</v>
@@ -8093,37 +8093,37 @@
         <v>1052.8</v>
       </c>
       <c r="M83">
-        <v>2388.343380476854</v>
+        <v>2417.829101223482</v>
       </c>
       <c r="N83">
-        <v>-1335.543380476854</v>
+        <v>-1365.029101223482</v>
       </c>
       <c r="O83">
-        <v>-133.5543380476854</v>
+        <v>-136.5029101223482</v>
       </c>
       <c r="P83">
-        <v>-1201.989042429168</v>
+        <v>-1228.526191101134</v>
       </c>
       <c r="Q83">
-        <v>23.31095757083153</v>
+        <v>-3.226191101133736</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1806967721141858</v>
+        <v>0.1881910372316405</v>
       </c>
       <c r="T83">
-        <v>2.703825032282966</v>
+        <v>2.854037534076463</v>
       </c>
       <c r="U83">
         <v>0.2056889784279693</v>
       </c>
       <c r="V83">
-        <v>0.04408076362075705</v>
+        <v>0.04354319333269903</v>
       </c>
       <c r="W83">
-        <v>0.1966220511904909</v>
+        <v>0.1967326234738748</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4408076362075705</v>
+        <v>0.4354319333269903</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1951951379502727</v>
+        <v>0.1967940277345523</v>
       </c>
       <c r="C84">
-        <v>-2865.841544904069</v>
+        <v>-3044.483337286303</v>
       </c>
       <c r="D84">
-        <v>5345.540455095931</v>
+        <v>5310.249662713699</v>
       </c>
       <c r="E84">
-        <v>7582.282000000001</v>
+        <v>7725.633000000002</v>
       </c>
       <c r="F84">
-        <v>11754.782</v>
+        <v>11898.133</v>
       </c>
       <c r="G84">
         <v>3543.4</v>
@@ -8175,37 +8175,37 @@
         <v>1052.8</v>
       </c>
       <c r="M84">
-        <v>2417.829101223482</v>
+        <v>2447.31482197011</v>
       </c>
       <c r="N84">
-        <v>-1365.029101223482</v>
+        <v>-1394.51482197011</v>
       </c>
       <c r="O84">
-        <v>-136.5029101223482</v>
+        <v>-139.451482197011</v>
       </c>
       <c r="P84">
-        <v>-1228.526191101134</v>
+        <v>-1255.063339773099</v>
       </c>
       <c r="Q84">
-        <v>-3.226191101133736</v>
+        <v>-29.76333977309878</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1881910372316405</v>
+        <v>0.1965669805982077</v>
       </c>
       <c r="T84">
-        <v>2.854037534076463</v>
+        <v>3.021922094904492</v>
       </c>
       <c r="U84">
         <v>0.2056889784279693</v>
       </c>
       <c r="V84">
-        <v>0.04354319333269903</v>
+        <v>0.04301857654555807</v>
       </c>
       <c r="W84">
-        <v>0.1967326234738748</v>
+        <v>0.196840531364888</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4354319333269903</v>
+        <v>0.4301857654555807</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1967940277345523</v>
+        <v>0.1983929175188321</v>
       </c>
       <c r="C85">
-        <v>-3044.483337286303</v>
+        <v>-3222.662212334882</v>
       </c>
       <c r="D85">
-        <v>5310.249662713699</v>
+        <v>5275.42178766512</v>
       </c>
       <c r="E85">
-        <v>7725.633000000002</v>
+        <v>7868.984000000002</v>
       </c>
       <c r="F85">
-        <v>11898.133</v>
+        <v>12041.484</v>
       </c>
       <c r="G85">
         <v>3543.4</v>
@@ -8257,37 +8257,37 @@
         <v>1052.8</v>
       </c>
       <c r="M85">
-        <v>2447.31482197011</v>
+        <v>2476.800542716738</v>
       </c>
       <c r="N85">
-        <v>-1394.51482197011</v>
+        <v>-1424.000542716738</v>
       </c>
       <c r="O85">
-        <v>-139.451482197011</v>
+        <v>-142.4000542716738</v>
       </c>
       <c r="P85">
-        <v>-1255.063339773099</v>
+        <v>-1281.600488445064</v>
       </c>
       <c r="Q85">
-        <v>-29.76333977309878</v>
+        <v>-56.30048844506405</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1965669805982077</v>
+        <v>0.2059899168855956</v>
       </c>
       <c r="T85">
-        <v>3.021922094904492</v>
+        <v>3.210792225836022</v>
       </c>
       <c r="U85">
         <v>0.2056889784279693</v>
       </c>
       <c r="V85">
-        <v>0.04301857654555807</v>
+        <v>0.04250645063430143</v>
       </c>
       <c r="W85">
-        <v>0.196840531364888</v>
+        <v>0.1969458700204009</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4301857654555807</v>
+        <v>0.4250645063430143</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.198392917518832</v>
+        <v>0.1999918073031117</v>
       </c>
       <c r="C86">
-        <v>-3222.662212334879</v>
+        <v>-3400.387218988908</v>
       </c>
       <c r="D86">
-        <v>5275.421787665121</v>
+        <v>5241.047781011092</v>
       </c>
       <c r="E86">
-        <v>7868.984</v>
+        <v>8012.334999999999</v>
       </c>
       <c r="F86">
-        <v>12041.484</v>
+        <v>12184.835</v>
       </c>
       <c r="G86">
         <v>3543.4</v>
@@ -8339,37 +8339,37 @@
         <v>1052.8</v>
       </c>
       <c r="M86">
-        <v>2476.800542716737</v>
+        <v>2506.286263463365</v>
       </c>
       <c r="N86">
-        <v>-1424.000542716737</v>
+        <v>-1453.486263463365</v>
       </c>
       <c r="O86">
-        <v>-142.4000542716737</v>
+        <v>-145.3486263463365</v>
       </c>
       <c r="P86">
-        <v>-1281.600488445064</v>
+        <v>-1308.137637117028</v>
       </c>
       <c r="Q86">
-        <v>-56.30048844506359</v>
+        <v>-82.83763711702841</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2059899168855955</v>
+        <v>0.2166692446779686</v>
       </c>
       <c r="T86">
-        <v>3.21079222583602</v>
+        <v>3.424845040891755</v>
       </c>
       <c r="U86">
         <v>0.2056889784279693</v>
       </c>
       <c r="V86">
-        <v>0.04250645063430144</v>
+        <v>0.04200637474448613</v>
       </c>
       <c r="W86">
-        <v>0.1969458700204009</v>
+        <v>0.1970487301193135</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4250645063430144</v>
+        <v>0.4200637474448613</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1999918073031117</v>
+        <v>0.2015906970873914</v>
       </c>
       <c r="C87">
-        <v>-3400.387218988908</v>
+        <v>-3577.667171867155</v>
       </c>
       <c r="D87">
-        <v>5241.047781011092</v>
+        <v>5207.118828132845</v>
       </c>
       <c r="E87">
-        <v>8012.334999999999</v>
+        <v>8155.686</v>
       </c>
       <c r="F87">
-        <v>12184.835</v>
+        <v>12328.186</v>
       </c>
       <c r="G87">
         <v>3543.4</v>
@@ -8421,37 +8421,37 @@
         <v>1052.8</v>
       </c>
       <c r="M87">
-        <v>2506.286263463365</v>
+        <v>2535.771984209993</v>
       </c>
       <c r="N87">
-        <v>-1453.486263463365</v>
+        <v>-1482.971984209993</v>
       </c>
       <c r="O87">
-        <v>-145.3486263463365</v>
+        <v>-148.2971984209993</v>
       </c>
       <c r="P87">
-        <v>-1308.137637117028</v>
+        <v>-1334.674785788994</v>
       </c>
       <c r="Q87">
-        <v>-82.83763711702841</v>
+        <v>-109.3747857889937</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2166692446779686</v>
+        <v>0.2288741907263949</v>
       </c>
       <c r="T87">
-        <v>3.424845040891755</v>
+        <v>3.66947682952688</v>
       </c>
       <c r="U87">
         <v>0.2056889784279693</v>
       </c>
       <c r="V87">
-        <v>0.04200637474448613</v>
+        <v>0.04151792852652699</v>
       </c>
       <c r="W87">
-        <v>0.1970487301193135</v>
+        <v>0.1971491981229025</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4200637474448613</v>
+        <v>0.4151792852652698</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2015906970873914</v>
+        <v>0.2031895868716711</v>
       </c>
       <c r="C88">
-        <v>-3577.667171867155</v>
+        <v>-3754.510658803847</v>
       </c>
       <c r="D88">
-        <v>5207.118828132845</v>
+        <v>5173.626341196154</v>
       </c>
       <c r="E88">
-        <v>8155.686</v>
+        <v>8299.037</v>
       </c>
       <c r="F88">
-        <v>12328.186</v>
+        <v>12471.537</v>
       </c>
       <c r="G88">
         <v>3543.4</v>
@@ -8503,37 +8503,37 @@
         <v>1052.8</v>
       </c>
       <c r="M88">
-        <v>2535.771984209993</v>
+        <v>2565.257704956621</v>
       </c>
       <c r="N88">
-        <v>-1482.971984209993</v>
+        <v>-1512.457704956621</v>
       </c>
       <c r="O88">
-        <v>-148.2971984209993</v>
+        <v>-151.2457704956621</v>
       </c>
       <c r="P88">
-        <v>-1334.674785788994</v>
+        <v>-1361.211934460959</v>
       </c>
       <c r="Q88">
-        <v>-109.3747857889937</v>
+        <v>-135.9119344609587</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2288741907263949</v>
+        <v>0.2429568207822714</v>
       </c>
       <c r="T88">
-        <v>3.66947682952688</v>
+        <v>3.951744277952025</v>
       </c>
       <c r="U88">
         <v>0.2056889784279693</v>
       </c>
       <c r="V88">
-        <v>0.04151792852652699</v>
+        <v>0.04104071095725656</v>
       </c>
       <c r="W88">
-        <v>0.1971491981229025</v>
+        <v>0.1972473565172136</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4151792852652698</v>
+        <v>0.4104071095725655</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2031895868716711</v>
+        <v>0.2047884766559508</v>
       </c>
       <c r="C89">
-        <v>-3754.510658803847</v>
+        <v>-3930.926048095529</v>
       </c>
       <c r="D89">
-        <v>5173.626341196154</v>
+        <v>5140.561951904471</v>
       </c>
       <c r="E89">
-        <v>8299.037</v>
+        <v>8442.388000000001</v>
       </c>
       <c r="F89">
-        <v>12471.537</v>
+        <v>12614.888</v>
       </c>
       <c r="G89">
         <v>3543.4</v>
@@ -8585,37 +8585,37 @@
         <v>1052.8</v>
       </c>
       <c r="M89">
-        <v>2565.257704956621</v>
+        <v>2594.743425703249</v>
       </c>
       <c r="N89">
-        <v>-1512.457704956621</v>
+        <v>-1541.943425703249</v>
       </c>
       <c r="O89">
-        <v>-151.2457704956621</v>
+        <v>-154.1943425703249</v>
       </c>
       <c r="P89">
-        <v>-1361.211934460959</v>
+        <v>-1387.749083132924</v>
       </c>
       <c r="Q89">
-        <v>-135.9119344609587</v>
+        <v>-162.449083132924</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2429568207822714</v>
+        <v>0.2593865558474607</v>
       </c>
       <c r="T89">
-        <v>3.951744277952025</v>
+        <v>4.281056301114694</v>
       </c>
       <c r="U89">
         <v>0.2056889784279693</v>
       </c>
       <c r="V89">
-        <v>0.04104071095725656</v>
+        <v>0.04057433924183319</v>
       </c>
       <c r="W89">
-        <v>0.1972473565172136</v>
+        <v>0.1973432840389267</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4104071095725655</v>
+        <v>0.4057433924183319</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2047884766559508</v>
+        <v>0.2063873664402305</v>
       </c>
       <c r="C90">
-        <v>-3930.926048095529</v>
+        <v>-4106.921495471768</v>
       </c>
       <c r="D90">
-        <v>5140.561951904471</v>
+        <v>5107.917504528234</v>
       </c>
       <c r="E90">
-        <v>8442.388000000001</v>
+        <v>8585.739000000001</v>
       </c>
       <c r="F90">
-        <v>12614.888</v>
+        <v>12758.239</v>
       </c>
       <c r="G90">
         <v>3543.4</v>
@@ -8667,37 +8667,37 @@
         <v>1052.8</v>
       </c>
       <c r="M90">
-        <v>2594.743425703249</v>
+        <v>2624.229146449877</v>
       </c>
       <c r="N90">
-        <v>-1541.943425703249</v>
+        <v>-1571.429146449877</v>
       </c>
       <c r="O90">
-        <v>-154.1943425703249</v>
+        <v>-157.1429146449877</v>
       </c>
       <c r="P90">
-        <v>-1387.749083132924</v>
+        <v>-1414.286231804889</v>
       </c>
       <c r="Q90">
-        <v>-162.449083132924</v>
+        <v>-188.986231804889</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2593865558474607</v>
+        <v>0.2788035154699572</v>
       </c>
       <c r="T90">
-        <v>4.281056301114694</v>
+        <v>4.670243237579667</v>
       </c>
       <c r="U90">
         <v>0.2056889784279693</v>
       </c>
       <c r="V90">
-        <v>0.04057433924183319</v>
+        <v>0.04011844778967776</v>
       </c>
       <c r="W90">
-        <v>0.1973432840389267</v>
+        <v>0.1974370558859946</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4057433924183319</v>
+        <v>0.4011844778967776</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2063873664402305</v>
+        <v>0.2079862562245102</v>
       </c>
       <c r="C91">
-        <v>-4106.921495471768</v>
+        <v>-4282.504950801973</v>
       </c>
       <c r="D91">
-        <v>5107.917504528234</v>
+        <v>5075.685049198028</v>
       </c>
       <c r="E91">
-        <v>8585.739000000001</v>
+        <v>8729.09</v>
       </c>
       <c r="F91">
-        <v>12758.239</v>
+        <v>12901.59</v>
       </c>
       <c r="G91">
         <v>3543.4</v>
@@ -8749,37 +8749,37 @@
         <v>1052.8</v>
       </c>
       <c r="M91">
-        <v>2624.229146449877</v>
+        <v>2653.714867196504</v>
       </c>
       <c r="N91">
-        <v>-1571.429146449877</v>
+        <v>-1600.914867196504</v>
       </c>
       <c r="O91">
-        <v>-157.1429146449877</v>
+        <v>-160.0914867196504</v>
       </c>
       <c r="P91">
-        <v>-1414.286231804889</v>
+        <v>-1440.823380476854</v>
       </c>
       <c r="Q91">
-        <v>-188.986231804889</v>
+        <v>-215.5233804768538</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2788035154699572</v>
+        <v>0.302103867016953</v>
       </c>
       <c r="T91">
-        <v>4.670243237579667</v>
+        <v>5.137267561337635</v>
       </c>
       <c r="U91">
         <v>0.2056889784279693</v>
       </c>
       <c r="V91">
-        <v>0.04011844778967776</v>
+        <v>0.03967268725868134</v>
       </c>
       <c r="W91">
-        <v>0.1974370558859946</v>
+        <v>0.1975287439142388</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4011844778967776</v>
+        <v>0.3967268725868134</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2079862562245102</v>
+        <v>0.2095851460087899</v>
       </c>
       <c r="C92">
-        <v>-4282.504950801973</v>
+        <v>-4457.684164549843</v>
       </c>
       <c r="D92">
-        <v>5075.685049198028</v>
+        <v>5043.856835450159</v>
       </c>
       <c r="E92">
-        <v>8729.09</v>
+        <v>8872.441000000001</v>
       </c>
       <c r="F92">
-        <v>12901.59</v>
+        <v>13044.941</v>
       </c>
       <c r="G92">
         <v>3543.4</v>
@@ -8831,37 +8831,37 @@
         <v>1052.8</v>
       </c>
       <c r="M92">
-        <v>2653.714867196504</v>
+        <v>2683.200587943132</v>
       </c>
       <c r="N92">
-        <v>-1600.914867196504</v>
+        <v>-1630.400587943132</v>
       </c>
       <c r="O92">
-        <v>-160.0914867196504</v>
+        <v>-163.0400587943132</v>
       </c>
       <c r="P92">
-        <v>-1440.823380476854</v>
+        <v>-1467.360529148819</v>
       </c>
       <c r="Q92">
-        <v>-215.5233804768538</v>
+        <v>-242.0605291488191</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.302103867016953</v>
+        <v>0.330582074463281</v>
       </c>
       <c r="T92">
-        <v>5.137267561337635</v>
+        <v>5.708075068152927</v>
       </c>
       <c r="U92">
         <v>0.2056889784279693</v>
       </c>
       <c r="V92">
-        <v>0.03967268725868134</v>
+        <v>0.0392367236624321</v>
       </c>
       <c r="W92">
-        <v>0.1975287439142388</v>
+        <v>0.1976184168209831</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3967268725868134</v>
+        <v>0.3923672366243209</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2095851460087899</v>
+        <v>0.2111840357930696</v>
       </c>
       <c r="C93">
-        <v>-4457.684164549843</v>
+        <v>-4632.466693986487</v>
       </c>
       <c r="D93">
-        <v>5043.856835450159</v>
+        <v>5012.425306013513</v>
       </c>
       <c r="E93">
-        <v>8872.441000000001</v>
+        <v>9015.792000000001</v>
       </c>
       <c r="F93">
-        <v>13044.941</v>
+        <v>13188.292</v>
       </c>
       <c r="G93">
         <v>3543.4</v>
@@ -8913,37 +8913,37 @@
         <v>1052.8</v>
       </c>
       <c r="M93">
-        <v>2683.200587943132</v>
+        <v>2712.68630868976</v>
       </c>
       <c r="N93">
-        <v>-1630.400587943132</v>
+        <v>-1659.88630868976</v>
       </c>
       <c r="O93">
-        <v>-163.0400587943132</v>
+        <v>-165.988630868976</v>
       </c>
       <c r="P93">
-        <v>-1467.360529148819</v>
+        <v>-1493.897677820784</v>
       </c>
       <c r="Q93">
-        <v>-242.0605291488191</v>
+        <v>-268.5976778207839</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.330582074463281</v>
+        <v>0.3661798337711913</v>
       </c>
       <c r="T93">
-        <v>5.708075068152927</v>
+        <v>6.421584451672046</v>
       </c>
       <c r="U93">
         <v>0.2056889784279693</v>
       </c>
       <c r="V93">
-        <v>0.0392367236624321</v>
+        <v>0.03881023753566654</v>
       </c>
       <c r="W93">
-        <v>0.1976184168209831</v>
+        <v>0.1977061403167112</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3923672366243209</v>
+        <v>0.3881023753566653</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2111840357930696</v>
+        <v>0.2127829255773493</v>
       </c>
       <c r="C94">
-        <v>-4632.466693986487</v>
+        <v>-4806.859909172714</v>
       </c>
       <c r="D94">
-        <v>5012.425306013513</v>
+        <v>4981.383090827288</v>
       </c>
       <c r="E94">
-        <v>9015.792000000001</v>
+        <v>9159.143000000002</v>
       </c>
       <c r="F94">
-        <v>13188.292</v>
+        <v>13331.643</v>
       </c>
       <c r="G94">
         <v>3543.4</v>
@@ -8995,37 +8995,37 @@
         <v>1052.8</v>
       </c>
       <c r="M94">
-        <v>2712.68630868976</v>
+        <v>2742.172029436388</v>
       </c>
       <c r="N94">
-        <v>-1659.88630868976</v>
+        <v>-1689.372029436388</v>
       </c>
       <c r="O94">
-        <v>-165.988630868976</v>
+        <v>-168.9372029436388</v>
       </c>
       <c r="P94">
-        <v>-1493.897677820784</v>
+        <v>-1520.434826492749</v>
       </c>
       <c r="Q94">
-        <v>-268.5976778207839</v>
+        <v>-295.134826492749</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3661798337711913</v>
+        <v>0.4119483814527901</v>
       </c>
       <c r="T94">
-        <v>6.421584451672046</v>
+        <v>7.338953659053767</v>
       </c>
       <c r="U94">
         <v>0.2056889784279693</v>
       </c>
       <c r="V94">
-        <v>0.03881023753566654</v>
+        <v>0.03839292315356259</v>
       </c>
       <c r="W94">
-        <v>0.1977061403167112</v>
+        <v>0.1977919772856495</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3881023753566653</v>
+        <v>0.3839292315356259</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2127829255773493</v>
+        <v>0.214381815361629</v>
       </c>
       <c r="C95">
-        <v>-4806.859909172714</v>
+        <v>-4980.870998720329</v>
       </c>
       <c r="D95">
-        <v>4981.383090827288</v>
+        <v>4950.723001279672</v>
       </c>
       <c r="E95">
-        <v>9159.143000000002</v>
+        <v>9302.494000000001</v>
       </c>
       <c r="F95">
-        <v>13331.643</v>
+        <v>13474.994</v>
       </c>
       <c r="G95">
         <v>3543.4</v>
@@ -9077,37 +9077,37 @@
         <v>1052.8</v>
       </c>
       <c r="M95">
-        <v>2742.172029436388</v>
+        <v>2771.657750183015</v>
       </c>
       <c r="N95">
-        <v>-1689.372029436388</v>
+        <v>-1718.857750183015</v>
       </c>
       <c r="O95">
-        <v>-168.9372029436388</v>
+        <v>-171.8857750183015</v>
       </c>
       <c r="P95">
-        <v>-1520.434826492749</v>
+        <v>-1546.971975164714</v>
       </c>
       <c r="Q95">
-        <v>-295.134826492749</v>
+        <v>-321.6719751647138</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4119483814527901</v>
+        <v>0.472973111694922</v>
       </c>
       <c r="T95">
-        <v>7.338953659053767</v>
+        <v>8.562112602229398</v>
       </c>
       <c r="U95">
         <v>0.2056889784279693</v>
       </c>
       <c r="V95">
-        <v>0.03839292315356259</v>
+        <v>0.03798448780086512</v>
       </c>
       <c r="W95">
-        <v>0.1977919772856495</v>
+        <v>0.1978759879360996</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3839292315356259</v>
+        <v>0.3798448780086512</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.214381815361629</v>
+        <v>0.2159807051459087</v>
       </c>
       <c r="C96">
-        <v>-4980.870998720329</v>
+        <v>-5154.506975342045</v>
       </c>
       <c r="D96">
-        <v>4950.723001279672</v>
+        <v>4920.438024657956</v>
       </c>
       <c r="E96">
-        <v>9302.494000000001</v>
+        <v>9445.845000000001</v>
       </c>
       <c r="F96">
-        <v>13474.994</v>
+        <v>13618.345</v>
       </c>
       <c r="G96">
         <v>3543.4</v>
@@ -9159,37 +9159,37 @@
         <v>1052.8</v>
       </c>
       <c r="M96">
-        <v>2771.657750183015</v>
+        <v>2801.143470929643</v>
       </c>
       <c r="N96">
-        <v>-1718.857750183015</v>
+        <v>-1748.343470929643</v>
       </c>
       <c r="O96">
-        <v>-171.8857750183015</v>
+        <v>-174.8343470929643</v>
       </c>
       <c r="P96">
-        <v>-1546.971975164714</v>
+        <v>-1573.509123836679</v>
       </c>
       <c r="Q96">
-        <v>-321.6719751647138</v>
+        <v>-348.2091238366791</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.472973111694922</v>
+        <v>0.5584077340339065</v>
       </c>
       <c r="T96">
-        <v>8.562112602229398</v>
+        <v>10.27453512267528</v>
       </c>
       <c r="U96">
         <v>0.2056889784279693</v>
       </c>
       <c r="V96">
-        <v>0.03798448780086512</v>
+        <v>0.0375846510871718</v>
       </c>
       <c r="W96">
-        <v>0.1978759879360996</v>
+        <v>0.1979582299412772</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3798448780086512</v>
+        <v>0.3758465108717179</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2159807051459087</v>
+        <v>0.2175795949301884</v>
       </c>
       <c r="C97">
-        <v>-5154.506975342045</v>
+        <v>-5327.774681198871</v>
       </c>
       <c r="D97">
-        <v>4920.438024657956</v>
+        <v>4890.521318801131</v>
       </c>
       <c r="E97">
-        <v>9445.845000000001</v>
+        <v>9589.196000000002</v>
       </c>
       <c r="F97">
-        <v>13618.345</v>
+        <v>13761.696</v>
       </c>
       <c r="G97">
         <v>3543.4</v>
@@ -9241,37 +9241,37 @@
         <v>1052.8</v>
       </c>
       <c r="M97">
-        <v>2801.143470929643</v>
+        <v>2830.629191676271</v>
       </c>
       <c r="N97">
-        <v>-1748.343470929643</v>
+        <v>-1777.829191676271</v>
       </c>
       <c r="O97">
-        <v>-174.8343470929643</v>
+        <v>-177.7829191676271</v>
       </c>
       <c r="P97">
-        <v>-1573.509123836679</v>
+        <v>-1600.046272508644</v>
       </c>
       <c r="Q97">
-        <v>-348.2091238366791</v>
+        <v>-374.7462725086441</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5584077340339065</v>
+        <v>0.6865596675423834</v>
       </c>
       <c r="T97">
-        <v>10.27453512267528</v>
+        <v>12.84316890334411</v>
       </c>
       <c r="U97">
         <v>0.2056889784279693</v>
       </c>
       <c r="V97">
-        <v>0.0375846510871718</v>
+        <v>0.03719314430501375</v>
       </c>
       <c r="W97">
-        <v>0.1979582299412772</v>
+        <v>0.198038758571347</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3758465108717179</v>
+        <v>0.3719314430501376</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2175795949301884</v>
+        <v>0.219178484714468</v>
       </c>
       <c r="C98">
-        <v>-5327.774681198867</v>
+        <v>-5500.680793053625</v>
       </c>
       <c r="D98">
-        <v>4890.521318801133</v>
+        <v>4860.966206946375</v>
       </c>
       <c r="E98">
-        <v>9589.196</v>
+        <v>9732.547</v>
       </c>
       <c r="F98">
-        <v>13761.696</v>
+        <v>13905.047</v>
       </c>
       <c r="G98">
         <v>3543.4</v>
@@ -9323,37 +9323,37 @@
         <v>1052.8</v>
       </c>
       <c r="M98">
-        <v>2830.629191676271</v>
+        <v>2860.114912422899</v>
       </c>
       <c r="N98">
-        <v>-1777.829191676271</v>
+        <v>-1807.314912422899</v>
       </c>
       <c r="O98">
-        <v>-177.7829191676271</v>
+        <v>-180.7314912422899</v>
       </c>
       <c r="P98">
-        <v>-1600.046272508644</v>
+        <v>-1626.583421180609</v>
       </c>
       <c r="Q98">
-        <v>-374.7462725086436</v>
+        <v>-401.2834211806089</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6865596675423817</v>
+        <v>0.9001462233898422</v>
       </c>
       <c r="T98">
-        <v>12.84316890334407</v>
+        <v>17.12422520445876</v>
       </c>
       <c r="U98">
         <v>0.2056889784279693</v>
       </c>
       <c r="V98">
-        <v>0.03719314430501377</v>
+        <v>0.03680970982764249</v>
       </c>
       <c r="W98">
-        <v>0.198038758571347</v>
+        <v>0.1981176268172915</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3719314430501376</v>
+        <v>0.3680970982764249</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.219178484714468</v>
+        <v>0.2207773744987477</v>
       </c>
       <c r="C99">
-        <v>-5500.680793053625</v>
+        <v>-5673.231827238735</v>
       </c>
       <c r="D99">
-        <v>4860.966206946375</v>
+        <v>4831.766172761264</v>
       </c>
       <c r="E99">
-        <v>9732.547</v>
+        <v>9875.897999999999</v>
       </c>
       <c r="F99">
-        <v>13905.047</v>
+        <v>14048.398</v>
       </c>
       <c r="G99">
         <v>3543.4</v>
@@ -9405,37 +9405,37 @@
         <v>1052.8</v>
       </c>
       <c r="M99">
-        <v>2860.114912422899</v>
+        <v>2889.600633169526</v>
       </c>
       <c r="N99">
-        <v>-1807.314912422899</v>
+        <v>-1836.800633169526</v>
       </c>
       <c r="O99">
-        <v>-180.7314912422899</v>
+        <v>-183.6800633169526</v>
       </c>
       <c r="P99">
-        <v>-1626.583421180609</v>
+        <v>-1653.120569852574</v>
       </c>
       <c r="Q99">
-        <v>-401.2834211806089</v>
+        <v>-427.8205698525737</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9001462233898422</v>
+        <v>1.327319335084763</v>
       </c>
       <c r="T99">
-        <v>17.12422520445876</v>
+        <v>25.68633780668814</v>
       </c>
       <c r="U99">
         <v>0.2056889784279693</v>
       </c>
       <c r="V99">
-        <v>0.03680970982764249</v>
+        <v>0.03643410054368695</v>
       </c>
       <c r="W99">
-        <v>0.1981176268172915</v>
+        <v>0.1981948855071964</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3680970982764249</v>
+        <v>0.3643410054368695</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2207773744987477</v>
+        <v>0.2223762642830274</v>
       </c>
       <c r="C100">
-        <v>-5673.231827238735</v>
+        <v>-5845.434144445988</v>
       </c>
       <c r="D100">
-        <v>4831.766172761264</v>
+        <v>4802.914855554012</v>
       </c>
       <c r="E100">
-        <v>9875.897999999999</v>
+        <v>10019.249</v>
       </c>
       <c r="F100">
-        <v>14048.398</v>
+        <v>14191.749</v>
       </c>
       <c r="G100">
         <v>3543.4</v>
@@ -9487,37 +9487,37 @@
         <v>1052.8</v>
       </c>
       <c r="M100">
-        <v>2889.600633169526</v>
+        <v>2919.086353916154</v>
       </c>
       <c r="N100">
-        <v>-1836.800633169526</v>
+        <v>-1866.286353916154</v>
       </c>
       <c r="O100">
-        <v>-183.6800633169526</v>
+        <v>-186.6286353916154</v>
       </c>
       <c r="P100">
-        <v>-1653.120569852574</v>
+        <v>-1679.657718524539</v>
       </c>
       <c r="Q100">
-        <v>-427.8205698525737</v>
+        <v>-454.3577185245388</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.327319335084763</v>
+        <v>2.608838670169527</v>
       </c>
       <c r="T100">
-        <v>25.68633780668814</v>
+        <v>51.37267561337629</v>
       </c>
       <c r="U100">
         <v>0.2056889784279693</v>
       </c>
       <c r="V100">
-        <v>0.03643410054368695</v>
+        <v>0.03606607932607395</v>
       </c>
       <c r="W100">
-        <v>0.1981948855071964</v>
+        <v>0.198270583415487</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3643410054368695</v>
+        <v>0.3606607932607395</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2223762642830274</v>
-      </c>
-      <c r="C101">
-        <v>-5845.434144445988</v>
-      </c>
-      <c r="D101">
-        <v>4802.914855554012</v>
-      </c>
-      <c r="E101">
-        <v>10019.249</v>
-      </c>
-      <c r="F101">
-        <v>14191.749</v>
-      </c>
-      <c r="G101">
-        <v>3543.4</v>
-      </c>
-      <c r="H101">
-        <v>10162.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2278.1</v>
-      </c>
-      <c r="K101">
-        <v>1225.3</v>
-      </c>
-      <c r="L101">
-        <v>1052.8</v>
-      </c>
-      <c r="M101">
-        <v>2919.086353916154</v>
-      </c>
-      <c r="N101">
-        <v>-1866.286353916154</v>
-      </c>
-      <c r="O101">
-        <v>-186.6286353916154</v>
-      </c>
-      <c r="P101">
-        <v>-1679.657718524539</v>
-      </c>
-      <c r="Q101">
-        <v>-454.3577185245388</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.608838670169527</v>
-      </c>
-      <c r="T101">
-        <v>51.37267561337629</v>
-      </c>
-      <c r="U101">
-        <v>0.2056889784279693</v>
-      </c>
-      <c r="V101">
-        <v>0.03606607932607395</v>
-      </c>
-      <c r="W101">
-        <v>0.198270583415487</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3606607932607395</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
